--- a/data/01_core_entities.xlsx
+++ b/data/01_core_entities.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R0d85c5bd7d334717"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Companies" sheetId="2" r:id="R3fa610c475c84eb7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Entity Registry" sheetId="3" r:id="R58604567e59a4cbb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="R049e24b848594bc1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company System Footprints" sheetId="5" r:id="Rd36b9e2cef8d44ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="People" sheetId="6" r:id="Rf7294a539d664168"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leadership Roles" sheetId="7" r:id="R32a6b75e8a2f4480"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Dictionary" sheetId="8" r:id="Rbfc2fdd3da8343a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runtime Table Crosswalk" sheetId="9" r:id="R8fecdbee8a2f43d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Queue" sheetId="10" r:id="R4f21d1cc3e624811"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="Rc4cb51bf60074634"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Companies" sheetId="2" r:id="R9657bdf7eebc4340"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Entity Registry" sheetId="3" r:id="R17d7551a04674a4e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="Re0cd8d410bc04c0c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company System Footprints" sheetId="5" r:id="R2fa4be1ddcb44933"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="People" sheetId="6" r:id="R966e3ebca8af471a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leadership Roles" sheetId="7" r:id="R8e632ff23ef343b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Dictionary" sheetId="8" r:id="R07116593e03e4568"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runtime Table Crosswalk" sheetId="9" r:id="R4fa7483f4476427d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Queue" sheetId="10" r:id="R96a1e701c2d14161"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -71,7 +71,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="16">
+  <x:cellXfs count="17">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -96,6 +96,7 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -12197,29 +12198,35 @@
         <x:v>COMP_SEASPAN_CORP</x:v>
       </x:c>
       <x:c r="B264" s="14" t="str">
-        <x:v>Seaspan Corporation</x:v>
+        <x:v>Seaspan Corporation Pte. Ltd.</x:v>
       </x:c>
       <x:c r="C264" s="14" t="str">
-        <x:v>Shipowner / lessor</x:v>
-      </x:c>
-      <x:c r="D264" s="14"/>
-      <x:c r="E264" s="14"/>
+        <x:v>Shipowner / maritime asset owner</x:v>
+      </x:c>
+      <x:c r="D264" s="14" t="str"/>
+      <x:c r="E264" s="14" t="str">
+        <x:v>Singapore / global</x:v>
+      </x:c>
       <x:c r="F264" s="14" t="str">
-        <x:v>Subsidiary of Atlas Corp.</x:v>
+        <x:v>Wholly owned subsidiary of Atlas Corp.; Atlas privately held through Poseidon</x:v>
       </x:c>
       <x:c r="G264" s="14" t="str">
-        <x:v>Containership ownership; long-term chartering</x:v>
-      </x:c>
-      <x:c r="H264" s="14"/>
-      <x:c r="I264" s="14"/>
+        <x:v>Containership ownership; PCTC; long-term fixed-rate chartering; ship management</x:v>
+      </x:c>
+      <x:c r="H264" s="14" t="str">
+        <x:v>Bing Chen</x:v>
+      </x:c>
+      <x:c r="I264" s="14" t="str">
+        <x:v>Chairman, President &amp; CEO</x:v>
+      </x:c>
       <x:c r="J264" s="14" t="str">
-        <x:v>Keep distinct from Canadian Seaspan ULC</x:v>
+        <x:v>Current company fleet page: 227 vessels and approx. 2.4m TEU on a fully delivered basis</x:v>
       </x:c>
       <x:c r="K264" s="14" t="str">
         <x:v>Active</x:v>
       </x:c>
       <x:c r="L264" s="14" t="str">
-        <x:v>SRC_V125_017</x:v>
+        <x:v>SRC_V1251_006</x:v>
       </x:c>
       <x:c r="M264" s="14" t="str">
         <x:v>2026-09-09</x:v>
@@ -12242,20 +12249,22 @@
         <x:v>Canada</x:v>
       </x:c>
       <x:c r="F265" s="14" t="str">
-        <x:v>Washington Companies-related private group</x:v>
+        <x:v>Privately owned; Dennis Washington / Washington Companies structure</x:v>
       </x:c>
       <x:c r="G265" s="14" t="str">
         <x:v>Shipyards; ferries; tugs; barges; marine services</x:v>
       </x:c>
-      <x:c r="H265" s="14"/>
-      <x:c r="I265" s="14"/>
+      <x:c r="H265" s="14" t="str"/>
+      <x:c r="I265" s="14" t="str"/>
       <x:c r="J265" s="14" t="str">
-        <x:v>Distinct Canadian Seaspan structure</x:v>
+        <x:v>Canadian Seaspan group; includes Vancouver Shipyards, Victoria Shipyards, Vancouver Drydock and Seaspan Ferries</x:v>
       </x:c>
       <x:c r="K265" s="14" t="str">
         <x:v>Active</x:v>
       </x:c>
-      <x:c r="L265" s="14"/>
+      <x:c r="L265" s="14" t="str">
+        <x:v>SRC_V1251_008</x:v>
+      </x:c>
       <x:c r="M265" s="14" t="str">
         <x:v>2026-09-09</x:v>
       </x:c>
@@ -12303,23 +12312,33 @@
       <x:c r="C267" s="14" t="str">
         <x:v>Marine / defence industrial group</x:v>
       </x:c>
-      <x:c r="D267" s="14"/>
-      <x:c r="E267" s="14"/>
+      <x:c r="D267" s="14" t="str">
+        <x:v>London</x:v>
+      </x:c>
+      <x:c r="E267" s="14" t="str">
+        <x:v>United Kingdom</x:v>
+      </x:c>
       <x:c r="F267" s="14" t="str">
-        <x:v>Private</x:v>
+        <x:v>Private / UK-owned group</x:v>
       </x:c>
       <x:c r="G267" s="14" t="str">
-        <x:v>Shipbuilding; defence; marine industrial assets</x:v>
-      </x:c>
-      <x:c r="H267" s="14"/>
-      <x:c r="I267" s="14"/>
+        <x:v>Shipbuilding; defence; Arctic capability; ship repair; industrial fabrication; fleet support</x:v>
+      </x:c>
+      <x:c r="H267" s="14" t="str">
+        <x:v>Alex Vicefield</x:v>
+      </x:c>
+      <x:c r="I267" s="14" t="str">
+        <x:v>Chairman &amp; CEO</x:v>
+      </x:c>
       <x:c r="J267" s="14" t="str">
-        <x:v>Group seed for Davie and Helsinki Shipyard testing</x:v>
+        <x:v>Group companies include Davie, Helsinki Shipyard, Gulf Copper and Sata Shipbuilding</x:v>
       </x:c>
       <x:c r="K267" s="14" t="str">
         <x:v>Active</x:v>
       </x:c>
-      <x:c r="L267" s="14"/>
+      <x:c r="L267" s="14" t="str">
+        <x:v>SRC_V1251_001</x:v>
+      </x:c>
       <x:c r="M267" s="14" t="str">
         <x:v>2026-09-09</x:v>
       </x:c>
@@ -12341,20 +12360,26 @@
         <x:v>Canada</x:v>
       </x:c>
       <x:c r="F268" s="14" t="str">
-        <x:v>Inocea group company</x:v>
+        <x:v>Part of Inocea Group</x:v>
       </x:c>
       <x:c r="G268" s="14" t="str">
-        <x:v>Shipbuilding; repair; icebreakers; government programmes</x:v>
-      </x:c>
-      <x:c r="H268" s="14"/>
-      <x:c r="I268" s="14"/>
+        <x:v>Icebreakers; ferries; warships; shipbuilding; repair; modernization</x:v>
+      </x:c>
+      <x:c r="H268" s="14" t="str">
+        <x:v>Lindsey Kettel</x:v>
+      </x:c>
+      <x:c r="I268" s="14" t="str">
+        <x:v>President</x:v>
+      </x:c>
       <x:c r="J268" s="14" t="str">
-        <x:v>Canadian shipyard / defence-industrial asset</x:v>
+        <x:v>Canada's largest/highest-capacity shipbuilder; 2026 contract for six Canadian Coast Guard Program Icebreakers</x:v>
       </x:c>
       <x:c r="K268" s="14" t="str">
         <x:v>Active</x:v>
       </x:c>
-      <x:c r="L268" s="14"/>
+      <x:c r="L268" s="14" t="str">
+        <x:v>SRC_V1251_002</x:v>
+      </x:c>
       <x:c r="M268" s="14" t="str">
         <x:v>2026-09-09</x:v>
       </x:c>
@@ -12376,21 +12401,167 @@
         <x:v>Finland</x:v>
       </x:c>
       <x:c r="F269" s="14" t="str">
-        <x:v>Inocea group company</x:v>
+        <x:v>Davie / Inocea group company</x:v>
       </x:c>
       <x:c r="G269" s="14" t="str">
-        <x:v>Shipbuilding; ice-capable and Arctic vessels</x:v>
-      </x:c>
-      <x:c r="H269" s="14"/>
-      <x:c r="I269" s="14"/>
+        <x:v>Icebreakers; Arctic vessels; government vessels; cruise and ferry ships</x:v>
+      </x:c>
+      <x:c r="H269" s="14" t="str"/>
+      <x:c r="I269" s="14" t="str"/>
       <x:c r="J269" s="14" t="str">
-        <x:v>Finnish Arctic-capable shipyard</x:v>
+        <x:v>World-leading icebreaker specialist; acquisition by Davie completed November 2023</x:v>
       </x:c>
       <x:c r="K269" s="14" t="str">
         <x:v>Active</x:v>
       </x:c>
-      <x:c r="L269" s="14"/>
+      <x:c r="L269" s="14" t="str">
+        <x:v>SRC_V1251_003</x:v>
+      </x:c>
       <x:c r="M269" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="270">
+      <x:c r="A270" s="14" t="str">
+        <x:v>COMP_GULF_COPPER</x:v>
+      </x:c>
+      <x:c r="B270" s="14" t="str">
+        <x:v>Gulf Copper</x:v>
+      </x:c>
+      <x:c r="C270" s="14" t="str">
+        <x:v>Shipyard / repair group</x:v>
+      </x:c>
+      <x:c r="D270" s="14" t="str">
+        <x:v>Galveston</x:v>
+      </x:c>
+      <x:c r="E270" s="14" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="F270" s="14" t="str">
+        <x:v>Inocea-owned U.S. shipyard group following Davie Defense acquisition</x:v>
+      </x:c>
+      <x:c r="G270" s="14" t="str">
+        <x:v>Shipbuilding; ship repair; fabrication; naval support; Arctic Security Cutters</x:v>
+      </x:c>
+      <x:c r="H270" s="14" t="str"/>
+      <x:c r="I270" s="14" t="str"/>
+      <x:c r="J270" s="14" t="str">
+        <x:v>Texas shipyard group with facilities in Galveston and Port Arthur</x:v>
+      </x:c>
+      <x:c r="K270" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L270" s="14" t="str">
+        <x:v>SRC_V1251_004</x:v>
+      </x:c>
+      <x:c r="M270" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="271">
+      <x:c r="A271" s="14" t="str">
+        <x:v>COMP_SATA_SHIPBUILDING</x:v>
+      </x:c>
+      <x:c r="B271" s="14" t="str">
+        <x:v>Sata Shipbuilding</x:v>
+      </x:c>
+      <x:c r="C271" s="14" t="str">
+        <x:v>Heavy industrial fabricator</x:v>
+      </x:c>
+      <x:c r="D271" s="14" t="str">
+        <x:v>Pori</x:v>
+      </x:c>
+      <x:c r="E271" s="14" t="str">
+        <x:v>Finland</x:v>
+      </x:c>
+      <x:c r="F271" s="14" t="str">
+        <x:v>Inocea company</x:v>
+      </x:c>
+      <x:c r="G271" s="14" t="str">
+        <x:v>Heavy industrial fabrication; icebreakers; offshore; government vessels</x:v>
+      </x:c>
+      <x:c r="H271" s="14" t="str"/>
+      <x:c r="I271" s="14" t="str"/>
+      <x:c r="J271" s="14" t="str">
+        <x:v>Finland-based heavy industrial fabricator working with Helsinki Shipyard</x:v>
+      </x:c>
+      <x:c r="K271" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L271" s="14" t="str">
+        <x:v>SRC_V1251_001</x:v>
+      </x:c>
+      <x:c r="M271" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="272">
+      <x:c r="A272" s="14" t="str">
+        <x:v>COMP_DAVIE_DEFENSE</x:v>
+      </x:c>
+      <x:c r="B272" s="14" t="str">
+        <x:v>Davie Defense</x:v>
+      </x:c>
+      <x:c r="C272" s="14" t="str">
+        <x:v>Shipbuilding / defence company</x:v>
+      </x:c>
+      <x:c r="D272" s="14" t="str"/>
+      <x:c r="E272" s="14" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="F272" s="14" t="str">
+        <x:v>U.S. arm of Inocea / Davie</x:v>
+      </x:c>
+      <x:c r="G272" s="14" t="str">
+        <x:v>U.S. shipbuilding; Arctic Security Cutters; defence industrial base</x:v>
+      </x:c>
+      <x:c r="H272" s="14" t="str"/>
+      <x:c r="I272" s="14" t="str"/>
+      <x:c r="J272" s="14" t="str">
+        <x:v>Acquired Gulf Copper shipbuilding assets in Galveston and Port Arthur in December 2025</x:v>
+      </x:c>
+      <x:c r="K272" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L272" s="14" t="str">
+        <x:v>SRC_V1251_004</x:v>
+      </x:c>
+      <x:c r="M272" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="273">
+      <x:c r="A273" s="14" t="str">
+        <x:v>COMP_FEDERAL_FLEET</x:v>
+      </x:c>
+      <x:c r="B273" s="14" t="str">
+        <x:v>Federal Fleet Services</x:v>
+      </x:c>
+      <x:c r="C273" s="14" t="str">
+        <x:v>Fleet support / naval services</x:v>
+      </x:c>
+      <x:c r="D273" s="14" t="str"/>
+      <x:c r="E273" s="14" t="str">
+        <x:v>Canada</x:v>
+      </x:c>
+      <x:c r="F273" s="14" t="str">
+        <x:v>Inocea group company / platform</x:v>
+      </x:c>
+      <x:c r="G273" s="14" t="str">
+        <x:v>Naval support; auxiliary fleet operations; NATO support</x:v>
+      </x:c>
+      <x:c r="H273" s="14" t="str"/>
+      <x:c r="I273" s="14" t="str"/>
+      <x:c r="J273" s="14" t="str">
+        <x:v>Inocea identifies Federal Fleet Services as supporting NATO naval operations worldwide</x:v>
+      </x:c>
+      <x:c r="K273" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L273" s="14" t="str">
+        <x:v>SRC_V1251_001</x:v>
+      </x:c>
+      <x:c r="M273" s="14" t="str">
         <x:v>2026-09-09</x:v>
       </x:c>
     </x:row>
@@ -46604,6 +46775,314 @@
         <x:v>COMP_CONCOR</x:v>
       </x:c>
       <x:c r="F1819" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1820">
+      <x:c r="A1820" s="14" t="str">
+        <x:v>COMP_CLI</x:v>
+      </x:c>
+      <x:c r="B1820" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1820" s="14" t="str">
+        <x:v>Corredor Logística e Infraestrutura (CLI)</x:v>
+      </x:c>
+      <x:c r="D1820" s="14" t="str">
+        <x:v>Brazil</x:v>
+      </x:c>
+      <x:c r="E1820" s="14" t="str"/>
+      <x:c r="F1820" s="14" t="str">
+        <x:v>Active / acquisition pending</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1821">
+      <x:c r="A1821" s="14" t="str">
+        <x:v>COMP_CLI_NORTE</x:v>
+      </x:c>
+      <x:c r="B1821" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1821" s="14" t="str">
+        <x:v>CLI Norte</x:v>
+      </x:c>
+      <x:c r="D1821" s="14" t="str">
+        <x:v>Brazil</x:v>
+      </x:c>
+      <x:c r="E1821" s="14" t="str">
+        <x:v>COMP_CLI</x:v>
+      </x:c>
+      <x:c r="F1821" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1822">
+      <x:c r="A1822" s="14" t="str">
+        <x:v>COMP_CLI_SUL</x:v>
+      </x:c>
+      <x:c r="B1822" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1822" s="14" t="str">
+        <x:v>CLI Sul</x:v>
+      </x:c>
+      <x:c r="D1822" s="14" t="str">
+        <x:v>Brazil</x:v>
+      </x:c>
+      <x:c r="E1822" s="14" t="str">
+        <x:v>COMP_CLI</x:v>
+      </x:c>
+      <x:c r="F1822" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1823">
+      <x:c r="A1823" s="14" t="str">
+        <x:v>COMP_OMERS</x:v>
+      </x:c>
+      <x:c r="B1823" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1823" s="14" t="str">
+        <x:v>OMERS</x:v>
+      </x:c>
+      <x:c r="D1823" s="14" t="str">
+        <x:v>Canada</x:v>
+      </x:c>
+      <x:c r="E1823" s="14" t="str"/>
+      <x:c r="F1823" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1824">
+      <x:c r="A1824" s="14" t="str">
+        <x:v>COMP_OMERS_INFRA</x:v>
+      </x:c>
+      <x:c r="B1824" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1824" s="14" t="str">
+        <x:v>OMERS Infrastructure</x:v>
+      </x:c>
+      <x:c r="D1824" s="14" t="str">
+        <x:v>Canada</x:v>
+      </x:c>
+      <x:c r="E1824" s="14" t="str">
+        <x:v>COMP_OMERS</x:v>
+      </x:c>
+      <x:c r="F1824" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1825">
+      <x:c r="A1825" s="14" t="str">
+        <x:v>COMP_TRAPAC</x:v>
+      </x:c>
+      <x:c r="B1825" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1825" s="14" t="str">
+        <x:v>TraPac, LLC</x:v>
+      </x:c>
+      <x:c r="D1825" s="14" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="E1825" s="14" t="str"/>
+      <x:c r="F1825" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1826">
+      <x:c r="A1826" s="14" t="str">
+        <x:v>COMP_QUBE</x:v>
+      </x:c>
+      <x:c r="B1826" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1826" s="14" t="str">
+        <x:v>Qube Holdings</x:v>
+      </x:c>
+      <x:c r="D1826" s="14" t="str">
+        <x:v>Australia</x:v>
+      </x:c>
+      <x:c r="E1826" s="14" t="str"/>
+      <x:c r="F1826" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1827">
+      <x:c r="A1827" s="14" t="str">
+        <x:v>COMP_SEASPAN_CORP</x:v>
+      </x:c>
+      <x:c r="B1827" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1827" s="14" t="str">
+        <x:v>Seaspan Corporation Pte. Ltd.</x:v>
+      </x:c>
+      <x:c r="D1827" s="14" t="str"/>
+      <x:c r="E1827" s="14" t="str">
+        <x:v>COMP_ATLAS_CORP</x:v>
+      </x:c>
+      <x:c r="F1827" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1828">
+      <x:c r="A1828" s="14" t="str">
+        <x:v>COMP_SEASPAN_ULC</x:v>
+      </x:c>
+      <x:c r="B1828" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1828" s="14" t="str">
+        <x:v>Seaspan ULC</x:v>
+      </x:c>
+      <x:c r="D1828" s="14" t="str">
+        <x:v>Canada</x:v>
+      </x:c>
+      <x:c r="E1828" s="14" t="str">
+        <x:v>COMP_WASHINGTON_COS</x:v>
+      </x:c>
+      <x:c r="F1828" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1829">
+      <x:c r="A1829" s="14" t="str">
+        <x:v>COMP_INOCEA</x:v>
+      </x:c>
+      <x:c r="B1829" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1829" s="14" t="str">
+        <x:v>Inocea Group</x:v>
+      </x:c>
+      <x:c r="D1829" s="14" t="str">
+        <x:v>United Kingdom</x:v>
+      </x:c>
+      <x:c r="E1829" s="14" t="str"/>
+      <x:c r="F1829" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1830">
+      <x:c r="A1830" s="14" t="str">
+        <x:v>COMP_DAVIE</x:v>
+      </x:c>
+      <x:c r="B1830" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1830" s="14" t="str">
+        <x:v>Davie Shipbuilding</x:v>
+      </x:c>
+      <x:c r="D1830" s="14" t="str">
+        <x:v>Canada</x:v>
+      </x:c>
+      <x:c r="E1830" s="14" t="str">
+        <x:v>COMP_INOCEA</x:v>
+      </x:c>
+      <x:c r="F1830" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1831">
+      <x:c r="A1831" s="14" t="str">
+        <x:v>COMP_HELSINKI_SHIPYARD</x:v>
+      </x:c>
+      <x:c r="B1831" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1831" s="14" t="str">
+        <x:v>Helsinki Shipyard</x:v>
+      </x:c>
+      <x:c r="D1831" s="14" t="str">
+        <x:v>Finland</x:v>
+      </x:c>
+      <x:c r="E1831" s="14" t="str">
+        <x:v>COMP_DAVIE</x:v>
+      </x:c>
+      <x:c r="F1831" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1832">
+      <x:c r="A1832" s="14" t="str">
+        <x:v>COMP_GULF_COPPER</x:v>
+      </x:c>
+      <x:c r="B1832" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1832" s="14" t="str">
+        <x:v>Gulf Copper</x:v>
+      </x:c>
+      <x:c r="D1832" s="14" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="E1832" s="14" t="str">
+        <x:v>COMP_INOCEA</x:v>
+      </x:c>
+      <x:c r="F1832" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1833">
+      <x:c r="A1833" s="14" t="str">
+        <x:v>COMP_SATA_SHIPBUILDING</x:v>
+      </x:c>
+      <x:c r="B1833" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1833" s="14" t="str">
+        <x:v>Sata Shipbuilding</x:v>
+      </x:c>
+      <x:c r="D1833" s="14" t="str">
+        <x:v>Finland</x:v>
+      </x:c>
+      <x:c r="E1833" s="14" t="str">
+        <x:v>COMP_INOCEA</x:v>
+      </x:c>
+      <x:c r="F1833" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1834">
+      <x:c r="A1834" s="14" t="str">
+        <x:v>COMP_DAVIE_DEFENSE</x:v>
+      </x:c>
+      <x:c r="B1834" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1834" s="14" t="str">
+        <x:v>Davie Defense</x:v>
+      </x:c>
+      <x:c r="D1834" s="14" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="E1834" s="14" t="str">
+        <x:v>COMP_INOCEA</x:v>
+      </x:c>
+      <x:c r="F1834" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1835">
+      <x:c r="A1835" s="14" t="str">
+        <x:v>COMP_FEDERAL_FLEET</x:v>
+      </x:c>
+      <x:c r="B1835" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1835" s="14" t="str">
+        <x:v>Federal Fleet Services</x:v>
+      </x:c>
+      <x:c r="D1835" s="14" t="str">
+        <x:v>Canada</x:v>
+      </x:c>
+      <x:c r="E1835" s="14" t="str">
+        <x:v>COMP_INOCEA</x:v>
+      </x:c>
+      <x:c r="F1835" s="14" t="str">
         <x:v>Active</x:v>
       </x:c>
     </x:row>
@@ -49953,6 +50432,190 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="G145" s="14"/>
+    </x:row>
+    <x:row r="146">
+      <x:c r="A146" s="14" t="str">
+        <x:v>REL_V1251_001</x:v>
+      </x:c>
+      <x:c r="B146" s="14" t="str">
+        <x:v>COMP_DAVIE</x:v>
+      </x:c>
+      <x:c r="C146" s="14" t="str">
+        <x:v>OWNS / CONTROLS</x:v>
+      </x:c>
+      <x:c r="D146" s="14" t="str">
+        <x:v>COMP_HELSINKI_SHIPYARD</x:v>
+      </x:c>
+      <x:c r="E146" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F146" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G146" s="14" t="str">
+        <x:v>SRC_V1251_003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147">
+      <x:c r="A147" s="14" t="str">
+        <x:v>REL_V1251_002</x:v>
+      </x:c>
+      <x:c r="B147" s="14" t="str">
+        <x:v>COMP_INOCEA</x:v>
+      </x:c>
+      <x:c r="C147" s="14" t="str">
+        <x:v>OWNS / CONTROLS</x:v>
+      </x:c>
+      <x:c r="D147" s="14" t="str">
+        <x:v>COMP_GULF_COPPER</x:v>
+      </x:c>
+      <x:c r="E147" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F147" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G147" s="14" t="str">
+        <x:v>SRC_V1251_001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148">
+      <x:c r="A148" s="14" t="str">
+        <x:v>REL_V1251_003</x:v>
+      </x:c>
+      <x:c r="B148" s="14" t="str">
+        <x:v>COMP_INOCEA</x:v>
+      </x:c>
+      <x:c r="C148" s="14" t="str">
+        <x:v>OWNS / CONTROLS</x:v>
+      </x:c>
+      <x:c r="D148" s="14" t="str">
+        <x:v>COMP_SATA_SHIPBUILDING</x:v>
+      </x:c>
+      <x:c r="E148" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F148" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G148" s="14" t="str">
+        <x:v>SRC_V1251_001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149">
+      <x:c r="A149" s="14" t="str">
+        <x:v>REL_V1251_004</x:v>
+      </x:c>
+      <x:c r="B149" s="14" t="str">
+        <x:v>COMP_INOCEA</x:v>
+      </x:c>
+      <x:c r="C149" s="14" t="str">
+        <x:v>PARENT_OF</x:v>
+      </x:c>
+      <x:c r="D149" s="14" t="str">
+        <x:v>COMP_DAVIE_DEFENSE</x:v>
+      </x:c>
+      <x:c r="E149" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F149" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G149" s="14" t="str">
+        <x:v>SRC_V1251_004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150">
+      <x:c r="A150" s="14" t="str">
+        <x:v>REL_V1251_005</x:v>
+      </x:c>
+      <x:c r="B150" s="14" t="str">
+        <x:v>COMP_DAVIE_DEFENSE</x:v>
+      </x:c>
+      <x:c r="C150" s="14" t="str">
+        <x:v>ACQUIRED_ASSETS_OF</x:v>
+      </x:c>
+      <x:c r="D150" s="14" t="str">
+        <x:v>COMP_GULF_COPPER</x:v>
+      </x:c>
+      <x:c r="E150" s="14" t="str">
+        <x:v>2025-12-02</x:v>
+      </x:c>
+      <x:c r="F150" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G150" s="14" t="str">
+        <x:v>SRC_V1251_004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151">
+      <x:c r="A151" s="14" t="str">
+        <x:v>REL_V1251_006</x:v>
+      </x:c>
+      <x:c r="B151" s="14" t="str">
+        <x:v>COMP_INOCEA</x:v>
+      </x:c>
+      <x:c r="C151" s="14" t="str">
+        <x:v>PARENT_OF</x:v>
+      </x:c>
+      <x:c r="D151" s="14" t="str">
+        <x:v>COMP_FEDERAL_FLEET</x:v>
+      </x:c>
+      <x:c r="E151" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F151" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G151" s="14" t="str">
+        <x:v>SRC_V1251_001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152">
+      <x:c r="A152" s="14" t="str">
+        <x:v>REL_V1251_007</x:v>
+      </x:c>
+      <x:c r="B152" s="14" t="str">
+        <x:v>COMP_SEASPAN_CORP</x:v>
+      </x:c>
+      <x:c r="C152" s="14" t="str">
+        <x:v>CHARTER_PARTNER_OF</x:v>
+      </x:c>
+      <x:c r="D152" s="14" t="str">
+        <x:v>COMP_CMA_CGM</x:v>
+      </x:c>
+      <x:c r="E152" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F152" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G152" s="14" t="str">
+        <x:v>SRC_V1251_006</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153">
+      <x:c r="A153" s="14" t="str">
+        <x:v>REL_V1251_008</x:v>
+      </x:c>
+      <x:c r="B153" s="14" t="str">
+        <x:v>COMP_SEASPAN_CORP</x:v>
+      </x:c>
+      <x:c r="C153" s="14" t="str">
+        <x:v>CHARTER_PARTNER_OF</x:v>
+      </x:c>
+      <x:c r="D153" s="14" t="str">
+        <x:v>COMP_MAERSK</x:v>
+      </x:c>
+      <x:c r="E153" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F153" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G153" s="14" t="str">
+        <x:v>SRC_V1251_007</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/01_core_entities.xlsx
+++ b/data/01_core_entities.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="Rc4cb51bf60074634"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Companies" sheetId="2" r:id="R9657bdf7eebc4340"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Entity Registry" sheetId="3" r:id="R17d7551a04674a4e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="Re0cd8d410bc04c0c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company System Footprints" sheetId="5" r:id="R2fa4be1ddcb44933"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="People" sheetId="6" r:id="R966e3ebca8af471a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leadership Roles" sheetId="7" r:id="R8e632ff23ef343b3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Dictionary" sheetId="8" r:id="R07116593e03e4568"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runtime Table Crosswalk" sheetId="9" r:id="R4fa7483f4476427d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Queue" sheetId="10" r:id="R96a1e701c2d14161"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="Rdff8dd28273d48aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Companies" sheetId="2" r:id="R54fcf8d9e2014731"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Entity Registry" sheetId="3" r:id="Rc7ceabae050b4384"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="R817063df89f2477a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company System Footprints" sheetId="5" r:id="R54edc5104b494337"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="People" sheetId="6" r:id="R5c5bcd9183434fb7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leadership Roles" sheetId="7" r:id="R321d51cece6c43c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Dictionary" sheetId="8" r:id="Ree83608f69b847ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runtime Table Crosswalk" sheetId="9" r:id="Refb205667aa84608"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Queue" sheetId="10" r:id="Rd82d192c9bc2411a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -12565,6 +12565,1002 @@
         <x:v>2026-09-09</x:v>
       </x:c>
     </x:row>
+    <x:row r="274">
+      <x:c r="A274" s="14" t="str">
+        <x:v>COMP_EMAP</x:v>
+      </x:c>
+      <x:c r="B274" s="14" t="str">
+        <x:v>EMAP / Maranhão Port Administration</x:v>
+      </x:c>
+      <x:c r="C274" s="14" t="str">
+        <x:v>Port authority / public company</x:v>
+      </x:c>
+      <x:c r="D274" s="14" t="str">
+        <x:v>São Luís</x:v>
+      </x:c>
+      <x:c r="E274" s="14" t="str">
+        <x:v>Brazil</x:v>
+      </x:c>
+      <x:c r="F274" s="14" t="str">
+        <x:v>State port administrator</x:v>
+      </x:c>
+      <x:c r="G274" s="14" t="str">
+        <x:v>Port administration; port infrastructure</x:v>
+      </x:c>
+      <x:c r="H274" s="14" t="str"/>
+      <x:c r="I274" s="14" t="str"/>
+      <x:c r="J274" s="14" t="str">
+        <x:v>Administrator of the Port of Itaqui</x:v>
+      </x:c>
+      <x:c r="K274" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L274" s="14" t="str">
+        <x:v>SRC126_017</x:v>
+      </x:c>
+      <x:c r="M274" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="275">
+      <x:c r="A275" s="14" t="str">
+        <x:v>COMP_TEGRAM</x:v>
+      </x:c>
+      <x:c r="B275" s="14" t="str">
+        <x:v>TEGRAM</x:v>
+      </x:c>
+      <x:c r="C275" s="14" t="str">
+        <x:v>Terminal consortium / operating system</x:v>
+      </x:c>
+      <x:c r="D275" s="14" t="str">
+        <x:v>São Luís</x:v>
+      </x:c>
+      <x:c r="E275" s="14" t="str">
+        <x:v>Brazil</x:v>
+      </x:c>
+      <x:c r="F275" s="14" t="str">
+        <x:v>Consortium / shared terminal structure</x:v>
+      </x:c>
+      <x:c r="G275" s="14" t="str">
+        <x:v>Grain terminal; shared infrastructure</x:v>
+      </x:c>
+      <x:c r="H275" s="14" t="str"/>
+      <x:c r="I275" s="14" t="str"/>
+      <x:c r="J275" s="14" t="str">
+        <x:v>Shared grain-terminal system at Port of Itaqui</x:v>
+      </x:c>
+      <x:c r="K275" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L275" s="14" t="str">
+        <x:v>SRC126_016</x:v>
+      </x:c>
+      <x:c r="M275" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="276">
+      <x:c r="A276" s="14" t="str">
+        <x:v>COMP_VITERRA_BR</x:v>
+      </x:c>
+      <x:c r="B276" s="14" t="str">
+        <x:v>Viterra Logística e Terminais Portuários</x:v>
+      </x:c>
+      <x:c r="C276" s="14" t="str">
+        <x:v>Logistics / terminal company</x:v>
+      </x:c>
+      <x:c r="D276" s="14" t="str"/>
+      <x:c r="E276" s="14" t="str">
+        <x:v>Brazil</x:v>
+      </x:c>
+      <x:c r="F276" s="14" t="str"/>
+      <x:c r="G276" s="14" t="str">
+        <x:v>Grain logistics; terminal operations</x:v>
+      </x:c>
+      <x:c r="H276" s="14" t="str"/>
+      <x:c r="I276" s="14" t="str"/>
+      <x:c r="J276" s="14" t="str">
+        <x:v>TEGRAM participant</x:v>
+      </x:c>
+      <x:c r="K276" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L276" s="14" t="str">
+        <x:v>SRC126_016</x:v>
+      </x:c>
+      <x:c r="M276" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="277">
+      <x:c r="A277" s="14" t="str">
+        <x:v>COMP_TCN</x:v>
+      </x:c>
+      <x:c r="B277" s="14" t="str">
+        <x:v>Terminal Corredor Norte (TCN)</x:v>
+      </x:c>
+      <x:c r="C277" s="14" t="str">
+        <x:v>Terminal company</x:v>
+      </x:c>
+      <x:c r="D277" s="14" t="str"/>
+      <x:c r="E277" s="14" t="str">
+        <x:v>Brazil</x:v>
+      </x:c>
+      <x:c r="F277" s="14" t="str"/>
+      <x:c r="G277" s="14" t="str">
+        <x:v>Grain terminal / logistics</x:v>
+      </x:c>
+      <x:c r="H277" s="14" t="str"/>
+      <x:c r="I277" s="14" t="str"/>
+      <x:c r="J277" s="14" t="str">
+        <x:v>TEGRAM participant</x:v>
+      </x:c>
+      <x:c r="K277" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L277" s="14" t="str">
+        <x:v>SRC126_016</x:v>
+      </x:c>
+      <x:c r="M277" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="278">
+      <x:c r="A278" s="14" t="str">
+        <x:v>COMP_ALZ</x:v>
+      </x:c>
+      <x:c r="B278" s="14" t="str">
+        <x:v>ALZ Grãos</x:v>
+      </x:c>
+      <x:c r="C278" s="14" t="str">
+        <x:v>JV / grain logistics company</x:v>
+      </x:c>
+      <x:c r="D278" s="14" t="str"/>
+      <x:c r="E278" s="14" t="str">
+        <x:v>Brazil</x:v>
+      </x:c>
+      <x:c r="F278" s="14" t="str"/>
+      <x:c r="G278" s="14" t="str">
+        <x:v>Grain logistics / terminal participation</x:v>
+      </x:c>
+      <x:c r="H278" s="14" t="str"/>
+      <x:c r="I278" s="14" t="str"/>
+      <x:c r="J278" s="14" t="str">
+        <x:v>TEGRAM participant</x:v>
+      </x:c>
+      <x:c r="K278" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L278" s="14" t="str">
+        <x:v>SRC126_016</x:v>
+      </x:c>
+      <x:c r="M278" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="279">
+      <x:c r="A279" s="14" t="str">
+        <x:v>COMP_GULFLINK</x:v>
+      </x:c>
+      <x:c r="B279" s="14" t="str">
+        <x:v>GulfLink</x:v>
+      </x:c>
+      <x:c r="C279" s="14" t="str">
+        <x:v>Logistics JV</x:v>
+      </x:c>
+      <x:c r="D279" s="14" t="str"/>
+      <x:c r="E279" s="14" t="str">
+        <x:v>Kazakhstan</x:v>
+      </x:c>
+      <x:c r="F279" s="14" t="str">
+        <x:v>51% AD Ports Group / 49% KTZ Express</x:v>
+      </x:c>
+      <x:c r="G279" s="14" t="str">
+        <x:v>Multimodal logistics; rail; corridor services</x:v>
+      </x:c>
+      <x:c r="H279" s="14" t="str"/>
+      <x:c r="I279" s="14" t="str"/>
+      <x:c r="J279" s="14" t="str">
+        <x:v>Central Asian logistics JV</x:v>
+      </x:c>
+      <x:c r="K279" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L279" s="14" t="str">
+        <x:v>SRC126_003</x:v>
+      </x:c>
+      <x:c r="M279" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="280">
+      <x:c r="A280" s="14" t="str">
+        <x:v>COMP_KTZ_EXPRESS</x:v>
+      </x:c>
+      <x:c r="B280" s="14" t="str">
+        <x:v>KTZ Express</x:v>
+      </x:c>
+      <x:c r="C280" s="14" t="str">
+        <x:v>Logistics company</x:v>
+      </x:c>
+      <x:c r="D280" s="14" t="str"/>
+      <x:c r="E280" s="14" t="str">
+        <x:v>Kazakhstan</x:v>
+      </x:c>
+      <x:c r="F280" s="14" t="str">
+        <x:v>Subsidiary of Kazakhstan Railways / KTZ</x:v>
+      </x:c>
+      <x:c r="G280" s="14" t="str">
+        <x:v>Freight forwarding; multimodal logistics</x:v>
+      </x:c>
+      <x:c r="H280" s="14" t="str"/>
+      <x:c r="I280" s="14" t="str"/>
+      <x:c r="J280" s="14" t="str">
+        <x:v>Partner in GulfLink</x:v>
+      </x:c>
+      <x:c r="K280" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L280" s="14" t="str">
+        <x:v>SRC126_002</x:v>
+      </x:c>
+      <x:c r="M280" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="281">
+      <x:c r="A281" s="14" t="str">
+        <x:v>COMP_POR_AUTH</x:v>
+      </x:c>
+      <x:c r="B281" s="14" t="str">
+        <x:v>Port of Rotterdam Authority</x:v>
+      </x:c>
+      <x:c r="C281" s="14" t="str">
+        <x:v>Port authority / company</x:v>
+      </x:c>
+      <x:c r="D281" s="14" t="str">
+        <x:v>Rotterdam</x:v>
+      </x:c>
+      <x:c r="E281" s="14" t="str">
+        <x:v>Netherlands</x:v>
+      </x:c>
+      <x:c r="F281" s="14" t="str">
+        <x:v>Public port authority structure</x:v>
+      </x:c>
+      <x:c r="G281" s="14" t="str">
+        <x:v>Port administration; infrastructure; landlord</x:v>
+      </x:c>
+      <x:c r="H281" s="14" t="str"/>
+      <x:c r="I281" s="14" t="str"/>
+      <x:c r="J281" s="14" t="str">
+        <x:v>Administers Port of Rotterdam</x:v>
+      </x:c>
+      <x:c r="K281" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L281" s="14" t="str">
+        <x:v>SRC126_004</x:v>
+      </x:c>
+      <x:c r="M281" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="282">
+      <x:c r="A282" s="14" t="str">
+        <x:v>COMP_RWG</x:v>
+      </x:c>
+      <x:c r="B282" s="14" t="str">
+        <x:v>Rotterdam World Gateway</x:v>
+      </x:c>
+      <x:c r="C282" s="14" t="str">
+        <x:v>Terminal operator / JV</x:v>
+      </x:c>
+      <x:c r="D282" s="14" t="str">
+        <x:v>Rotterdam</x:v>
+      </x:c>
+      <x:c r="E282" s="14" t="str">
+        <x:v>Netherlands</x:v>
+      </x:c>
+      <x:c r="F282" s="14" t="str"/>
+      <x:c r="G282" s="14" t="str">
+        <x:v>Container terminal operations</x:v>
+      </x:c>
+      <x:c r="H282" s="14" t="str"/>
+      <x:c r="I282" s="14" t="str"/>
+      <x:c r="J282" s="14" t="str">
+        <x:v>Maasvlakte container terminal</x:v>
+      </x:c>
+      <x:c r="K282" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L282" s="14" t="str">
+        <x:v>SRC126_004</x:v>
+      </x:c>
+      <x:c r="M282" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="283">
+      <x:c r="A283" s="14" t="str">
+        <x:v>COMP_ECT</x:v>
+      </x:c>
+      <x:c r="B283" s="14" t="str">
+        <x:v>Hutchison Ports ECT Rotterdam</x:v>
+      </x:c>
+      <x:c r="C283" s="14" t="str">
+        <x:v>Terminal operator</x:v>
+      </x:c>
+      <x:c r="D283" s="14" t="str">
+        <x:v>Rotterdam</x:v>
+      </x:c>
+      <x:c r="E283" s="14" t="str">
+        <x:v>Netherlands</x:v>
+      </x:c>
+      <x:c r="F283" s="14" t="str">
+        <x:v>Hutchison Ports group</x:v>
+      </x:c>
+      <x:c r="G283" s="14" t="str">
+        <x:v>Container terminal operations</x:v>
+      </x:c>
+      <x:c r="H283" s="14" t="str"/>
+      <x:c r="I283" s="14" t="str"/>
+      <x:c r="J283" s="14" t="str">
+        <x:v>ECT Delta terminal operator</x:v>
+      </x:c>
+      <x:c r="K283" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L283" s="14" t="str">
+        <x:v>SRC126_004</x:v>
+      </x:c>
+      <x:c r="M283" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="284">
+      <x:c r="A284" s="14" t="str">
+        <x:v>COMP_VFPA</x:v>
+      </x:c>
+      <x:c r="B284" s="14" t="str">
+        <x:v>Vancouver Fraser Port Authority</x:v>
+      </x:c>
+      <x:c r="C284" s="14" t="str">
+        <x:v>Port authority</x:v>
+      </x:c>
+      <x:c r="D284" s="14" t="str">
+        <x:v>Vancouver</x:v>
+      </x:c>
+      <x:c r="E284" s="14" t="str">
+        <x:v>Canada</x:v>
+      </x:c>
+      <x:c r="F284" s="14" t="str">
+        <x:v>Canada Port Authority</x:v>
+      </x:c>
+      <x:c r="G284" s="14" t="str">
+        <x:v>Port administration; infrastructure</x:v>
+      </x:c>
+      <x:c r="H284" s="14" t="str"/>
+      <x:c r="I284" s="14" t="str"/>
+      <x:c r="J284" s="14" t="str">
+        <x:v>Administers Port of Vancouver</x:v>
+      </x:c>
+      <x:c r="K284" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L284" s="14" t="str">
+        <x:v>SRC126_018</x:v>
+      </x:c>
+      <x:c r="M284" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="285">
+      <x:c r="A285" s="14" t="str">
+        <x:v>COMP_GCT</x:v>
+      </x:c>
+      <x:c r="B285" s="14" t="str">
+        <x:v>Global Container Terminals (GCT)</x:v>
+      </x:c>
+      <x:c r="C285" s="14" t="str">
+        <x:v>Terminal operator</x:v>
+      </x:c>
+      <x:c r="D285" s="14" t="str">
+        <x:v>Vancouver</x:v>
+      </x:c>
+      <x:c r="E285" s="14" t="str">
+        <x:v>Canada</x:v>
+      </x:c>
+      <x:c r="F285" s="14" t="str"/>
+      <x:c r="G285" s="14" t="str">
+        <x:v>Container terminal operations</x:v>
+      </x:c>
+      <x:c r="H285" s="14" t="str"/>
+      <x:c r="I285" s="14" t="str"/>
+      <x:c r="J285" s="14" t="str">
+        <x:v>Operator associated with Deltaport</x:v>
+      </x:c>
+      <x:c r="K285" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L285" s="14" t="str">
+        <x:v>SRC126_018</x:v>
+      </x:c>
+      <x:c r="M285" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="286">
+      <x:c r="A286" s="14" t="str">
+        <x:v>COMP_PRPA</x:v>
+      </x:c>
+      <x:c r="B286" s="14" t="str">
+        <x:v>Prince Rupert Port Authority</x:v>
+      </x:c>
+      <x:c r="C286" s="14" t="str">
+        <x:v>Port authority</x:v>
+      </x:c>
+      <x:c r="D286" s="14" t="str">
+        <x:v>Prince Rupert</x:v>
+      </x:c>
+      <x:c r="E286" s="14" t="str">
+        <x:v>Canada</x:v>
+      </x:c>
+      <x:c r="F286" s="14" t="str">
+        <x:v>Canada Port Authority</x:v>
+      </x:c>
+      <x:c r="G286" s="14" t="str">
+        <x:v>Port administration; infrastructure</x:v>
+      </x:c>
+      <x:c r="H286" s="14" t="str"/>
+      <x:c r="I286" s="14" t="str"/>
+      <x:c r="J286" s="14" t="str">
+        <x:v>Administers Port of Prince Rupert</x:v>
+      </x:c>
+      <x:c r="K286" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L286" s="14" t="str">
+        <x:v>SRC126_005</x:v>
+      </x:c>
+      <x:c r="M286" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="287">
+      <x:c r="A287" s="14" t="str">
+        <x:v>COMP_MPA_SG</x:v>
+      </x:c>
+      <x:c r="B287" s="14" t="str">
+        <x:v>Maritime and Port Authority of Singapore</x:v>
+      </x:c>
+      <x:c r="C287" s="14" t="str">
+        <x:v>Maritime authority / regulator</x:v>
+      </x:c>
+      <x:c r="D287" s="14" t="str">
+        <x:v>Singapore</x:v>
+      </x:c>
+      <x:c r="E287" s="14" t="str">
+        <x:v>Singapore</x:v>
+      </x:c>
+      <x:c r="F287" s="14" t="str">
+        <x:v>Government authority</x:v>
+      </x:c>
+      <x:c r="G287" s="14" t="str">
+        <x:v>Port regulation; planning; maritime services</x:v>
+      </x:c>
+      <x:c r="H287" s="14" t="str"/>
+      <x:c r="I287" s="14" t="str"/>
+      <x:c r="J287" s="14" t="str">
+        <x:v>Regulator and planner of Port of Singapore</x:v>
+      </x:c>
+      <x:c r="K287" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L287" s="14" t="str">
+        <x:v>SRC126_006</x:v>
+      </x:c>
+      <x:c r="M287" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="288">
+      <x:c r="A288" s="14" t="str">
+        <x:v>COMP_JURONG_PORT</x:v>
+      </x:c>
+      <x:c r="B288" s="14" t="str">
+        <x:v>Jurong Port</x:v>
+      </x:c>
+      <x:c r="C288" s="14" t="str">
+        <x:v>Port / terminal operator</x:v>
+      </x:c>
+      <x:c r="D288" s="14" t="str">
+        <x:v>Singapore</x:v>
+      </x:c>
+      <x:c r="E288" s="14" t="str">
+        <x:v>Singapore</x:v>
+      </x:c>
+      <x:c r="F288" s="14" t="str"/>
+      <x:c r="G288" s="14" t="str">
+        <x:v>Bulk and conventional cargo terminal operations</x:v>
+      </x:c>
+      <x:c r="H288" s="14" t="str"/>
+      <x:c r="I288" s="14" t="str"/>
+      <x:c r="J288" s="14" t="str">
+        <x:v>Singapore commercial terminal operator</x:v>
+      </x:c>
+      <x:c r="K288" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L288" s="14" t="str">
+        <x:v>SRC126_006</x:v>
+      </x:c>
+      <x:c r="M288" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="289">
+      <x:c r="A289" s="14" t="str">
+        <x:v>COMP_SIPG</x:v>
+      </x:c>
+      <x:c r="B289" s="14" t="str">
+        <x:v>Shanghai International Port Group (SIPG)</x:v>
+      </x:c>
+      <x:c r="C289" s="14" t="str">
+        <x:v>Listed port group</x:v>
+      </x:c>
+      <x:c r="D289" s="14" t="str">
+        <x:v>Shanghai</x:v>
+      </x:c>
+      <x:c r="E289" s="14" t="str">
+        <x:v>China</x:v>
+      </x:c>
+      <x:c r="F289" s="14" t="str">
+        <x:v>Listed on Shanghai Stock Exchange</x:v>
+      </x:c>
+      <x:c r="G289" s="14" t="str">
+        <x:v>Port handling; logistics; port investment</x:v>
+      </x:c>
+      <x:c r="H289" s="14" t="str"/>
+      <x:c r="I289" s="14" t="str"/>
+      <x:c r="J289" s="14" t="str">
+        <x:v>Operator of public terminals in Port of Shanghai</x:v>
+      </x:c>
+      <x:c r="K289" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L289" s="14" t="str">
+        <x:v>SRC126_007</x:v>
+      </x:c>
+      <x:c r="M289" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="290">
+      <x:c r="A290" s="14" t="str">
+        <x:v>COMP_GOTH_AUTH</x:v>
+      </x:c>
+      <x:c r="B290" s="14" t="str">
+        <x:v>Gothenburg Port Authority</x:v>
+      </x:c>
+      <x:c r="C290" s="14" t="str">
+        <x:v>Port authority</x:v>
+      </x:c>
+      <x:c r="D290" s="14" t="str">
+        <x:v>Gothenburg</x:v>
+      </x:c>
+      <x:c r="E290" s="14" t="str">
+        <x:v>Sweden</x:v>
+      </x:c>
+      <x:c r="F290" s="14" t="str"/>
+      <x:c r="G290" s="14" t="str">
+        <x:v>Port administration; rail/terminal infrastructure</x:v>
+      </x:c>
+      <x:c r="H290" s="14" t="str"/>
+      <x:c r="I290" s="14" t="str"/>
+      <x:c r="J290" s="14" t="str">
+        <x:v>Port of Gothenburg authority</x:v>
+      </x:c>
+      <x:c r="K290" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L290" s="14" t="str">
+        <x:v>SRC126_011</x:v>
+      </x:c>
+      <x:c r="M290" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="291">
+      <x:c r="A291" s="14" t="str">
+        <x:v>COMP_PORT_TALLINN</x:v>
+      </x:c>
+      <x:c r="B291" s="14" t="str">
+        <x:v>Port of Tallinn</x:v>
+      </x:c>
+      <x:c r="C291" s="14" t="str">
+        <x:v>Port group / listed company</x:v>
+      </x:c>
+      <x:c r="D291" s="14" t="str">
+        <x:v>Tallinn</x:v>
+      </x:c>
+      <x:c r="E291" s="14" t="str">
+        <x:v>Estonia</x:v>
+      </x:c>
+      <x:c r="F291" s="14" t="str"/>
+      <x:c r="G291" s="14" t="str">
+        <x:v>Multi-harbour port operations; real estate</x:v>
+      </x:c>
+      <x:c r="H291" s="14" t="str"/>
+      <x:c r="I291" s="14" t="str"/>
+      <x:c r="J291" s="14" t="str">
+        <x:v>Operates Muuga and other harbours</x:v>
+      </x:c>
+      <x:c r="K291" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L291" s="14" t="str">
+        <x:v>SRC126_008</x:v>
+      </x:c>
+      <x:c r="M291" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="292">
+      <x:c r="A292" s="14" t="str">
+        <x:v>COMP_HHLA_TK</x:v>
+      </x:c>
+      <x:c r="B292" s="14" t="str">
+        <x:v>HHLA TK Estonia</x:v>
+      </x:c>
+      <x:c r="C292" s="14" t="str">
+        <x:v>Terminal operator</x:v>
+      </x:c>
+      <x:c r="D292" s="14" t="str">
+        <x:v>Muuga</x:v>
+      </x:c>
+      <x:c r="E292" s="14" t="str">
+        <x:v>Estonia</x:v>
+      </x:c>
+      <x:c r="F292" s="14" t="str">
+        <x:v>HHLA-linked operator</x:v>
+      </x:c>
+      <x:c r="G292" s="14" t="str">
+        <x:v>Containers; RoRo; bulk; general cargo</x:v>
+      </x:c>
+      <x:c r="H292" s="14" t="str"/>
+      <x:c r="I292" s="14" t="str"/>
+      <x:c r="J292" s="14" t="str">
+        <x:v>Terminal operator at Muuga Harbour</x:v>
+      </x:c>
+      <x:c r="K292" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L292" s="14" t="str">
+        <x:v>SRC126_008</x:v>
+      </x:c>
+      <x:c r="M292" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="293">
+      <x:c r="A293" s="14" t="str">
+        <x:v>COMP_KLAIPEDA_AUTH</x:v>
+      </x:c>
+      <x:c r="B293" s="14" t="str">
+        <x:v>Klaipėda State Seaport Authority</x:v>
+      </x:c>
+      <x:c r="C293" s="14" t="str">
+        <x:v>Port authority</x:v>
+      </x:c>
+      <x:c r="D293" s="14" t="str">
+        <x:v>Klaipėda</x:v>
+      </x:c>
+      <x:c r="E293" s="14" t="str">
+        <x:v>Lithuania</x:v>
+      </x:c>
+      <x:c r="F293" s="14" t="str">
+        <x:v>State-owned port authority</x:v>
+      </x:c>
+      <x:c r="G293" s="14" t="str">
+        <x:v>Landlord; infrastructure; navigation</x:v>
+      </x:c>
+      <x:c r="H293" s="14" t="str"/>
+      <x:c r="I293" s="14" t="str"/>
+      <x:c r="J293" s="14" t="str">
+        <x:v>Landlord authority at Port of Klaipėda</x:v>
+      </x:c>
+      <x:c r="K293" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L293" s="14" t="str">
+        <x:v>SRC126_009</x:v>
+      </x:c>
+      <x:c r="M293" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="294">
+      <x:c r="A294" s="14" t="str">
+        <x:v>COMP_GDANSK_AUTH</x:v>
+      </x:c>
+      <x:c r="B294" s="14" t="str">
+        <x:v>Port of Gdańsk Authority</x:v>
+      </x:c>
+      <x:c r="C294" s="14" t="str">
+        <x:v>Port authority</x:v>
+      </x:c>
+      <x:c r="D294" s="14" t="str">
+        <x:v>Gdańsk</x:v>
+      </x:c>
+      <x:c r="E294" s="14" t="str">
+        <x:v>Poland</x:v>
+      </x:c>
+      <x:c r="F294" s="14" t="str"/>
+      <x:c r="G294" s="14" t="str">
+        <x:v>Port administration / infrastructure</x:v>
+      </x:c>
+      <x:c r="H294" s="14" t="str"/>
+      <x:c r="I294" s="14" t="str"/>
+      <x:c r="J294" s="14" t="str">
+        <x:v>Port authority for Port of Gdańsk</x:v>
+      </x:c>
+      <x:c r="K294" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L294" s="14" t="str">
+        <x:v>SRC126_010</x:v>
+      </x:c>
+      <x:c r="M294" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="295">
+      <x:c r="A295" s="14" t="str">
+        <x:v>COMP_SOUTH_LA</x:v>
+      </x:c>
+      <x:c r="B295" s="14" t="str">
+        <x:v>Port of South Louisiana</x:v>
+      </x:c>
+      <x:c r="C295" s="14" t="str">
+        <x:v>Port authority / district</x:v>
+      </x:c>
+      <x:c r="D295" s="14" t="str"/>
+      <x:c r="E295" s="14" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="F295" s="14" t="str">
+        <x:v>Public port district</x:v>
+      </x:c>
+      <x:c r="G295" s="14" t="str">
+        <x:v>Port development; industrial / intermodal gateway</x:v>
+      </x:c>
+      <x:c r="H295" s="14" t="str"/>
+      <x:c r="I295" s="14" t="str"/>
+      <x:c r="J295" s="14" t="str">
+        <x:v>54-mile Mississippi River port district</x:v>
+      </x:c>
+      <x:c r="K295" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L295" s="14" t="str">
+        <x:v>SRC126_013</x:v>
+      </x:c>
+      <x:c r="M295" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="296">
+      <x:c r="A296" s="14" t="str">
+        <x:v>COMP_WLSPA</x:v>
+      </x:c>
+      <x:c r="B296" s="14" t="str">
+        <x:v>Western Ligurian Sea Port Authority</x:v>
+      </x:c>
+      <x:c r="C296" s="14" t="str">
+        <x:v>Port authority</x:v>
+      </x:c>
+      <x:c r="D296" s="14" t="str">
+        <x:v>Genoa</x:v>
+      </x:c>
+      <x:c r="E296" s="14" t="str">
+        <x:v>Italy</x:v>
+      </x:c>
+      <x:c r="F296" s="14" t="str">
+        <x:v>Public port-system authority</x:v>
+      </x:c>
+      <x:c r="G296" s="14" t="str">
+        <x:v>Port administration; marine access; infrastructure</x:v>
+      </x:c>
+      <x:c r="H296" s="14" t="str"/>
+      <x:c r="I296" s="14" t="str"/>
+      <x:c r="J296" s="14" t="str">
+        <x:v>Administers Genoa, Pra', Savona and Vado Ligure port system</x:v>
+      </x:c>
+      <x:c r="K296" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L296" s="14" t="str">
+        <x:v>SRC1261_002</x:v>
+      </x:c>
+      <x:c r="M296" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="297">
+      <x:c r="A297" s="14" t="str">
+        <x:v>COMP_PERGENOVA</x:v>
+      </x:c>
+      <x:c r="B297" s="14" t="str">
+        <x:v>PerGenova Breakwater Consortium</x:v>
+      </x:c>
+      <x:c r="C297" s="14" t="str">
+        <x:v>Construction consortium</x:v>
+      </x:c>
+      <x:c r="D297" s="14" t="str">
+        <x:v>Genoa</x:v>
+      </x:c>
+      <x:c r="E297" s="14" t="str">
+        <x:v>Italy</x:v>
+      </x:c>
+      <x:c r="F297" s="14" t="str">
+        <x:v>Project consortium</x:v>
+      </x:c>
+      <x:c r="G297" s="14" t="str">
+        <x:v>Marine construction; breakwater</x:v>
+      </x:c>
+      <x:c r="H297" s="14" t="str"/>
+      <x:c r="I297" s="14" t="str"/>
+      <x:c r="J297" s="14" t="str">
+        <x:v>Consortium delivering Genoa New Breakwater</x:v>
+      </x:c>
+      <x:c r="K297" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L297" s="14" t="str">
+        <x:v>SRC1261_001</x:v>
+      </x:c>
+      <x:c r="M297" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="298">
+      <x:c r="A298" s="14" t="str">
+        <x:v>COMP_WEBUILD</x:v>
+      </x:c>
+      <x:c r="B298" s="14" t="str">
+        <x:v>Webuild</x:v>
+      </x:c>
+      <x:c r="C298" s="14" t="str">
+        <x:v>Engineering / construction company</x:v>
+      </x:c>
+      <x:c r="D298" s="14" t="str">
+        <x:v>Milan</x:v>
+      </x:c>
+      <x:c r="E298" s="14" t="str">
+        <x:v>Italy</x:v>
+      </x:c>
+      <x:c r="F298" s="14" t="str">
+        <x:v>Listed engineering group</x:v>
+      </x:c>
+      <x:c r="G298" s="14" t="str">
+        <x:v>Major infrastructure; rail; marine works</x:v>
+      </x:c>
+      <x:c r="H298" s="14" t="str"/>
+      <x:c r="I298" s="14" t="str"/>
+      <x:c r="J298" s="14" t="str">
+        <x:v>Lead member of PerGenova Breakwater consortium</x:v>
+      </x:c>
+      <x:c r="K298" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L298" s="14" t="str">
+        <x:v>SRC1261_001</x:v>
+      </x:c>
+      <x:c r="M298" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="299">
+      <x:c r="A299" s="14" t="str">
+        <x:v>COMP_FINCANTIERI_INFRA</x:v>
+      </x:c>
+      <x:c r="B299" s="14" t="str">
+        <x:v>Fincantieri Infrastructure Opere Marittime</x:v>
+      </x:c>
+      <x:c r="C299" s="14" t="str">
+        <x:v>Marine infrastructure company</x:v>
+      </x:c>
+      <x:c r="D299" s="14" t="str"/>
+      <x:c r="E299" s="14" t="str">
+        <x:v>Italy</x:v>
+      </x:c>
+      <x:c r="F299" s="14" t="str">
+        <x:v>Fincantieri group company</x:v>
+      </x:c>
+      <x:c r="G299" s="14" t="str">
+        <x:v>Marine infrastructure / construction</x:v>
+      </x:c>
+      <x:c r="H299" s="14" t="str"/>
+      <x:c r="I299" s="14" t="str"/>
+      <x:c r="J299" s="14" t="str">
+        <x:v>PerGenova consortium participant</x:v>
+      </x:c>
+      <x:c r="K299" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L299" s="14" t="str">
+        <x:v>SRC1261_003</x:v>
+      </x:c>
+      <x:c r="M299" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="300">
+      <x:c r="A300" s="14" t="str">
+        <x:v>COMP_FINCOSIT</x:v>
+      </x:c>
+      <x:c r="B300" s="14" t="str">
+        <x:v>Fincosit</x:v>
+      </x:c>
+      <x:c r="C300" s="14" t="str">
+        <x:v>Marine construction company</x:v>
+      </x:c>
+      <x:c r="D300" s="14" t="str"/>
+      <x:c r="E300" s="14" t="str">
+        <x:v>Italy</x:v>
+      </x:c>
+      <x:c r="F300" s="14" t="str"/>
+      <x:c r="G300" s="14" t="str">
+        <x:v>Marine civil works</x:v>
+      </x:c>
+      <x:c r="H300" s="14" t="str"/>
+      <x:c r="I300" s="14" t="str"/>
+      <x:c r="J300" s="14" t="str">
+        <x:v>PerGenova consortium participant</x:v>
+      </x:c>
+      <x:c r="K300" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L300" s="14" t="str">
+        <x:v>SRC1261_003</x:v>
+      </x:c>
+      <x:c r="M300" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="301">
+      <x:c r="A301" s="14" t="str">
+        <x:v>COMP_SIDRA</x:v>
+      </x:c>
+      <x:c r="B301" s="14" t="str">
+        <x:v>SIDRA – Società Italiana Dragaggi</x:v>
+      </x:c>
+      <x:c r="C301" s="14" t="str">
+        <x:v>Marine construction / dredging company</x:v>
+      </x:c>
+      <x:c r="D301" s="14" t="str"/>
+      <x:c r="E301" s="14" t="str">
+        <x:v>Italy</x:v>
+      </x:c>
+      <x:c r="F301" s="14" t="str"/>
+      <x:c r="G301" s="14" t="str">
+        <x:v>Dredging / marine works</x:v>
+      </x:c>
+      <x:c r="H301" s="14" t="str"/>
+      <x:c r="I301" s="14" t="str"/>
+      <x:c r="J301" s="14" t="str">
+        <x:v>PerGenova consortium participant</x:v>
+      </x:c>
+      <x:c r="K301" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L301" s="14" t="str">
+        <x:v>SRC1261_003</x:v>
+      </x:c>
+      <x:c r="M301" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -47083,6 +48079,588 @@
         <x:v>COMP_INOCEA</x:v>
       </x:c>
       <x:c r="F1835" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1836">
+      <x:c r="A1836" s="14" t="str">
+        <x:v>COMP_EMAP</x:v>
+      </x:c>
+      <x:c r="B1836" s="14" t="str">
+        <x:v>Authority</x:v>
+      </x:c>
+      <x:c r="C1836" s="14" t="str">
+        <x:v>EMAP / Maranhão Port Administration</x:v>
+      </x:c>
+      <x:c r="D1836" s="14" t="str">
+        <x:v>Brazil</x:v>
+      </x:c>
+      <x:c r="E1836" s="14" t="str"/>
+      <x:c r="F1836" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1837">
+      <x:c r="A1837" s="14" t="str">
+        <x:v>COMP_TEGRAM</x:v>
+      </x:c>
+      <x:c r="B1837" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1837" s="14" t="str">
+        <x:v>TEGRAM</x:v>
+      </x:c>
+      <x:c r="D1837" s="14" t="str">
+        <x:v>Brazil</x:v>
+      </x:c>
+      <x:c r="E1837" s="14" t="str"/>
+      <x:c r="F1837" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1838">
+      <x:c r="A1838" s="14" t="str">
+        <x:v>COMP_VITERRA_BR</x:v>
+      </x:c>
+      <x:c r="B1838" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1838" s="14" t="str">
+        <x:v>Viterra Logística e Terminais Portuários</x:v>
+      </x:c>
+      <x:c r="D1838" s="14" t="str">
+        <x:v>Brazil</x:v>
+      </x:c>
+      <x:c r="E1838" s="14" t="str"/>
+      <x:c r="F1838" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1839">
+      <x:c r="A1839" s="14" t="str">
+        <x:v>COMP_TCN</x:v>
+      </x:c>
+      <x:c r="B1839" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1839" s="14" t="str">
+        <x:v>Terminal Corredor Norte (TCN)</x:v>
+      </x:c>
+      <x:c r="D1839" s="14" t="str">
+        <x:v>Brazil</x:v>
+      </x:c>
+      <x:c r="E1839" s="14" t="str"/>
+      <x:c r="F1839" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1840">
+      <x:c r="A1840" s="14" t="str">
+        <x:v>COMP_ALZ</x:v>
+      </x:c>
+      <x:c r="B1840" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1840" s="14" t="str">
+        <x:v>ALZ Grãos</x:v>
+      </x:c>
+      <x:c r="D1840" s="14" t="str">
+        <x:v>Brazil</x:v>
+      </x:c>
+      <x:c r="E1840" s="14" t="str"/>
+      <x:c r="F1840" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1841">
+      <x:c r="A1841" s="14" t="str">
+        <x:v>COMP_GULFLINK</x:v>
+      </x:c>
+      <x:c r="B1841" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1841" s="14" t="str">
+        <x:v>GulfLink</x:v>
+      </x:c>
+      <x:c r="D1841" s="14" t="str">
+        <x:v>Kazakhstan</x:v>
+      </x:c>
+      <x:c r="E1841" s="14" t="str"/>
+      <x:c r="F1841" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1842">
+      <x:c r="A1842" s="14" t="str">
+        <x:v>COMP_KTZ_EXPRESS</x:v>
+      </x:c>
+      <x:c r="B1842" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1842" s="14" t="str">
+        <x:v>KTZ Express</x:v>
+      </x:c>
+      <x:c r="D1842" s="14" t="str">
+        <x:v>Kazakhstan</x:v>
+      </x:c>
+      <x:c r="E1842" s="14" t="str"/>
+      <x:c r="F1842" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1843">
+      <x:c r="A1843" s="14" t="str">
+        <x:v>COMP_POR_AUTH</x:v>
+      </x:c>
+      <x:c r="B1843" s="14" t="str">
+        <x:v>Authority</x:v>
+      </x:c>
+      <x:c r="C1843" s="14" t="str">
+        <x:v>Port of Rotterdam Authority</x:v>
+      </x:c>
+      <x:c r="D1843" s="14" t="str">
+        <x:v>Netherlands</x:v>
+      </x:c>
+      <x:c r="E1843" s="14" t="str"/>
+      <x:c r="F1843" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1844">
+      <x:c r="A1844" s="14" t="str">
+        <x:v>COMP_RWG</x:v>
+      </x:c>
+      <x:c r="B1844" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1844" s="14" t="str">
+        <x:v>Rotterdam World Gateway</x:v>
+      </x:c>
+      <x:c r="D1844" s="14" t="str">
+        <x:v>Netherlands</x:v>
+      </x:c>
+      <x:c r="E1844" s="14" t="str"/>
+      <x:c r="F1844" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1845">
+      <x:c r="A1845" s="14" t="str">
+        <x:v>COMP_ECT</x:v>
+      </x:c>
+      <x:c r="B1845" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1845" s="14" t="str">
+        <x:v>Hutchison Ports ECT Rotterdam</x:v>
+      </x:c>
+      <x:c r="D1845" s="14" t="str">
+        <x:v>Netherlands</x:v>
+      </x:c>
+      <x:c r="E1845" s="14" t="str"/>
+      <x:c r="F1845" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1846">
+      <x:c r="A1846" s="14" t="str">
+        <x:v>COMP_VFPA</x:v>
+      </x:c>
+      <x:c r="B1846" s="14" t="str">
+        <x:v>Authority</x:v>
+      </x:c>
+      <x:c r="C1846" s="14" t="str">
+        <x:v>Vancouver Fraser Port Authority</x:v>
+      </x:c>
+      <x:c r="D1846" s="14" t="str">
+        <x:v>Canada</x:v>
+      </x:c>
+      <x:c r="E1846" s="14" t="str"/>
+      <x:c r="F1846" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1847">
+      <x:c r="A1847" s="14" t="str">
+        <x:v>COMP_GCT</x:v>
+      </x:c>
+      <x:c r="B1847" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1847" s="14" t="str">
+        <x:v>Global Container Terminals (GCT)</x:v>
+      </x:c>
+      <x:c r="D1847" s="14" t="str">
+        <x:v>Canada</x:v>
+      </x:c>
+      <x:c r="E1847" s="14" t="str"/>
+      <x:c r="F1847" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1848">
+      <x:c r="A1848" s="14" t="str">
+        <x:v>COMP_PRPA</x:v>
+      </x:c>
+      <x:c r="B1848" s="14" t="str">
+        <x:v>Authority</x:v>
+      </x:c>
+      <x:c r="C1848" s="14" t="str">
+        <x:v>Prince Rupert Port Authority</x:v>
+      </x:c>
+      <x:c r="D1848" s="14" t="str">
+        <x:v>Canada</x:v>
+      </x:c>
+      <x:c r="E1848" s="14" t="str"/>
+      <x:c r="F1848" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1849">
+      <x:c r="A1849" s="14" t="str">
+        <x:v>COMP_MPA_SG</x:v>
+      </x:c>
+      <x:c r="B1849" s="14" t="str">
+        <x:v>Authority</x:v>
+      </x:c>
+      <x:c r="C1849" s="14" t="str">
+        <x:v>Maritime and Port Authority of Singapore</x:v>
+      </x:c>
+      <x:c r="D1849" s="14" t="str">
+        <x:v>Singapore</x:v>
+      </x:c>
+      <x:c r="E1849" s="14" t="str"/>
+      <x:c r="F1849" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1850">
+      <x:c r="A1850" s="14" t="str">
+        <x:v>COMP_JURONG_PORT</x:v>
+      </x:c>
+      <x:c r="B1850" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1850" s="14" t="str">
+        <x:v>Jurong Port</x:v>
+      </x:c>
+      <x:c r="D1850" s="14" t="str">
+        <x:v>Singapore</x:v>
+      </x:c>
+      <x:c r="E1850" s="14" t="str"/>
+      <x:c r="F1850" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1851">
+      <x:c r="A1851" s="14" t="str">
+        <x:v>COMP_SIPG</x:v>
+      </x:c>
+      <x:c r="B1851" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1851" s="14" t="str">
+        <x:v>Shanghai International Port Group (SIPG)</x:v>
+      </x:c>
+      <x:c r="D1851" s="14" t="str">
+        <x:v>China</x:v>
+      </x:c>
+      <x:c r="E1851" s="14" t="str"/>
+      <x:c r="F1851" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1852">
+      <x:c r="A1852" s="14" t="str">
+        <x:v>COMP_GOTH_AUTH</x:v>
+      </x:c>
+      <x:c r="B1852" s="14" t="str">
+        <x:v>Authority</x:v>
+      </x:c>
+      <x:c r="C1852" s="14" t="str">
+        <x:v>Gothenburg Port Authority</x:v>
+      </x:c>
+      <x:c r="D1852" s="14" t="str">
+        <x:v>Sweden</x:v>
+      </x:c>
+      <x:c r="E1852" s="14" t="str"/>
+      <x:c r="F1852" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1853">
+      <x:c r="A1853" s="14" t="str">
+        <x:v>COMP_PORT_TALLINN</x:v>
+      </x:c>
+      <x:c r="B1853" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1853" s="14" t="str">
+        <x:v>Port of Tallinn</x:v>
+      </x:c>
+      <x:c r="D1853" s="14" t="str">
+        <x:v>Estonia</x:v>
+      </x:c>
+      <x:c r="E1853" s="14" t="str"/>
+      <x:c r="F1853" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1854">
+      <x:c r="A1854" s="14" t="str">
+        <x:v>COMP_HHLA_TK</x:v>
+      </x:c>
+      <x:c r="B1854" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1854" s="14" t="str">
+        <x:v>HHLA TK Estonia</x:v>
+      </x:c>
+      <x:c r="D1854" s="14" t="str">
+        <x:v>Estonia</x:v>
+      </x:c>
+      <x:c r="E1854" s="14" t="str"/>
+      <x:c r="F1854" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1855">
+      <x:c r="A1855" s="14" t="str">
+        <x:v>COMP_KLAIPEDA_AUTH</x:v>
+      </x:c>
+      <x:c r="B1855" s="14" t="str">
+        <x:v>Authority</x:v>
+      </x:c>
+      <x:c r="C1855" s="14" t="str">
+        <x:v>Klaipėda State Seaport Authority</x:v>
+      </x:c>
+      <x:c r="D1855" s="14" t="str">
+        <x:v>Lithuania</x:v>
+      </x:c>
+      <x:c r="E1855" s="14" t="str"/>
+      <x:c r="F1855" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1856">
+      <x:c r="A1856" s="14" t="str">
+        <x:v>COMP_GDANSK_AUTH</x:v>
+      </x:c>
+      <x:c r="B1856" s="14" t="str">
+        <x:v>Authority</x:v>
+      </x:c>
+      <x:c r="C1856" s="14" t="str">
+        <x:v>Port of Gdańsk Authority</x:v>
+      </x:c>
+      <x:c r="D1856" s="14" t="str">
+        <x:v>Poland</x:v>
+      </x:c>
+      <x:c r="E1856" s="14" t="str"/>
+      <x:c r="F1856" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1857">
+      <x:c r="A1857" s="14" t="str">
+        <x:v>COMP_SOUTH_LA</x:v>
+      </x:c>
+      <x:c r="B1857" s="14" t="str">
+        <x:v>Authority</x:v>
+      </x:c>
+      <x:c r="C1857" s="14" t="str">
+        <x:v>Port of South Louisiana</x:v>
+      </x:c>
+      <x:c r="D1857" s="14" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="E1857" s="14" t="str"/>
+      <x:c r="F1857" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1858">
+      <x:c r="A1858" s="14" t="str">
+        <x:v>COMP_WLSPA</x:v>
+      </x:c>
+      <x:c r="B1858" s="14" t="str">
+        <x:v>Authority</x:v>
+      </x:c>
+      <x:c r="C1858" s="14" t="str">
+        <x:v>Western Ligurian Sea Port Authority</x:v>
+      </x:c>
+      <x:c r="D1858" s="14" t="str">
+        <x:v>Italy</x:v>
+      </x:c>
+      <x:c r="E1858" s="14" t="str"/>
+      <x:c r="F1858" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1859">
+      <x:c r="A1859" s="14" t="str">
+        <x:v>COMP_PERGENOVA</x:v>
+      </x:c>
+      <x:c r="B1859" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1859" s="14" t="str">
+        <x:v>PerGenova Breakwater Consortium</x:v>
+      </x:c>
+      <x:c r="D1859" s="14" t="str">
+        <x:v>Italy</x:v>
+      </x:c>
+      <x:c r="E1859" s="14" t="str"/>
+      <x:c r="F1859" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1860">
+      <x:c r="A1860" s="14" t="str">
+        <x:v>COMP_WEBUILD</x:v>
+      </x:c>
+      <x:c r="B1860" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1860" s="14" t="str">
+        <x:v>Webuild</x:v>
+      </x:c>
+      <x:c r="D1860" s="14" t="str">
+        <x:v>Italy</x:v>
+      </x:c>
+      <x:c r="E1860" s="14" t="str"/>
+      <x:c r="F1860" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1861">
+      <x:c r="A1861" s="14" t="str">
+        <x:v>COMP_FINCANTIERI_INFRA</x:v>
+      </x:c>
+      <x:c r="B1861" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1861" s="14" t="str">
+        <x:v>Fincantieri Infrastructure Opere Marittime</x:v>
+      </x:c>
+      <x:c r="D1861" s="14" t="str">
+        <x:v>Italy</x:v>
+      </x:c>
+      <x:c r="E1861" s="14" t="str">
+        <x:v>COMP_FINCANTIERI</x:v>
+      </x:c>
+      <x:c r="F1861" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1862">
+      <x:c r="A1862" s="14" t="str">
+        <x:v>COMP_FINCOSIT</x:v>
+      </x:c>
+      <x:c r="B1862" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1862" s="14" t="str">
+        <x:v>Fincosit</x:v>
+      </x:c>
+      <x:c r="D1862" s="14" t="str">
+        <x:v>Italy</x:v>
+      </x:c>
+      <x:c r="E1862" s="14" t="str"/>
+      <x:c r="F1862" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1863">
+      <x:c r="A1863" s="14" t="str">
+        <x:v>COMP_SIDRA</x:v>
+      </x:c>
+      <x:c r="B1863" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1863" s="14" t="str">
+        <x:v>SIDRA – Società Italiana Dragaggi</x:v>
+      </x:c>
+      <x:c r="D1863" s="14" t="str">
+        <x:v>Italy</x:v>
+      </x:c>
+      <x:c r="E1863" s="14" t="str"/>
+      <x:c r="F1863" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1864">
+      <x:c r="A1864" s="14" t="str">
+        <x:v>PORT_GENOA</x:v>
+      </x:c>
+      <x:c r="B1864" s="14" t="str">
+        <x:v>Port</x:v>
+      </x:c>
+      <x:c r="C1864" s="14" t="str">
+        <x:v>Port of Genoa</x:v>
+      </x:c>
+      <x:c r="D1864" s="14" t="str">
+        <x:v>Italy</x:v>
+      </x:c>
+      <x:c r="E1864" s="14" t="str">
+        <x:v>COMP_WLSPA</x:v>
+      </x:c>
+      <x:c r="F1864" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1865">
+      <x:c r="A1865" s="14" t="str">
+        <x:v>ASSET_GENOA_BREAKWATER</x:v>
+      </x:c>
+      <x:c r="B1865" s="14" t="str">
+        <x:v>Asset</x:v>
+      </x:c>
+      <x:c r="C1865" s="14" t="str">
+        <x:v>New Genoa Breakwater</x:v>
+      </x:c>
+      <x:c r="D1865" s="14" t="str">
+        <x:v>Italy</x:v>
+      </x:c>
+      <x:c r="E1865" s="14" t="str">
+        <x:v>PORT_GENOA</x:v>
+      </x:c>
+      <x:c r="F1865" s="14" t="str">
+        <x:v>Under construction</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1866">
+      <x:c r="A1866" s="14" t="str">
+        <x:v>ASSET_TERZO_VALICO</x:v>
+      </x:c>
+      <x:c r="B1866" s="14" t="str">
+        <x:v>Asset</x:v>
+      </x:c>
+      <x:c r="C1866" s="14" t="str">
+        <x:v>Terzo Valico dei Giovi–Genoa Junction</x:v>
+      </x:c>
+      <x:c r="D1866" s="14" t="str">
+        <x:v>Italy</x:v>
+      </x:c>
+      <x:c r="E1866" s="14" t="str"/>
+      <x:c r="F1866" s="14" t="str">
+        <x:v>Under construction</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1867">
+      <x:c r="A1867" s="14" t="str">
+        <x:v>CORR_RHINE_ALPINE</x:v>
+      </x:c>
+      <x:c r="B1867" s="14" t="str">
+        <x:v>Corridor</x:v>
+      </x:c>
+      <x:c r="C1867" s="14" t="str">
+        <x:v>Rhine–Alpine Corridor</x:v>
+      </x:c>
+      <x:c r="D1867" s="14" t="str">
+        <x:v>Europe</x:v>
+      </x:c>
+      <x:c r="E1867" s="14" t="str"/>
+      <x:c r="F1867" s="14" t="str">
         <x:v>Active</x:v>
       </x:c>
     </x:row>
@@ -50615,6 +52193,305 @@
       </x:c>
       <x:c r="G153" s="14" t="str">
         <x:v>SRC_V1251_007</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154">
+      <x:c r="A154" s="14" t="str">
+        <x:v>REL126_001</x:v>
+      </x:c>
+      <x:c r="B154" s="14" t="str">
+        <x:v>COMP_ADPORTS</x:v>
+      </x:c>
+      <x:c r="C154" s="14" t="str">
+        <x:v>JV_PARTNER_51_PERCENT</x:v>
+      </x:c>
+      <x:c r="D154" s="14" t="str">
+        <x:v>COMP_GULFLINK</x:v>
+      </x:c>
+      <x:c r="E154" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F154" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G154" s="14" t="str">
+        <x:v>SRC126_003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155">
+      <x:c r="A155" s="14" t="str">
+        <x:v>REL126_002</x:v>
+      </x:c>
+      <x:c r="B155" s="14" t="str">
+        <x:v>COMP_KTZ_EXPRESS</x:v>
+      </x:c>
+      <x:c r="C155" s="14" t="str">
+        <x:v>JV_PARTNER_49_PERCENT</x:v>
+      </x:c>
+      <x:c r="D155" s="14" t="str">
+        <x:v>COMP_GULFLINK</x:v>
+      </x:c>
+      <x:c r="E155" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F155" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G155" s="14" t="str">
+        <x:v>SRC126_003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156">
+      <x:c r="A156" s="14" t="str">
+        <x:v>REL126_003</x:v>
+      </x:c>
+      <x:c r="B156" s="14" t="str">
+        <x:v>COMP_KTZ</x:v>
+      </x:c>
+      <x:c r="C156" s="14" t="str">
+        <x:v>PARENT_OF</x:v>
+      </x:c>
+      <x:c r="D156" s="14" t="str">
+        <x:v>COMP_KTZ_EXPRESS</x:v>
+      </x:c>
+      <x:c r="E156" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F156" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G156" s="14" t="str">
+        <x:v>SRC126_002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157">
+      <x:c r="A157" s="14" t="str">
+        <x:v>REL126_004</x:v>
+      </x:c>
+      <x:c r="B157" s="14" t="str">
+        <x:v>COMP_HHLA</x:v>
+      </x:c>
+      <x:c r="C157" s="14" t="str">
+        <x:v>PARENT_OF</x:v>
+      </x:c>
+      <x:c r="D157" s="14" t="str">
+        <x:v>COMP_HHLA_TK</x:v>
+      </x:c>
+      <x:c r="E157" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F157" s="14" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="G157" s="14" t="str">
+        <x:v>SRC126_008</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158">
+      <x:c r="A158" s="14" t="str">
+        <x:v>REL1261_001</x:v>
+      </x:c>
+      <x:c r="B158" s="14" t="str">
+        <x:v>COMP_WLSPA</x:v>
+      </x:c>
+      <x:c r="C158" s="14" t="str">
+        <x:v>ADMINISTERS</x:v>
+      </x:c>
+      <x:c r="D158" s="14" t="str">
+        <x:v>PORT_GENOA</x:v>
+      </x:c>
+      <x:c r="E158" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F158" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G158" s="14" t="str">
+        <x:v>SRC1261_002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159">
+      <x:c r="A159" s="14" t="str">
+        <x:v>REL1261_002</x:v>
+      </x:c>
+      <x:c r="B159" s="14" t="str">
+        <x:v>COMP_WLSPA</x:v>
+      </x:c>
+      <x:c r="C159" s="14" t="str">
+        <x:v>COMMISSIONS</x:v>
+      </x:c>
+      <x:c r="D159" s="14" t="str">
+        <x:v>ASSET_GENOA_BREAKWATER</x:v>
+      </x:c>
+      <x:c r="E159" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F159" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G159" s="14" t="str">
+        <x:v>SRC1261_001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160">
+      <x:c r="A160" s="14" t="str">
+        <x:v>REL1261_003</x:v>
+      </x:c>
+      <x:c r="B160" s="14" t="str">
+        <x:v>COMP_PERGENOVA</x:v>
+      </x:c>
+      <x:c r="C160" s="14" t="str">
+        <x:v>CONSTRUCTS</x:v>
+      </x:c>
+      <x:c r="D160" s="14" t="str">
+        <x:v>ASSET_GENOA_BREAKWATER</x:v>
+      </x:c>
+      <x:c r="E160" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F160" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G160" s="14" t="str">
+        <x:v>SRC1261_001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161">
+      <x:c r="A161" s="14" t="str">
+        <x:v>REL1261_004</x:v>
+      </x:c>
+      <x:c r="B161" s="14" t="str">
+        <x:v>COMP_WEBUILD</x:v>
+      </x:c>
+      <x:c r="C161" s="14" t="str">
+        <x:v>LEADS_CONSORTIUM</x:v>
+      </x:c>
+      <x:c r="D161" s="14" t="str">
+        <x:v>COMP_PERGENOVA</x:v>
+      </x:c>
+      <x:c r="E161" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F161" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G161" s="14" t="str">
+        <x:v>SRC1261_001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162">
+      <x:c r="A162" s="14" t="str">
+        <x:v>REL1261_005</x:v>
+      </x:c>
+      <x:c r="B162" s="14" t="str">
+        <x:v>COMP_FINCANTIERI_INFRA</x:v>
+      </x:c>
+      <x:c r="C162" s="14" t="str">
+        <x:v>PARTICIPATES_IN</x:v>
+      </x:c>
+      <x:c r="D162" s="14" t="str">
+        <x:v>COMP_PERGENOVA</x:v>
+      </x:c>
+      <x:c r="E162" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F162" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G162" s="14" t="str">
+        <x:v>SRC1261_003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163">
+      <x:c r="A163" s="14" t="str">
+        <x:v>REL1261_006</x:v>
+      </x:c>
+      <x:c r="B163" s="14" t="str">
+        <x:v>COMP_FINCOSIT</x:v>
+      </x:c>
+      <x:c r="C163" s="14" t="str">
+        <x:v>PARTICIPATES_IN</x:v>
+      </x:c>
+      <x:c r="D163" s="14" t="str">
+        <x:v>COMP_PERGENOVA</x:v>
+      </x:c>
+      <x:c r="E163" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F163" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G163" s="14" t="str">
+        <x:v>SRC1261_003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="164">
+      <x:c r="A164" s="14" t="str">
+        <x:v>REL1261_007</x:v>
+      </x:c>
+      <x:c r="B164" s="14" t="str">
+        <x:v>COMP_SIDRA</x:v>
+      </x:c>
+      <x:c r="C164" s="14" t="str">
+        <x:v>PARTICIPATES_IN</x:v>
+      </x:c>
+      <x:c r="D164" s="14" t="str">
+        <x:v>COMP_PERGENOVA</x:v>
+      </x:c>
+      <x:c r="E164" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F164" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G164" s="14" t="str">
+        <x:v>SRC1261_003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="165">
+      <x:c r="A165" s="14" t="str">
+        <x:v>REL1261_008</x:v>
+      </x:c>
+      <x:c r="B165" s="14" t="str">
+        <x:v>PORT_GENOA</x:v>
+      </x:c>
+      <x:c r="C165" s="14" t="str">
+        <x:v>CONNECTED_BY_RAIL_PROJECT</x:v>
+      </x:c>
+      <x:c r="D165" s="14" t="str">
+        <x:v>ASSET_TERZO_VALICO</x:v>
+      </x:c>
+      <x:c r="E165" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F165" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G165" s="14" t="str">
+        <x:v>SRC1261_003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="166">
+      <x:c r="A166" s="14" t="str">
+        <x:v>REL1261_009</x:v>
+      </x:c>
+      <x:c r="B166" s="14" t="str">
+        <x:v>PORT_GENOA</x:v>
+      </x:c>
+      <x:c r="C166" s="14" t="str">
+        <x:v>PART_OF</x:v>
+      </x:c>
+      <x:c r="D166" s="14" t="str">
+        <x:v>CORR_RHINE_ALPINE</x:v>
+      </x:c>
+      <x:c r="E166" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F166" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G166" s="14" t="str">
+        <x:v>SRC1261_003</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/data/01_core_entities.xlsx
+++ b/data/01_core_entities.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="Rdff8dd28273d48aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Companies" sheetId="2" r:id="R54fcf8d9e2014731"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Entity Registry" sheetId="3" r:id="Rc7ceabae050b4384"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="R817063df89f2477a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company System Footprints" sheetId="5" r:id="R54edc5104b494337"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="People" sheetId="6" r:id="R5c5bcd9183434fb7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leadership Roles" sheetId="7" r:id="R321d51cece6c43c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Dictionary" sheetId="8" r:id="Ree83608f69b847ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runtime Table Crosswalk" sheetId="9" r:id="Refb205667aa84608"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Queue" sheetId="10" r:id="Rd82d192c9bc2411a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="Rbec542a3b3254636"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Companies" sheetId="2" r:id="R6c3c913d5ec44e71"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Entity Registry" sheetId="3" r:id="R0b0fd4adda4b4708"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="Rdd4142a93f074187"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company System Footprints" sheetId="5" r:id="R357e5d16c5614df1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="People" sheetId="6" r:id="R5c294c44e38a4e07"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leadership Roles" sheetId="7" r:id="R4eebb6a795824a7a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Dictionary" sheetId="8" r:id="R34f0c38ae04c4d11"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runtime Table Crosswalk" sheetId="9" r:id="R69da433867b8431a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Queue" sheetId="10" r:id="Rb0d92e6fe0eb4277"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13561,6 +13561,568 @@
         <x:v>2026-09-09</x:v>
       </x:c>
     </x:row>
+    <x:row r="302">
+      <x:c r="A302" s="14" t="str">
+        <x:v>COMP_EDGE</x:v>
+      </x:c>
+      <x:c r="B302" s="14" t="str">
+        <x:v>EDGE Group</x:v>
+      </x:c>
+      <x:c r="C302" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="D302" s="14" t="str">
+        <x:v>Abu Dhabi</x:v>
+      </x:c>
+      <x:c r="E302" s="14" t="str">
+        <x:v>United Arab Emirates</x:v>
+      </x:c>
+      <x:c r="F302" s="14" t="str">
+        <x:v>State-linked UAE defence technology group</x:v>
+      </x:c>
+      <x:c r="G302" s="14" t="str">
+        <x:v>Defence technology; platforms; weapons; autonomous systems</x:v>
+      </x:c>
+      <x:c r="H302" s="14" t="str"/>
+      <x:c r="I302" s="14" t="str"/>
+      <x:c r="J302" s="14" t="str">
+        <x:v>Parent group for ADSB and other defence entities</x:v>
+      </x:c>
+      <x:c r="K302" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L302" s="14" t="str">
+        <x:v>SRC127_001</x:v>
+      </x:c>
+      <x:c r="M302" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="N302" s="14" t="str"/>
+    </x:row>
+    <x:row r="303">
+      <x:c r="A303" s="14" t="str">
+        <x:v>COMP_ADSB</x:v>
+      </x:c>
+      <x:c r="B303" s="14" t="str">
+        <x:v>Abu Dhabi Ship Building (ADSB)</x:v>
+      </x:c>
+      <x:c r="C303" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="D303" s="14" t="str">
+        <x:v>Abu Dhabi</x:v>
+      </x:c>
+      <x:c r="E303" s="14" t="str">
+        <x:v>United Arab Emirates</x:v>
+      </x:c>
+      <x:c r="F303" s="14" t="str">
+        <x:v>Part of EDGE Group</x:v>
+      </x:c>
+      <x:c r="G303" s="14" t="str">
+        <x:v>Naval shipbuilding; coast guard; MRO; commercial/offshore</x:v>
+      </x:c>
+      <x:c r="H303" s="14" t="str"/>
+      <x:c r="I303" s="14" t="str"/>
+      <x:c r="J303" s="14" t="str">
+        <x:v>Strategic Abu Dhabi shipbuilder</x:v>
+      </x:c>
+      <x:c r="K303" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L303" s="14" t="str">
+        <x:v>SRC127_002</x:v>
+      </x:c>
+      <x:c r="M303" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="N303" s="14" t="str"/>
+    </x:row>
+    <x:row r="304">
+      <x:c r="A304" s="14" t="str">
+        <x:v>COMP_MAESTRAL</x:v>
+      </x:c>
+      <x:c r="B304" s="14" t="str">
+        <x:v>MAESTRAL</x:v>
+      </x:c>
+      <x:c r="C304" s="14" t="str">
+        <x:v>JV / Company</x:v>
+      </x:c>
+      <x:c r="D304" s="14" t="str">
+        <x:v>Abu Dhabi</x:v>
+      </x:c>
+      <x:c r="E304" s="14" t="str">
+        <x:v>United Arab Emirates</x:v>
+      </x:c>
+      <x:c r="F304" s="14" t="str">
+        <x:v>EDGE 51%; Fincantieri 49%</x:v>
+      </x:c>
+      <x:c r="G304" s="14" t="str">
+        <x:v>Naval shipbuilding; export programmes</x:v>
+      </x:c>
+      <x:c r="H304" s="14" t="str"/>
+      <x:c r="I304" s="14" t="str"/>
+      <x:c r="J304" s="14" t="str">
+        <x:v>Abu Dhabi-based shipbuilding JV</x:v>
+      </x:c>
+      <x:c r="K304" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L304" s="14" t="str">
+        <x:v>SRC127_001</x:v>
+      </x:c>
+      <x:c r="M304" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="N304" s="14" t="str"/>
+    </x:row>
+    <x:row r="305">
+      <x:c r="A305" s="14" t="str">
+        <x:v>COMP_IRVING</x:v>
+      </x:c>
+      <x:c r="B305" s="14" t="str">
+        <x:v>Irving Shipbuilding Inc.</x:v>
+      </x:c>
+      <x:c r="C305" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="D305" s="14" t="str">
+        <x:v>Halifax</x:v>
+      </x:c>
+      <x:c r="E305" s="14" t="str">
+        <x:v>Canada</x:v>
+      </x:c>
+      <x:c r="F305" s="14" t="str">
+        <x:v>Privately held / Irving group</x:v>
+      </x:c>
+      <x:c r="G305" s="14" t="str">
+        <x:v>Naval shipbuilding; coast guard shipbuilding</x:v>
+      </x:c>
+      <x:c r="H305" s="14" t="str"/>
+      <x:c r="I305" s="14" t="str"/>
+      <x:c r="J305" s="14" t="str">
+        <x:v>Halifax Shipyard strategic builder under Canada's NSS</x:v>
+      </x:c>
+      <x:c r="K305" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L305" s="14" t="str">
+        <x:v>SRC127_003</x:v>
+      </x:c>
+      <x:c r="M305" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="N305" s="14" t="str"/>
+    </x:row>
+    <x:row r="306">
+      <x:c r="A306" s="14" t="str">
+        <x:v>COMP_BOLLINGER</x:v>
+      </x:c>
+      <x:c r="B306" s="14" t="str">
+        <x:v>Bollinger Shipyards</x:v>
+      </x:c>
+      <x:c r="C306" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="D306" s="14" t="str">
+        <x:v>Lockport</x:v>
+      </x:c>
+      <x:c r="E306" s="14" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="F306" s="14" t="str">
+        <x:v>Private</x:v>
+      </x:c>
+      <x:c r="G306" s="14" t="str">
+        <x:v>Defence; coast guard; research; commercial shipbuilding; repair</x:v>
+      </x:c>
+      <x:c r="H306" s="14" t="str"/>
+      <x:c r="I306" s="14" t="str"/>
+      <x:c r="J306" s="14" t="str">
+        <x:v>Multi-yard Gulf Coast shipbuilding network</x:v>
+      </x:c>
+      <x:c r="K306" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L306" s="14" t="str">
+        <x:v>SRC127_011</x:v>
+      </x:c>
+      <x:c r="M306" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="N306" s="14" t="str"/>
+    </x:row>
+    <x:row r="307">
+      <x:c r="A307" s="14" t="str">
+        <x:v>COMP_RMC</x:v>
+      </x:c>
+      <x:c r="B307" s="14" t="str">
+        <x:v>Rauma Marine Constructions Oy</x:v>
+      </x:c>
+      <x:c r="C307" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="D307" s="14" t="str">
+        <x:v>Rauma</x:v>
+      </x:c>
+      <x:c r="E307" s="14" t="str">
+        <x:v>Finland</x:v>
+      </x:c>
+      <x:c r="F307" s="14" t="str">
+        <x:v>Private</x:v>
+      </x:c>
+      <x:c r="G307" s="14" t="str">
+        <x:v>Naval; ferries; government vessels; ice-capable shipbuilding</x:v>
+      </x:c>
+      <x:c r="H307" s="14" t="str"/>
+      <x:c r="I307" s="14" t="str"/>
+      <x:c r="J307" s="14" t="str">
+        <x:v>Strategic Rauma shipbuilder</x:v>
+      </x:c>
+      <x:c r="K307" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L307" s="14" t="str">
+        <x:v>SRC127_013</x:v>
+      </x:c>
+      <x:c r="M307" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="N307" s="14" t="str"/>
+    </x:row>
+    <x:row r="308">
+      <x:c r="A308" s="14" t="str">
+        <x:v>COMP_AKER_ARCTIC</x:v>
+      </x:c>
+      <x:c r="B308" s="14" t="str">
+        <x:v>Aker Arctic Technology Inc.</x:v>
+      </x:c>
+      <x:c r="C308" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="D308" s="14" t="str">
+        <x:v>Helsinki</x:v>
+      </x:c>
+      <x:c r="E308" s="14" t="str">
+        <x:v>Finland</x:v>
+      </x:c>
+      <x:c r="F308" s="14" t="str"/>
+      <x:c r="G308" s="14" t="str">
+        <x:v>Icebreaker design; engineering; Arctic technology</x:v>
+      </x:c>
+      <x:c r="H308" s="14" t="str"/>
+      <x:c r="I308" s="14" t="str"/>
+      <x:c r="J308" s="14" t="str">
+        <x:v>Design partner on MPI / ASC concept</x:v>
+      </x:c>
+      <x:c r="K308" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L308" s="14" t="str">
+        <x:v>SRC127_006</x:v>
+      </x:c>
+      <x:c r="M308" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="N308" s="14" t="str"/>
+    </x:row>
+    <x:row r="309">
+      <x:c r="A309" s="14" t="str">
+        <x:v>COMP_DAMEN</x:v>
+      </x:c>
+      <x:c r="B309" s="14" t="str">
+        <x:v>Damen Shipyards Group</x:v>
+      </x:c>
+      <x:c r="C309" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="D309" s="14" t="str">
+        <x:v>Gorinchem</x:v>
+      </x:c>
+      <x:c r="E309" s="14" t="str">
+        <x:v>Netherlands</x:v>
+      </x:c>
+      <x:c r="F309" s="14" t="str">
+        <x:v>Private</x:v>
+      </x:c>
+      <x:c r="G309" s="14" t="str">
+        <x:v>Defence; coast guard; commercial shipbuilding; repair</x:v>
+      </x:c>
+      <x:c r="H309" s="14" t="str"/>
+      <x:c r="I309" s="14" t="str"/>
+      <x:c r="J309" s="14" t="str">
+        <x:v>Global shipbuilding group with Turkish yard presence</x:v>
+      </x:c>
+      <x:c r="K309" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L309" s="14" t="str">
+        <x:v>SRC127_014</x:v>
+      </x:c>
+      <x:c r="M309" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="N309" s="14" t="str"/>
+    </x:row>
+    <x:row r="310">
+      <x:c r="A310" s="14" t="str">
+        <x:v>COMP_RMK</x:v>
+      </x:c>
+      <x:c r="B310" s="14" t="str">
+        <x:v>RMK Marine</x:v>
+      </x:c>
+      <x:c r="C310" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="D310" s="14" t="str">
+        <x:v>Istanbul</x:v>
+      </x:c>
+      <x:c r="E310" s="14" t="str">
+        <x:v>Turkey</x:v>
+      </x:c>
+      <x:c r="F310" s="14" t="str">
+        <x:v>Koç Group company</x:v>
+      </x:c>
+      <x:c r="G310" s="14" t="str">
+        <x:v>Naval platforms; commercial vessels; superyachts; repair</x:v>
+      </x:c>
+      <x:c r="H310" s="14" t="str"/>
+      <x:c r="I310" s="14" t="str"/>
+      <x:c r="J310" s="14" t="str">
+        <x:v>Dual-use Tuzla shipyard</x:v>
+      </x:c>
+      <x:c r="K310" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L310" s="14" t="str">
+        <x:v>SRC127_016</x:v>
+      </x:c>
+      <x:c r="M310" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="N310" s="14" t="str"/>
+    </x:row>
+    <x:row r="311">
+      <x:c r="A311" s="14" t="str">
+        <x:v>COMP_SEFINE</x:v>
+      </x:c>
+      <x:c r="B311" s="14" t="str">
+        <x:v>Sefine Shipyard</x:v>
+      </x:c>
+      <x:c r="C311" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="D311" s="14" t="str">
+        <x:v>Yalova</x:v>
+      </x:c>
+      <x:c r="E311" s="14" t="str">
+        <x:v>Turkey</x:v>
+      </x:c>
+      <x:c r="F311" s="14" t="str"/>
+      <x:c r="G311" s="14" t="str">
+        <x:v>Commercial shipbuilding; government craft; repair; conversion; steel structures</x:v>
+      </x:c>
+      <x:c r="H311" s="14" t="str"/>
+      <x:c r="I311" s="14" t="str"/>
+      <x:c r="J311" s="14" t="str">
+        <x:v>Altınova dual-use/commercial yard</x:v>
+      </x:c>
+      <x:c r="K311" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L311" s="14" t="str">
+        <x:v>SRC127_017</x:v>
+      </x:c>
+      <x:c r="M311" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="N311" s="14" t="str"/>
+    </x:row>
+    <x:row r="312">
+      <x:c r="A312" s="14" t="str">
+        <x:v>COMP_LOCKHEED_MARTIN_CANADA</x:v>
+      </x:c>
+      <x:c r="B312" s="14" t="str">
+        <x:v>Lockheed Martin Canada</x:v>
+      </x:c>
+      <x:c r="C312" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="D312" s="14" t="str">
+        <x:v>Ottawa</x:v>
+      </x:c>
+      <x:c r="E312" s="14" t="str">
+        <x:v>Canada</x:v>
+      </x:c>
+      <x:c r="F312" s="14" t="str">
+        <x:v>Lockheed Martin subsidiary</x:v>
+      </x:c>
+      <x:c r="G312" s="14" t="str">
+        <x:v>Defence systems; naval design; systems integration</x:v>
+      </x:c>
+      <x:c r="H312" s="14" t="str"/>
+      <x:c r="I312" s="14" t="str"/>
+      <x:c r="J312" s="14" t="str">
+        <x:v>River-class destroyer design team lead</x:v>
+      </x:c>
+      <x:c r="K312" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L312" s="14" t="str">
+        <x:v>SRC127_003</x:v>
+      </x:c>
+      <x:c r="M312" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="N312" s="14" t="str"/>
+    </x:row>
+    <x:row r="313">
+      <x:c r="A313" s="14" t="str">
+        <x:v>COMP_BAE_SYSTEMS</x:v>
+      </x:c>
+      <x:c r="B313" s="14" t="str">
+        <x:v>BAE Systems</x:v>
+      </x:c>
+      <x:c r="C313" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="D313" s="14" t="str">
+        <x:v>London</x:v>
+      </x:c>
+      <x:c r="E313" s="14" t="str">
+        <x:v>United Kingdom</x:v>
+      </x:c>
+      <x:c r="F313" s="14" t="str">
+        <x:v>Publicly listed defence group</x:v>
+      </x:c>
+      <x:c r="G313" s="14" t="str">
+        <x:v>Naval design; defence systems; aerospace</x:v>
+      </x:c>
+      <x:c r="H313" s="14" t="str"/>
+      <x:c r="I313" s="14" t="str"/>
+      <x:c r="J313" s="14" t="str">
+        <x:v>Type 26 design origin for River-class Destroyer</x:v>
+      </x:c>
+      <x:c r="K313" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L313" s="14" t="str">
+        <x:v>SRC127_003</x:v>
+      </x:c>
+      <x:c r="M313" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="N313" s="14" t="str"/>
+    </x:row>
+    <x:row r="314">
+      <x:c r="A314" s="14" t="str">
+        <x:v>COMP_BABCOCK_CANADA</x:v>
+      </x:c>
+      <x:c r="B314" s="14" t="str">
+        <x:v>Babcock Canada</x:v>
+      </x:c>
+      <x:c r="C314" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="D314" s="14" t="str"/>
+      <x:c r="E314" s="14" t="str">
+        <x:v>Canada</x:v>
+      </x:c>
+      <x:c r="F314" s="14" t="str">
+        <x:v>Babcock International group</x:v>
+      </x:c>
+      <x:c r="G314" s="14" t="str">
+        <x:v>Naval support; submarine MRO; engineering</x:v>
+      </x:c>
+      <x:c r="H314" s="14" t="str"/>
+      <x:c r="I314" s="14" t="str"/>
+      <x:c r="J314" s="14" t="str">
+        <x:v>VISSC prime with Seaspan Victoria as prime subcontractor</x:v>
+      </x:c>
+      <x:c r="K314" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L314" s="14" t="str">
+        <x:v>SRC127_005</x:v>
+      </x:c>
+      <x:c r="M314" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="N314" s="14" t="str"/>
+    </x:row>
+    <x:row r="315">
+      <x:c r="A315" s="14" t="str">
+        <x:v>COMP_BADAGRY_PORT_DEV</x:v>
+      </x:c>
+      <x:c r="B315" s="14" t="str">
+        <x:v>Badagry Port Development</x:v>
+      </x:c>
+      <x:c r="C315" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="D315" s="14" t="str">
+        <x:v>Lagos</x:v>
+      </x:c>
+      <x:c r="E315" s="14" t="str">
+        <x:v>Nigeria</x:v>
+      </x:c>
+      <x:c r="F315" s="14" t="str"/>
+      <x:c r="G315" s="14" t="str">
+        <x:v>Greenfield port development</x:v>
+      </x:c>
+      <x:c r="H315" s="14" t="str"/>
+      <x:c r="I315" s="14" t="str"/>
+      <x:c r="J315" s="14" t="str">
+        <x:v>Developer associated with Badagry Deep Sea Port negotiations</x:v>
+      </x:c>
+      <x:c r="K315" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L315" s="14" t="str">
+        <x:v>SRC127_019</x:v>
+      </x:c>
+      <x:c r="M315" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="N315" s="14" t="str"/>
+    </x:row>
+    <x:row r="316">
+      <x:c r="A316" s="14" t="str">
+        <x:v>COMP_SIMFER</x:v>
+      </x:c>
+      <x:c r="B316" s="14" t="str">
+        <x:v>SimFer</x:v>
+      </x:c>
+      <x:c r="C316" s="14" t="str">
+        <x:v>JV / Company</x:v>
+      </x:c>
+      <x:c r="D316" s="14" t="str">
+        <x:v>Conakry</x:v>
+      </x:c>
+      <x:c r="E316" s="14" t="str">
+        <x:v>Guinea</x:v>
+      </x:c>
+      <x:c r="F316" s="14" t="str">
+        <x:v>Government of Guinea + Rio Tinto + CIOH consortium</x:v>
+      </x:c>
+      <x:c r="G316" s="14" t="str">
+        <x:v>Mining; rail; port infrastructure; iron ore exports</x:v>
+      </x:c>
+      <x:c r="H316" s="14" t="str"/>
+      <x:c r="I316" s="14" t="str"/>
+      <x:c r="J316" s="14" t="str">
+        <x:v>Integrated Simandou mine-rail-port JV</x:v>
+      </x:c>
+      <x:c r="K316" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L316" s="14" t="str">
+        <x:v>SRC127_018</x:v>
+      </x:c>
+      <x:c r="M316" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="N316" s="14" t="str"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -48661,6 +49223,276 @@
       </x:c>
       <x:c r="E1867" s="14" t="str"/>
       <x:c r="F1867" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1868">
+      <x:c r="A1868" s="14" t="str">
+        <x:v>COMP_EDGE</x:v>
+      </x:c>
+      <x:c r="B1868" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1868" s="14" t="str">
+        <x:v>EDGE Group</x:v>
+      </x:c>
+      <x:c r="D1868" s="14" t="str">
+        <x:v>United Arab Emirates</x:v>
+      </x:c>
+      <x:c r="E1868" s="14" t="str"/>
+      <x:c r="F1868" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1869">
+      <x:c r="A1869" s="14" t="str">
+        <x:v>COMP_ADSB</x:v>
+      </x:c>
+      <x:c r="B1869" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1869" s="14" t="str">
+        <x:v>Abu Dhabi Ship Building (ADSB)</x:v>
+      </x:c>
+      <x:c r="D1869" s="14" t="str">
+        <x:v>United Arab Emirates</x:v>
+      </x:c>
+      <x:c r="E1869" s="14" t="str"/>
+      <x:c r="F1869" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1870">
+      <x:c r="A1870" s="14" t="str">
+        <x:v>COMP_MAESTRAL</x:v>
+      </x:c>
+      <x:c r="B1870" s="14" t="str">
+        <x:v>JV</x:v>
+      </x:c>
+      <x:c r="C1870" s="14" t="str">
+        <x:v>MAESTRAL</x:v>
+      </x:c>
+      <x:c r="D1870" s="14" t="str">
+        <x:v>United Arab Emirates</x:v>
+      </x:c>
+      <x:c r="E1870" s="14" t="str"/>
+      <x:c r="F1870" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1871">
+      <x:c r="A1871" s="14" t="str">
+        <x:v>COMP_IRVING</x:v>
+      </x:c>
+      <x:c r="B1871" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1871" s="14" t="str">
+        <x:v>Irving Shipbuilding Inc.</x:v>
+      </x:c>
+      <x:c r="D1871" s="14" t="str">
+        <x:v>Canada</x:v>
+      </x:c>
+      <x:c r="E1871" s="14" t="str"/>
+      <x:c r="F1871" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1872">
+      <x:c r="A1872" s="14" t="str">
+        <x:v>COMP_BOLLINGER</x:v>
+      </x:c>
+      <x:c r="B1872" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1872" s="14" t="str">
+        <x:v>Bollinger Shipyards</x:v>
+      </x:c>
+      <x:c r="D1872" s="14" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="E1872" s="14" t="str"/>
+      <x:c r="F1872" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1873">
+      <x:c r="A1873" s="14" t="str">
+        <x:v>COMP_RMC</x:v>
+      </x:c>
+      <x:c r="B1873" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1873" s="14" t="str">
+        <x:v>Rauma Marine Constructions Oy</x:v>
+      </x:c>
+      <x:c r="D1873" s="14" t="str">
+        <x:v>Finland</x:v>
+      </x:c>
+      <x:c r="E1873" s="14" t="str"/>
+      <x:c r="F1873" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1874">
+      <x:c r="A1874" s="14" t="str">
+        <x:v>COMP_AKER_ARCTIC</x:v>
+      </x:c>
+      <x:c r="B1874" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1874" s="14" t="str">
+        <x:v>Aker Arctic Technology Inc.</x:v>
+      </x:c>
+      <x:c r="D1874" s="14" t="str">
+        <x:v>Finland</x:v>
+      </x:c>
+      <x:c r="E1874" s="14" t="str"/>
+      <x:c r="F1874" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1875">
+      <x:c r="A1875" s="14" t="str">
+        <x:v>COMP_DAMEN</x:v>
+      </x:c>
+      <x:c r="B1875" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1875" s="14" t="str">
+        <x:v>Damen Shipyards Group</x:v>
+      </x:c>
+      <x:c r="D1875" s="14" t="str">
+        <x:v>Netherlands</x:v>
+      </x:c>
+      <x:c r="E1875" s="14" t="str"/>
+      <x:c r="F1875" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1876">
+      <x:c r="A1876" s="14" t="str">
+        <x:v>COMP_RMK</x:v>
+      </x:c>
+      <x:c r="B1876" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1876" s="14" t="str">
+        <x:v>RMK Marine</x:v>
+      </x:c>
+      <x:c r="D1876" s="14" t="str">
+        <x:v>Turkey</x:v>
+      </x:c>
+      <x:c r="E1876" s="14" t="str"/>
+      <x:c r="F1876" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1877">
+      <x:c r="A1877" s="14" t="str">
+        <x:v>COMP_SEFINE</x:v>
+      </x:c>
+      <x:c r="B1877" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1877" s="14" t="str">
+        <x:v>Sefine Shipyard</x:v>
+      </x:c>
+      <x:c r="D1877" s="14" t="str">
+        <x:v>Turkey</x:v>
+      </x:c>
+      <x:c r="E1877" s="14" t="str"/>
+      <x:c r="F1877" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1878">
+      <x:c r="A1878" s="14" t="str">
+        <x:v>COMP_LOCKHEED_MARTIN_CANADA</x:v>
+      </x:c>
+      <x:c r="B1878" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1878" s="14" t="str">
+        <x:v>Lockheed Martin Canada</x:v>
+      </x:c>
+      <x:c r="D1878" s="14" t="str">
+        <x:v>Canada</x:v>
+      </x:c>
+      <x:c r="E1878" s="14" t="str"/>
+      <x:c r="F1878" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1879">
+      <x:c r="A1879" s="14" t="str">
+        <x:v>COMP_BAE_SYSTEMS</x:v>
+      </x:c>
+      <x:c r="B1879" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1879" s="14" t="str">
+        <x:v>BAE Systems</x:v>
+      </x:c>
+      <x:c r="D1879" s="14" t="str">
+        <x:v>United Kingdom</x:v>
+      </x:c>
+      <x:c r="E1879" s="14" t="str"/>
+      <x:c r="F1879" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1880">
+      <x:c r="A1880" s="14" t="str">
+        <x:v>COMP_BABCOCK_CANADA</x:v>
+      </x:c>
+      <x:c r="B1880" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1880" s="14" t="str">
+        <x:v>Babcock Canada</x:v>
+      </x:c>
+      <x:c r="D1880" s="14" t="str">
+        <x:v>Canada</x:v>
+      </x:c>
+      <x:c r="E1880" s="14" t="str"/>
+      <x:c r="F1880" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1881">
+      <x:c r="A1881" s="14" t="str">
+        <x:v>COMP_BADAGRY_PORT_DEV</x:v>
+      </x:c>
+      <x:c r="B1881" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1881" s="14" t="str">
+        <x:v>Badagry Port Development</x:v>
+      </x:c>
+      <x:c r="D1881" s="14" t="str">
+        <x:v>Nigeria</x:v>
+      </x:c>
+      <x:c r="E1881" s="14" t="str"/>
+      <x:c r="F1881" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1882">
+      <x:c r="A1882" s="14" t="str">
+        <x:v>COMP_SIMFER</x:v>
+      </x:c>
+      <x:c r="B1882" s="14" t="str">
+        <x:v>JV</x:v>
+      </x:c>
+      <x:c r="C1882" s="14" t="str">
+        <x:v>SimFer</x:v>
+      </x:c>
+      <x:c r="D1882" s="14" t="str">
+        <x:v>Guinea</x:v>
+      </x:c>
+      <x:c r="E1882" s="14" t="str"/>
+      <x:c r="F1882" s="14" t="str">
         <x:v>Active</x:v>
       </x:c>
     </x:row>
@@ -52492,6 +53324,98 @@
       </x:c>
       <x:c r="G166" s="14" t="str">
         <x:v>SRC1261_003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="167">
+      <x:c r="A167" s="14" t="str">
+        <x:v>REL127_001</x:v>
+      </x:c>
+      <x:c r="B167" s="14" t="str">
+        <x:v>COMP_EDGE</x:v>
+      </x:c>
+      <x:c r="C167" s="14" t="str">
+        <x:v>OWNS_51_PERCENT</x:v>
+      </x:c>
+      <x:c r="D167" s="14" t="str">
+        <x:v>COMP_MAESTRAL</x:v>
+      </x:c>
+      <x:c r="E167" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F167" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G167" s="14" t="str">
+        <x:v>SRC127_001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="168">
+      <x:c r="A168" s="14" t="str">
+        <x:v>REL127_002</x:v>
+      </x:c>
+      <x:c r="B168" s="14" t="str">
+        <x:v>COMP_FINCANTIERI</x:v>
+      </x:c>
+      <x:c r="C168" s="14" t="str">
+        <x:v>OWNS_49_PERCENT</x:v>
+      </x:c>
+      <x:c r="D168" s="14" t="str">
+        <x:v>COMP_MAESTRAL</x:v>
+      </x:c>
+      <x:c r="E168" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F168" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G168" s="14" t="str">
+        <x:v>SRC127_001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="169">
+      <x:c r="A169" s="14" t="str">
+        <x:v>REL127_003</x:v>
+      </x:c>
+      <x:c r="B169" s="14" t="str">
+        <x:v>COMP_EDGE</x:v>
+      </x:c>
+      <x:c r="C169" s="14" t="str">
+        <x:v>PARENT_OF</x:v>
+      </x:c>
+      <x:c r="D169" s="14" t="str">
+        <x:v>COMP_ADSB</x:v>
+      </x:c>
+      <x:c r="E169" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F169" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G169" s="14" t="str">
+        <x:v>SRC127_002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170">
+      <x:c r="A170" s="14" t="str">
+        <x:v>REL127_004</x:v>
+      </x:c>
+      <x:c r="B170" s="14" t="str">
+        <x:v>COMP_BABCOCK_CANADA</x:v>
+      </x:c>
+      <x:c r="C170" s="14" t="str">
+        <x:v>PRIME_SUPPORT_CONTRACTOR_WITH</x:v>
+      </x:c>
+      <x:c r="D170" s="14" t="str">
+        <x:v>COMP_SEASPAN_ULC</x:v>
+      </x:c>
+      <x:c r="E170" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F170" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G170" s="14" t="str">
+        <x:v>SRC127_005</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/data/01_core_entities.xlsx
+++ b/data/01_core_entities.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="Rbec542a3b3254636"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Companies" sheetId="2" r:id="R6c3c913d5ec44e71"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Entity Registry" sheetId="3" r:id="R0b0fd4adda4b4708"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="Rdd4142a93f074187"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company System Footprints" sheetId="5" r:id="R357e5d16c5614df1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="People" sheetId="6" r:id="R5c294c44e38a4e07"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leadership Roles" sheetId="7" r:id="R4eebb6a795824a7a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Dictionary" sheetId="8" r:id="R34f0c38ae04c4d11"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runtime Table Crosswalk" sheetId="9" r:id="R69da433867b8431a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Queue" sheetId="10" r:id="Rb0d92e6fe0eb4277"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R78348d594aa3421a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Companies" sheetId="2" r:id="R440315df678d4899"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Entity Registry" sheetId="3" r:id="R0cc33758108a4567"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="Rc71bbcd9e60f4689"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company System Footprints" sheetId="5" r:id="R20036de615074f22"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="People" sheetId="6" r:id="Re395b021bc9d4ab9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leadership Roles" sheetId="7" r:id="R1b256cc0a3054b30"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Dictionary" sheetId="8" r:id="Rc1ecffa12d6a4aeb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runtime Table Crosswalk" sheetId="9" r:id="R128d33591ce64515"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Queue" sheetId="10" r:id="R6fbc5c2f4ccb4825"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -14123,6 +14123,181 @@
       </x:c>
       <x:c r="N316" s="14" t="str"/>
     </x:row>
+    <x:row r="317">
+      <x:c r="A317" t="str">
+        <x:v>COMP_MG_FLOT</x:v>
+      </x:c>
+      <x:c r="B317" t="str">
+        <x:v>MG-FLOT LLC</x:v>
+      </x:c>
+      <x:c r="C317" t="str">
+        <x:v>Shipping company / vessel owner-manager</x:v>
+      </x:c>
+      <x:c r="D317"/>
+      <x:c r="E317" t="str">
+        <x:v>Russia</x:v>
+      </x:c>
+      <x:c r="F317" t="str">
+        <x:v>Sanctioned Russian maritime shipping company; formerly Transmorflot LLC</x:v>
+      </x:c>
+      <x:c r="G317" t="str">
+        <x:v>Vessel ownership; commercial management; ISM management</x:v>
+      </x:c>
+      <x:c r="H317"/>
+      <x:c r="I317"/>
+      <x:c r="J317" t="str">
+        <x:v>Owner/manager of LADY MARIIA; former name Transmorflot LLC</x:v>
+      </x:c>
+      <x:c r="K317" t="str">
+        <x:v>Active / sanctioned</x:v>
+      </x:c>
+      <x:c r="L317" t="str">
+        <x:v>SRC130_001</x:v>
+      </x:c>
+      <x:c r="M317" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="318">
+      <x:c r="A318" t="str">
+        <x:v>COMP_WAVEWHISPER</x:v>
+      </x:c>
+      <x:c r="B318" t="str">
+        <x:v>Wavewhisper Shipping Ltd</x:v>
+      </x:c>
+      <x:c r="C318" t="str">
+        <x:v>Shipping company / vessel owner-operator</x:v>
+      </x:c>
+      <x:c r="D318"/>
+      <x:c r="E318"/>
+      <x:c r="F318"/>
+      <x:c r="G318" t="str">
+        <x:v>Tanker ownership / operation</x:v>
+      </x:c>
+      <x:c r="H318"/>
+      <x:c r="I318"/>
+      <x:c r="J318" t="str">
+        <x:v>UK sanctions list identifies as current owner/operator of SUN (IMO 9293117)</x:v>
+      </x:c>
+      <x:c r="K318" t="str">
+        <x:v>Active / sanctions-linked</x:v>
+      </x:c>
+      <x:c r="L318" t="str">
+        <x:v>SRC130_002</x:v>
+      </x:c>
+      <x:c r="M318" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="319">
+      <x:c r="A319" t="str">
+        <x:v>COMP_VROOM_MARINE</x:v>
+      </x:c>
+      <x:c r="B319" t="str">
+        <x:v>Vroom Marine Venture FZE</x:v>
+      </x:c>
+      <x:c r="C319" t="str">
+        <x:v>Ship management company</x:v>
+      </x:c>
+      <x:c r="D319" t="str">
+        <x:v>Sharjah</x:v>
+      </x:c>
+      <x:c r="E319" t="str">
+        <x:v>United Arab Emirates</x:v>
+      </x:c>
+      <x:c r="F319" t="str">
+        <x:v>Private UAE free-zone company</x:v>
+      </x:c>
+      <x:c r="G319" t="str">
+        <x:v>Ship management; tanker management</x:v>
+      </x:c>
+      <x:c r="H319"/>
+      <x:c r="I319"/>
+      <x:c r="J319" t="str">
+        <x:v>OFAC-designated company linked to ELOISE (IMO 9233234)</x:v>
+      </x:c>
+      <x:c r="K319" t="str">
+        <x:v>Active / sanctioned</x:v>
+      </x:c>
+      <x:c r="L319" t="str">
+        <x:v>SRC130_003</x:v>
+      </x:c>
+      <x:c r="M319" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="320">
+      <x:c r="A320" t="str">
+        <x:v>COMP_MANARAT_ALKHALEEJ</x:v>
+      </x:c>
+      <x:c r="B320" t="str">
+        <x:v>Manarat Alkhaleej Marine Services FZE</x:v>
+      </x:c>
+      <x:c r="C320" t="str">
+        <x:v>Marine services / ship management company</x:v>
+      </x:c>
+      <x:c r="D320" t="str">
+        <x:v>Sharjah</x:v>
+      </x:c>
+      <x:c r="E320" t="str">
+        <x:v>United Arab Emirates</x:v>
+      </x:c>
+      <x:c r="F320" t="str">
+        <x:v>Private UAE free-zone company</x:v>
+      </x:c>
+      <x:c r="G320" t="str">
+        <x:v>Marine services; ship management</x:v>
+      </x:c>
+      <x:c r="H320"/>
+      <x:c r="I320"/>
+      <x:c r="J320" t="str">
+        <x:v>OFAC-designated company linked to AL SAFA (IMO 9222649)</x:v>
+      </x:c>
+      <x:c r="K320" t="str">
+        <x:v>Active / sanctioned</x:v>
+      </x:c>
+      <x:c r="L320" t="str">
+        <x:v>SRC130_004</x:v>
+      </x:c>
+      <x:c r="M320" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="321">
+      <x:c r="A321" t="str">
+        <x:v>COMP_LAUREL_SHIPPING</x:v>
+      </x:c>
+      <x:c r="B321" t="str">
+        <x:v>Laurel Shipping Ltd</x:v>
+      </x:c>
+      <x:c r="C321" t="str">
+        <x:v>Shipping company</x:v>
+      </x:c>
+      <x:c r="D321"/>
+      <x:c r="E321" t="str">
+        <x:v>Cayman Islands</x:v>
+      </x:c>
+      <x:c r="F321" t="str">
+        <x:v>Private</x:v>
+      </x:c>
+      <x:c r="G321" t="str">
+        <x:v>Tanker ownership / shipping</x:v>
+      </x:c>
+      <x:c r="H321"/>
+      <x:c r="I321"/>
+      <x:c r="J321" t="str">
+        <x:v>OFAC-designated company linked to ANSHUN II (IMO 9253117)</x:v>
+      </x:c>
+      <x:c r="K321" t="str">
+        <x:v>Active / sanctioned</x:v>
+      </x:c>
+      <x:c r="L321" t="str">
+        <x:v>SRC130_005</x:v>
+      </x:c>
+      <x:c r="M321" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -49494,6 +49669,94 @@
       <x:c r="E1882" s="14" t="str"/>
       <x:c r="F1882" s="14" t="str">
         <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1883">
+      <x:c r="A1883" t="str">
+        <x:v>COMP_MG_FLOT</x:v>
+      </x:c>
+      <x:c r="B1883" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1883" t="str">
+        <x:v>MG-FLOT LLC</x:v>
+      </x:c>
+      <x:c r="D1883" t="str">
+        <x:v>Russia</x:v>
+      </x:c>
+      <x:c r="E1883"/>
+      <x:c r="F1883" t="str">
+        <x:v>Active / sanctioned</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1884">
+      <x:c r="A1884" t="str">
+        <x:v>COMP_WAVEWHISPER</x:v>
+      </x:c>
+      <x:c r="B1884" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1884" t="str">
+        <x:v>Wavewhisper Shipping Ltd</x:v>
+      </x:c>
+      <x:c r="D1884"/>
+      <x:c r="E1884"/>
+      <x:c r="F1884" t="str">
+        <x:v>Active / sanctions-linked</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1885">
+      <x:c r="A1885" t="str">
+        <x:v>COMP_VROOM_MARINE</x:v>
+      </x:c>
+      <x:c r="B1885" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1885" t="str">
+        <x:v>Vroom Marine Venture FZE</x:v>
+      </x:c>
+      <x:c r="D1885" t="str">
+        <x:v>United Arab Emirates</x:v>
+      </x:c>
+      <x:c r="E1885"/>
+      <x:c r="F1885" t="str">
+        <x:v>Active / sanctioned</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1886">
+      <x:c r="A1886" t="str">
+        <x:v>COMP_MANARAT_ALKHALEEJ</x:v>
+      </x:c>
+      <x:c r="B1886" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1886" t="str">
+        <x:v>Manarat Alkhaleej Marine Services FZE</x:v>
+      </x:c>
+      <x:c r="D1886" t="str">
+        <x:v>United Arab Emirates</x:v>
+      </x:c>
+      <x:c r="E1886"/>
+      <x:c r="F1886" t="str">
+        <x:v>Active / sanctioned</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1887">
+      <x:c r="A1887" t="str">
+        <x:v>COMP_LAUREL_SHIPPING</x:v>
+      </x:c>
+      <x:c r="B1887" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1887" t="str">
+        <x:v>Laurel Shipping Ltd</x:v>
+      </x:c>
+      <x:c r="D1887" t="str">
+        <x:v>Cayman Islands</x:v>
+      </x:c>
+      <x:c r="E1887"/>
+      <x:c r="F1887" t="str">
+        <x:v>Active / sanctioned</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -53417,6 +53680,136 @@
       <x:c r="G170" s="14" t="str">
         <x:v>SRC127_005</x:v>
       </x:c>
+    </x:row>
+    <x:row r="171">
+      <x:c r="A171" t="str">
+        <x:v>REL130_001</x:v>
+      </x:c>
+      <x:c r="B171" t="str">
+        <x:v>COMP_MG_FLOT</x:v>
+      </x:c>
+      <x:c r="C171" t="str">
+        <x:v>OWNS / MANAGES</x:v>
+      </x:c>
+      <x:c r="D171" t="str">
+        <x:v>VESSEL_SAN_001</x:v>
+      </x:c>
+      <x:c r="E171" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F171" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G171" t="str">
+        <x:v>SRC130_001</x:v>
+      </x:c>
+      <x:c r="H171"/>
+      <x:c r="I171"/>
+      <x:c r="J171"/>
+    </x:row>
+    <x:row r="172">
+      <x:c r="A172" t="str">
+        <x:v>REL130_002</x:v>
+      </x:c>
+      <x:c r="B172" t="str">
+        <x:v>COMP_WAVEWHISPER</x:v>
+      </x:c>
+      <x:c r="C172" t="str">
+        <x:v>OWNS / OPERATES</x:v>
+      </x:c>
+      <x:c r="D172" t="str">
+        <x:v>VESSEL_SAN_002</x:v>
+      </x:c>
+      <x:c r="E172" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F172" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G172" t="str">
+        <x:v>SRC130_002</x:v>
+      </x:c>
+      <x:c r="H172"/>
+      <x:c r="I172"/>
+      <x:c r="J172"/>
+    </x:row>
+    <x:row r="173">
+      <x:c r="A173" t="str">
+        <x:v>REL130_003</x:v>
+      </x:c>
+      <x:c r="B173" t="str">
+        <x:v>COMP_VROOM_MARINE</x:v>
+      </x:c>
+      <x:c r="C173" t="str">
+        <x:v>MANAGES</x:v>
+      </x:c>
+      <x:c r="D173" t="str">
+        <x:v>VESSEL_SAN_003</x:v>
+      </x:c>
+      <x:c r="E173" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F173" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G173" t="str">
+        <x:v>SRC130_003</x:v>
+      </x:c>
+      <x:c r="H173"/>
+      <x:c r="I173"/>
+      <x:c r="J173"/>
+    </x:row>
+    <x:row r="174">
+      <x:c r="A174" t="str">
+        <x:v>REL130_004</x:v>
+      </x:c>
+      <x:c r="B174" t="str">
+        <x:v>COMP_MANARAT_ALKHALEEJ</x:v>
+      </x:c>
+      <x:c r="C174" t="str">
+        <x:v>MANAGES</x:v>
+      </x:c>
+      <x:c r="D174" t="str">
+        <x:v>VESSEL_SAN_004</x:v>
+      </x:c>
+      <x:c r="E174" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F174" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G174" t="str">
+        <x:v>SRC130_004</x:v>
+      </x:c>
+      <x:c r="H174"/>
+      <x:c r="I174"/>
+      <x:c r="J174"/>
+    </x:row>
+    <x:row r="175">
+      <x:c r="A175" t="str">
+        <x:v>REL130_005</x:v>
+      </x:c>
+      <x:c r="B175" t="str">
+        <x:v>COMP_LAUREL_SHIPPING</x:v>
+      </x:c>
+      <x:c r="C175" t="str">
+        <x:v>OWNS / MANAGES</x:v>
+      </x:c>
+      <x:c r="D175" t="str">
+        <x:v>VESSEL_SAN_005</x:v>
+      </x:c>
+      <x:c r="E175" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F175" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G175" t="str">
+        <x:v>SRC130_005</x:v>
+      </x:c>
+      <x:c r="H175"/>
+      <x:c r="I175"/>
+      <x:c r="J175"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/01_core_entities.xlsx
+++ b/data/01_core_entities.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R78348d594aa3421a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Companies" sheetId="2" r:id="R440315df678d4899"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Entity Registry" sheetId="3" r:id="R0cc33758108a4567"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="Rc71bbcd9e60f4689"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company System Footprints" sheetId="5" r:id="R20036de615074f22"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="People" sheetId="6" r:id="Re395b021bc9d4ab9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leadership Roles" sheetId="7" r:id="R1b256cc0a3054b30"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Dictionary" sheetId="8" r:id="Rc1ecffa12d6a4aeb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runtime Table Crosswalk" sheetId="9" r:id="R128d33591ce64515"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Queue" sheetId="10" r:id="R6fbc5c2f4ccb4825"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R6713dd1b92d64292"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Companies" sheetId="2" r:id="R869a1e6a85674035"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Entity Registry" sheetId="3" r:id="R81e93ad7af6d4db1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="R9de640cc68ec48f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company System Footprints" sheetId="5" r:id="Rdd9e623c0e384fd9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="People" sheetId="6" r:id="R944a6b3a44874e0e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leadership Roles" sheetId="7" r:id="R0ed7d95529fa400b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Dictionary" sheetId="8" r:id="Rab22a5d4eed043a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runtime Table Crosswalk" sheetId="9" r:id="Rc516d217edd74f65"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Queue" sheetId="10" r:id="Rac70f59014c64b58"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -14298,6 +14298,80 @@
         <x:v>2026-09-09</x:v>
       </x:c>
     </x:row>
+    <x:row r="322">
+      <x:c r="A322" t="str">
+        <x:v>COMP_NAVAL_GROUP</x:v>
+      </x:c>
+      <x:c r="B322" t="str">
+        <x:v>Naval Group</x:v>
+      </x:c>
+      <x:c r="C322" t="str">
+        <x:v>Naval shipbuilder</x:v>
+      </x:c>
+      <x:c r="D322" t="str">
+        <x:v>Paris</x:v>
+      </x:c>
+      <x:c r="E322" t="str">
+        <x:v>France</x:v>
+      </x:c>
+      <x:c r="F322" t="str">
+        <x:v>French state-influenced naval defence group</x:v>
+      </x:c>
+      <x:c r="G322" t="str">
+        <x:v>Naval design; construction; combat systems; services</x:v>
+      </x:c>
+      <x:c r="H322"/>
+      <x:c r="I322"/>
+      <x:c r="J322" t="str">
+        <x:v>Builder of UAE Bani Yas-class Gowind corvettes at Lorient</x:v>
+      </x:c>
+      <x:c r="K322" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L322" t="str">
+        <x:v>SRC131_010</x:v>
+      </x:c>
+      <x:c r="M322" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="323">
+      <x:c r="A323" t="str">
+        <x:v>COMP_CMN_NAVAL</x:v>
+      </x:c>
+      <x:c r="B323" t="str">
+        <x:v>CMN Naval</x:v>
+      </x:c>
+      <x:c r="C323" t="str">
+        <x:v>Naval and commercial shipbuilder</x:v>
+      </x:c>
+      <x:c r="D323" t="str">
+        <x:v>Cherbourg</x:v>
+      </x:c>
+      <x:c r="E323" t="str">
+        <x:v>France</x:v>
+      </x:c>
+      <x:c r="F323" t="str">
+        <x:v>Private shipbuilder</x:v>
+      </x:c>
+      <x:c r="G323" t="str">
+        <x:v>Patrol craft; corvettes; commercial craft</x:v>
+      </x:c>
+      <x:c r="H323"/>
+      <x:c r="I323"/>
+      <x:c r="J323" t="str">
+        <x:v>Built lead Baynunah-class corvette and supports EDGE export programmes</x:v>
+      </x:c>
+      <x:c r="K323" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L323" t="str">
+        <x:v>SRC131_011</x:v>
+      </x:c>
+      <x:c r="M323" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -49757,6 +49831,158 @@
       <x:c r="E1887"/>
       <x:c r="F1887" t="str">
         <x:v>Active / sanctioned</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1888">
+      <x:c r="A1888" t="str">
+        <x:v>COMP_NAVAL_GROUP</x:v>
+      </x:c>
+      <x:c r="B1888" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1888" t="str">
+        <x:v>Naval Group</x:v>
+      </x:c>
+      <x:c r="D1888" t="str">
+        <x:v>France</x:v>
+      </x:c>
+      <x:c r="E1888"/>
+      <x:c r="F1888" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1889">
+      <x:c r="A1889" t="str">
+        <x:v>COMP_CMN_NAVAL</x:v>
+      </x:c>
+      <x:c r="B1889" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1889" t="str">
+        <x:v>CMN Naval</x:v>
+      </x:c>
+      <x:c r="D1889" t="str">
+        <x:v>France</x:v>
+      </x:c>
+      <x:c r="E1889"/>
+      <x:c r="F1889" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1890">
+      <x:c r="A1890" t="str">
+        <x:v>GOV_CANADA</x:v>
+      </x:c>
+      <x:c r="B1890" t="str">
+        <x:v>Government</x:v>
+      </x:c>
+      <x:c r="C1890" t="str">
+        <x:v>Government of Canada</x:v>
+      </x:c>
+      <x:c r="D1890" t="str">
+        <x:v>Canada</x:v>
+      </x:c>
+      <x:c r="E1890"/>
+      <x:c r="F1890" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1891">
+      <x:c r="A1891" t="str">
+        <x:v>MIL_RCN</x:v>
+      </x:c>
+      <x:c r="B1891" t="str">
+        <x:v>Military Service</x:v>
+      </x:c>
+      <x:c r="C1891" t="str">
+        <x:v>Royal Canadian Navy</x:v>
+      </x:c>
+      <x:c r="D1891" t="str">
+        <x:v>Canada</x:v>
+      </x:c>
+      <x:c r="E1891" t="str">
+        <x:v>GOV_CANADA</x:v>
+      </x:c>
+      <x:c r="F1891" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1892">
+      <x:c r="A1892" t="str">
+        <x:v>GOV_CCG</x:v>
+      </x:c>
+      <x:c r="B1892" t="str">
+        <x:v>Coast Guard</x:v>
+      </x:c>
+      <x:c r="C1892" t="str">
+        <x:v>Canadian Coast Guard</x:v>
+      </x:c>
+      <x:c r="D1892" t="str">
+        <x:v>Canada</x:v>
+      </x:c>
+      <x:c r="E1892" t="str">
+        <x:v>GOV_CANADA</x:v>
+      </x:c>
+      <x:c r="F1892" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1893">
+      <x:c r="A1893" t="str">
+        <x:v>GOV_UAE</x:v>
+      </x:c>
+      <x:c r="B1893" t="str">
+        <x:v>Government</x:v>
+      </x:c>
+      <x:c r="C1893" t="str">
+        <x:v>Government of the United Arab Emirates</x:v>
+      </x:c>
+      <x:c r="D1893" t="str">
+        <x:v>United Arab Emirates</x:v>
+      </x:c>
+      <x:c r="E1893"/>
+      <x:c r="F1893" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1894">
+      <x:c r="A1894" t="str">
+        <x:v>MIL_UAE_NAVY</x:v>
+      </x:c>
+      <x:c r="B1894" t="str">
+        <x:v>Military Service</x:v>
+      </x:c>
+      <x:c r="C1894" t="str">
+        <x:v>UAE Navy</x:v>
+      </x:c>
+      <x:c r="D1894" t="str">
+        <x:v>United Arab Emirates</x:v>
+      </x:c>
+      <x:c r="E1894" t="str">
+        <x:v>GOV_UAE</x:v>
+      </x:c>
+      <x:c r="F1894" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1895">
+      <x:c r="A1895" t="str">
+        <x:v>GOV_UAE_CG</x:v>
+      </x:c>
+      <x:c r="B1895" t="str">
+        <x:v>Coast Guard</x:v>
+      </x:c>
+      <x:c r="C1895" t="str">
+        <x:v>UAE Coast Guard</x:v>
+      </x:c>
+      <x:c r="D1895" t="str">
+        <x:v>United Arab Emirates</x:v>
+      </x:c>
+      <x:c r="E1895" t="str">
+        <x:v>GOV_UAE</x:v>
+      </x:c>
+      <x:c r="F1895" t="str">
+        <x:v>Active</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/data/01_core_entities.xlsx
+++ b/data/01_core_entities.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R6713dd1b92d64292"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Companies" sheetId="2" r:id="R869a1e6a85674035"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Entity Registry" sheetId="3" r:id="R81e93ad7af6d4db1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="R9de640cc68ec48f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company System Footprints" sheetId="5" r:id="Rdd9e623c0e384fd9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="People" sheetId="6" r:id="R944a6b3a44874e0e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leadership Roles" sheetId="7" r:id="R0ed7d95529fa400b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Dictionary" sheetId="8" r:id="Rab22a5d4eed043a5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runtime Table Crosswalk" sheetId="9" r:id="Rc516d217edd74f65"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Queue" sheetId="10" r:id="Rac70f59014c64b58"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R8d48ea72abe9450f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Companies" sheetId="2" r:id="R0bf620b565714430"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Entity Registry" sheetId="3" r:id="R20ced59a7359414e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="Rfd230bf0dea04b6a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company System Footprints" sheetId="5" r:id="R1802128bce3a4b02"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="People" sheetId="6" r:id="R7c63e9bd402447d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leadership Roles" sheetId="7" r:id="Rb72bfe5b2e1646c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Dictionary" sheetId="8" r:id="R3bbf9ba122304789"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runtime Table Crosswalk" sheetId="9" r:id="R33c501cbb6c9426c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Queue" sheetId="10" r:id="R62cc4662163843da"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -14372,6 +14372,179 @@
         <x:v>2026-09-09</x:v>
       </x:c>
     </x:row>
+    <x:row r="324">
+      <x:c r="A324" t="str">
+        <x:v>COMP_ARKADIA_MARITIME</x:v>
+      </x:c>
+      <x:c r="B324" t="str">
+        <x:v>Arkadia Maritime Incorporated</x:v>
+      </x:c>
+      <x:c r="C324" t="str">
+        <x:v>Shipping company / tanker owner</x:v>
+      </x:c>
+      <x:c r="D324"/>
+      <x:c r="E324"/>
+      <x:c r="F324" t="str">
+        <x:v>Private shipping company</x:v>
+      </x:c>
+      <x:c r="G324" t="str">
+        <x:v>Tanker ownership</x:v>
+      </x:c>
+      <x:c r="H324"/>
+      <x:c r="I324"/>
+      <x:c r="J324" t="str">
+        <x:v>OFAC linked AQUARIS (IMO 9251822; now RIESCO) to Arkadia at designation</x:v>
+      </x:c>
+      <x:c r="K324" t="str">
+        <x:v>Sanctions-linked</x:v>
+      </x:c>
+      <x:c r="L324" t="str">
+        <x:v>SRC132_006</x:v>
+      </x:c>
+      <x:c r="M324" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="325">
+      <x:c r="A325" t="str">
+        <x:v>COMP_ALGAE_SHIP</x:v>
+      </x:c>
+      <x:c r="B325" t="str">
+        <x:v>Algae Ship Charter - FZCO</x:v>
+      </x:c>
+      <x:c r="C325" t="str">
+        <x:v>Shipping / chartering company</x:v>
+      </x:c>
+      <x:c r="D325" t="str">
+        <x:v>Dubai</x:v>
+      </x:c>
+      <x:c r="E325" t="str">
+        <x:v>United Arab Emirates</x:v>
+      </x:c>
+      <x:c r="F325" t="str">
+        <x:v>Free-zone company</x:v>
+      </x:c>
+      <x:c r="G325" t="str">
+        <x:v>Ship chartering / tanker operations</x:v>
+      </x:c>
+      <x:c r="H325"/>
+      <x:c r="I325"/>
+      <x:c r="J325" t="str">
+        <x:v>OFAC linked CHARMINAR (IMO 9318022) to Algae Ship Charter - FZCO</x:v>
+      </x:c>
+      <x:c r="K325" t="str">
+        <x:v>Sanctioned / designation-linked</x:v>
+      </x:c>
+      <x:c r="L325" t="str">
+        <x:v>SRC132_005</x:v>
+      </x:c>
+      <x:c r="M325" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="326">
+      <x:c r="A326" t="str">
+        <x:v>COMP_INVINCIBLE_SHIPPING</x:v>
+      </x:c>
+      <x:c r="B326" t="str">
+        <x:v>Invincible Shipping Services Inc.</x:v>
+      </x:c>
+      <x:c r="C326" t="str">
+        <x:v>Shipping company / registered owner</x:v>
+      </x:c>
+      <x:c r="D326"/>
+      <x:c r="E326"/>
+      <x:c r="F326" t="str">
+        <x:v>Private shipping company</x:v>
+      </x:c>
+      <x:c r="G326" t="str">
+        <x:v>Tanker ownership</x:v>
+      </x:c>
+      <x:c r="H326"/>
+      <x:c r="I326"/>
+      <x:c r="J326" t="str">
+        <x:v>ClassNK lists registered owner of NEW ANDROS (IMO 9294252)</x:v>
+      </x:c>
+      <x:c r="K326" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L326" t="str">
+        <x:v>SRC132_007</x:v>
+      </x:c>
+      <x:c r="M326" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="327">
+      <x:c r="A327" t="str">
+        <x:v>COMP_NEW_SHIPPING</x:v>
+      </x:c>
+      <x:c r="B327" t="str">
+        <x:v>New Shipping Limited</x:v>
+      </x:c>
+      <x:c r="C327" t="str">
+        <x:v>Ship management company</x:v>
+      </x:c>
+      <x:c r="D327"/>
+      <x:c r="E327"/>
+      <x:c r="F327" t="str">
+        <x:v>Private ship manager</x:v>
+      </x:c>
+      <x:c r="G327" t="str">
+        <x:v>Ship management / ISM management</x:v>
+      </x:c>
+      <x:c r="H327"/>
+      <x:c r="I327"/>
+      <x:c r="J327" t="str">
+        <x:v>ClassNK lists management company of NEW ANDROS (IMO 9294252)</x:v>
+      </x:c>
+      <x:c r="K327" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L327" t="str">
+        <x:v>SRC132_007</x:v>
+      </x:c>
+      <x:c r="M327" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="328">
+      <x:c r="A328" t="str">
+        <x:v>COMP_IOTC</x:v>
+      </x:c>
+      <x:c r="B328" t="str">
+        <x:v>Iraqi Oil Tankers Company</x:v>
+      </x:c>
+      <x:c r="C328" t="str">
+        <x:v>State-owned tanker / shipping company</x:v>
+      </x:c>
+      <x:c r="D328" t="str">
+        <x:v>Basra</x:v>
+      </x:c>
+      <x:c r="E328" t="str">
+        <x:v>Iraq</x:v>
+      </x:c>
+      <x:c r="F328" t="str">
+        <x:v>State-owned</x:v>
+      </x:c>
+      <x:c r="G328" t="str">
+        <x:v>Tanker operations; chartering; floating storage</x:v>
+      </x:c>
+      <x:c r="H328"/>
+      <x:c r="I328"/>
+      <x:c r="J328" t="str">
+        <x:v>Reuters reports NEW ANDROS was chartered by Iraqi Oil Tankers Company as fuel-oil storage</x:v>
+      </x:c>
+      <x:c r="K328" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L328" t="str">
+        <x:v>SRC132_003</x:v>
+      </x:c>
+      <x:c r="M328" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -49982,6 +50155,90 @@
         <x:v>GOV_UAE</x:v>
       </x:c>
       <x:c r="F1895" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1896">
+      <x:c r="A1896" t="str">
+        <x:v>COMP_ARKADIA_MARITIME</x:v>
+      </x:c>
+      <x:c r="B1896" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1896" t="str">
+        <x:v>Arkadia Maritime Incorporated</x:v>
+      </x:c>
+      <x:c r="D1896"/>
+      <x:c r="E1896"/>
+      <x:c r="F1896" t="str">
+        <x:v>Sanctions-linked</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1897">
+      <x:c r="A1897" t="str">
+        <x:v>COMP_ALGAE_SHIP</x:v>
+      </x:c>
+      <x:c r="B1897" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1897" t="str">
+        <x:v>Algae Ship Charter - FZCO</x:v>
+      </x:c>
+      <x:c r="D1897" t="str">
+        <x:v>United Arab Emirates</x:v>
+      </x:c>
+      <x:c r="E1897"/>
+      <x:c r="F1897" t="str">
+        <x:v>Sanctioned / designation-linked</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1898">
+      <x:c r="A1898" t="str">
+        <x:v>COMP_INVINCIBLE_SHIPPING</x:v>
+      </x:c>
+      <x:c r="B1898" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1898" t="str">
+        <x:v>Invincible Shipping Services Inc.</x:v>
+      </x:c>
+      <x:c r="D1898"/>
+      <x:c r="E1898"/>
+      <x:c r="F1898" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1899">
+      <x:c r="A1899" t="str">
+        <x:v>COMP_NEW_SHIPPING</x:v>
+      </x:c>
+      <x:c r="B1899" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1899" t="str">
+        <x:v>New Shipping Limited</x:v>
+      </x:c>
+      <x:c r="D1899"/>
+      <x:c r="E1899"/>
+      <x:c r="F1899" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1900">
+      <x:c r="A1900" t="str">
+        <x:v>COMP_IOTC</x:v>
+      </x:c>
+      <x:c r="B1900" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1900" t="str">
+        <x:v>Iraqi Oil Tankers Company</x:v>
+      </x:c>
+      <x:c r="D1900" t="str">
+        <x:v>Iraq</x:v>
+      </x:c>
+      <x:c r="E1900"/>
+      <x:c r="F1900" t="str">
         <x:v>Active</x:v>
       </x:c>
     </x:row>
@@ -54036,6 +54293,190 @@
       <x:c r="H175"/>
       <x:c r="I175"/>
       <x:c r="J175"/>
+    </x:row>
+    <x:row r="176">
+      <x:c r="A176" t="str">
+        <x:v>REL132_001</x:v>
+      </x:c>
+      <x:c r="B176" t="str">
+        <x:v>COMP_ARKADIA_MARITIME</x:v>
+      </x:c>
+      <x:c r="C176" t="str">
+        <x:v>DESIGNATION_LINKED_OWNER_OF</x:v>
+      </x:c>
+      <x:c r="D176" t="str">
+        <x:v>VES_GULF_RIESCO</x:v>
+      </x:c>
+      <x:c r="E176" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F176" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G176" t="str">
+        <x:v>SRC132_006</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="177">
+      <x:c r="A177" t="str">
+        <x:v>REL132_002</x:v>
+      </x:c>
+      <x:c r="B177" t="str">
+        <x:v>COMP_ALGAE_SHIP</x:v>
+      </x:c>
+      <x:c r="C177" t="str">
+        <x:v>DESIGNATION_LINKED_TO</x:v>
+      </x:c>
+      <x:c r="D177" t="str">
+        <x:v>VES_GULF_CHARMINAR</x:v>
+      </x:c>
+      <x:c r="E177" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F177" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G177" t="str">
+        <x:v>SRC132_005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="178">
+      <x:c r="A178" t="str">
+        <x:v>REL132_003</x:v>
+      </x:c>
+      <x:c r="B178" t="str">
+        <x:v>COMP_NITC</x:v>
+      </x:c>
+      <x:c r="C178" t="str">
+        <x:v>OWNS / MANAGES</x:v>
+      </x:c>
+      <x:c r="D178" t="str">
+        <x:v>VES_GULF_DERYA</x:v>
+      </x:c>
+      <x:c r="E178" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F178" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G178" t="str">
+        <x:v>SRC132_004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="179">
+      <x:c r="A179" t="str">
+        <x:v>REL132_004</x:v>
+      </x:c>
+      <x:c r="B179" t="str">
+        <x:v>COMP_INVINCIBLE_SHIPPING</x:v>
+      </x:c>
+      <x:c r="C179" t="str">
+        <x:v>REGISTERED_OWNER_OF</x:v>
+      </x:c>
+      <x:c r="D179" t="str">
+        <x:v>VES_GULF_NEW_ANDROS</x:v>
+      </x:c>
+      <x:c r="E179" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F179" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G179" t="str">
+        <x:v>SRC132_007</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="180">
+      <x:c r="A180" t="str">
+        <x:v>REL132_005</x:v>
+      </x:c>
+      <x:c r="B180" t="str">
+        <x:v>COMP_NEW_SHIPPING</x:v>
+      </x:c>
+      <x:c r="C180" t="str">
+        <x:v>MANAGES</x:v>
+      </x:c>
+      <x:c r="D180" t="str">
+        <x:v>VES_GULF_NEW_ANDROS</x:v>
+      </x:c>
+      <x:c r="E180" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F180" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G180" t="str">
+        <x:v>SRC132_007</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="181">
+      <x:c r="A181" t="str">
+        <x:v>REL132_006</x:v>
+      </x:c>
+      <x:c r="B181" t="str">
+        <x:v>COMP_IOTC</x:v>
+      </x:c>
+      <x:c r="C181" t="str">
+        <x:v>CHARTERS / USES_AS_STORAGE</x:v>
+      </x:c>
+      <x:c r="D181" t="str">
+        <x:v>VES_GULF_NEW_ANDROS</x:v>
+      </x:c>
+      <x:c r="E181" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F181" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G181" t="str">
+        <x:v>SRC132_003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="182">
+      <x:c r="A182" t="str">
+        <x:v>REL132_007</x:v>
+      </x:c>
+      <x:c r="B182" t="str">
+        <x:v>COMP_ALGAE_SHIP</x:v>
+      </x:c>
+      <x:c r="C182" t="str">
+        <x:v>SANCTIONS_LINKED_CHARTERER_OF</x:v>
+      </x:c>
+      <x:c r="D182" t="str">
+        <x:v>VES_GULF_CHARMINAR</x:v>
+      </x:c>
+      <x:c r="E182" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F182" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G182" t="str">
+        <x:v>SRC132_005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="183">
+      <x:c r="A183" t="str">
+        <x:v>REL132_008</x:v>
+      </x:c>
+      <x:c r="B183" t="str">
+        <x:v>COMP_NITC</x:v>
+      </x:c>
+      <x:c r="C183" t="str">
+        <x:v>SANCTIONS_LINKED_TO</x:v>
+      </x:c>
+      <x:c r="D183" t="str">
+        <x:v>VES_GULF_DERYA</x:v>
+      </x:c>
+      <x:c r="E183" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F183" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G183" t="str">
+        <x:v>SRC132_004</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/01_core_entities.xlsx
+++ b/data/01_core_entities.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R8d48ea72abe9450f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Companies" sheetId="2" r:id="R0bf620b565714430"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Entity Registry" sheetId="3" r:id="R20ced59a7359414e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="Rfd230bf0dea04b6a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company System Footprints" sheetId="5" r:id="R1802128bce3a4b02"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="People" sheetId="6" r:id="R7c63e9bd402447d2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leadership Roles" sheetId="7" r:id="Rb72bfe5b2e1646c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Dictionary" sheetId="8" r:id="R3bbf9ba122304789"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runtime Table Crosswalk" sheetId="9" r:id="R33c501cbb6c9426c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Queue" sheetId="10" r:id="R62cc4662163843da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R627e106700f04014"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Companies" sheetId="2" r:id="R11a5ce07f2e542be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Entity Registry" sheetId="3" r:id="R64a8ae53029e482f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="Rc98128ea385c4cca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company System Footprints" sheetId="5" r:id="R2bf7983dabeb4273"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="People" sheetId="6" r:id="Ra06f0f7fd4294e3a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leadership Roles" sheetId="7" r:id="R61052d6f2aff4026"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Dictionary" sheetId="8" r:id="Re4b7b49a94d74484"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runtime Table Crosswalk" sheetId="9" r:id="Rebc31a6bf8f04427"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Queue" sheetId="10" r:id="R4a565c8175164648"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -14545,6 +14545,740 @@
         <x:v>2026-09-09</x:v>
       </x:c>
     </x:row>
+    <x:row r="329">
+      <x:c r="A329" t="str">
+        <x:v>COMP_PENINSULA</x:v>
+      </x:c>
+      <x:c r="B329" t="str">
+        <x:v>Peninsula</x:v>
+      </x:c>
+      <x:c r="C329" t="str">
+        <x:v>Marine fuel supplier</x:v>
+      </x:c>
+      <x:c r="D329" t="str">
+        <x:v>Gibraltar</x:v>
+      </x:c>
+      <x:c r="E329" t="str">
+        <x:v>Gibraltar</x:v>
+      </x:c>
+      <x:c r="F329" t="str">
+        <x:v>Private</x:v>
+      </x:c>
+      <x:c r="G329" t="str">
+        <x:v>Marine fuel supply; bunker tanker chartering</x:v>
+      </x:c>
+      <x:c r="H329" t="str"/>
+      <x:c r="I329" t="str"/>
+      <x:c r="J329" t="str">
+        <x:v>Charterer of HERCULES STAR.</x:v>
+      </x:c>
+      <x:c r="K329" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L329" t="str">
+        <x:v>SRC133_001</x:v>
+      </x:c>
+      <x:c r="M329" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="330">
+      <x:c r="A330" t="str">
+        <x:v>COMP_HERCULES_TANKER</x:v>
+      </x:c>
+      <x:c r="B330" t="str">
+        <x:v>Hercules Tanker Management</x:v>
+      </x:c>
+      <x:c r="C330" t="str">
+        <x:v>Tanker management company</x:v>
+      </x:c>
+      <x:c r="D330" t="str"/>
+      <x:c r="E330" t="str">
+        <x:v>Gibraltar</x:v>
+      </x:c>
+      <x:c r="F330" t="str">
+        <x:v>Sister company to Peninsula</x:v>
+      </x:c>
+      <x:c r="G330" t="str">
+        <x:v>Bunker tanker provision; tanker management</x:v>
+      </x:c>
+      <x:c r="H330" t="str"/>
+      <x:c r="I330" t="str"/>
+      <x:c r="J330" t="str">
+        <x:v>Provides HERCULES STAR to Peninsula under charter.</x:v>
+      </x:c>
+      <x:c r="K330" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L330" t="str">
+        <x:v>SRC133_001</x:v>
+      </x:c>
+      <x:c r="M330" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="331">
+      <x:c r="A331" t="str">
+        <x:v>COMP_SAFEEN_MARINE</x:v>
+      </x:c>
+      <x:c r="B331" t="str">
+        <x:v>SAFEEN Marine Services</x:v>
+      </x:c>
+      <x:c r="C331" t="str">
+        <x:v>Maritime services company</x:v>
+      </x:c>
+      <x:c r="D331" t="str">
+        <x:v>Abu Dhabi</x:v>
+      </x:c>
+      <x:c r="E331" t="str">
+        <x:v>United Arab Emirates</x:v>
+      </x:c>
+      <x:c r="F331" t="str">
+        <x:v>AD Ports Group</x:v>
+      </x:c>
+      <x:c r="G331" t="str">
+        <x:v>Towage; harbour craft; pilotage; marine services</x:v>
+      </x:c>
+      <x:c r="H331" t="str"/>
+      <x:c r="I331" t="str"/>
+      <x:c r="J331" t="str">
+        <x:v>AD Ports maritime-services fleet, linked to Noatum through the group operating ecosystem.</x:v>
+      </x:c>
+      <x:c r="K331" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L331" t="str">
+        <x:v>SRC133_006</x:v>
+      </x:c>
+      <x:c r="M331" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="332">
+      <x:c r="A332" t="str">
+        <x:v>COMP_SAFEEN_OFFSHORE</x:v>
+      </x:c>
+      <x:c r="B332" t="str">
+        <x:v>SAFEEN Offshore</x:v>
+      </x:c>
+      <x:c r="C332" t="str">
+        <x:v>Offshore services business</x:v>
+      </x:c>
+      <x:c r="D332" t="str">
+        <x:v>Abu Dhabi</x:v>
+      </x:c>
+      <x:c r="E332" t="str">
+        <x:v>United Arab Emirates</x:v>
+      </x:c>
+      <x:c r="F332" t="str">
+        <x:v>AD Ports Group</x:v>
+      </x:c>
+      <x:c r="G332" t="str">
+        <x:v>Offshore support; subsea; project logistics</x:v>
+      </x:c>
+      <x:c r="H332" t="str"/>
+      <x:c r="I332" t="str"/>
+      <x:c r="J332" t="str">
+        <x:v>Offshore division within the AD Ports maritime cluster.</x:v>
+      </x:c>
+      <x:c r="K332" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L332" t="str">
+        <x:v>SRC133_004</x:v>
+      </x:c>
+      <x:c r="M332" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="333">
+      <x:c r="A333" t="str">
+        <x:v>COMP_ROYAL_CARIBBEAN_GROUP</x:v>
+      </x:c>
+      <x:c r="B333" t="str">
+        <x:v>Royal Caribbean Group</x:v>
+      </x:c>
+      <x:c r="C333" t="str">
+        <x:v>Cruise group</x:v>
+      </x:c>
+      <x:c r="D333" t="str">
+        <x:v>Miami</x:v>
+      </x:c>
+      <x:c r="E333" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="F333" t="str">
+        <x:v>Public company</x:v>
+      </x:c>
+      <x:c r="G333" t="str">
+        <x:v>Cruise lines; private destinations</x:v>
+      </x:c>
+      <x:c r="H333" t="str"/>
+      <x:c r="I333" t="str"/>
+      <x:c r="J333" t="str">
+        <x:v>Parent of Royal Caribbean International, Celebrity Cruises and Silversea.</x:v>
+      </x:c>
+      <x:c r="K333" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L333" t="str">
+        <x:v>SRC133_003</x:v>
+      </x:c>
+      <x:c r="M333" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="334">
+      <x:c r="A334" t="str">
+        <x:v>COMP_ROYAL_CARIBBEAN_INTL</x:v>
+      </x:c>
+      <x:c r="B334" t="str">
+        <x:v>Royal Caribbean International</x:v>
+      </x:c>
+      <x:c r="C334" t="str">
+        <x:v>Cruise line</x:v>
+      </x:c>
+      <x:c r="D334" t="str">
+        <x:v>Miami</x:v>
+      </x:c>
+      <x:c r="E334" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="F334" t="str">
+        <x:v>Royal Caribbean Group</x:v>
+      </x:c>
+      <x:c r="G334" t="str">
+        <x:v>Ocean cruise; private destinations</x:v>
+      </x:c>
+      <x:c r="H334" t="str"/>
+      <x:c r="I334" t="str"/>
+      <x:c r="J334" t="str">
+        <x:v>Large-ship global cruise brand with major Caribbean deployment.</x:v>
+      </x:c>
+      <x:c r="K334" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L334" t="str">
+        <x:v>SRC133_007</x:v>
+      </x:c>
+      <x:c r="M334" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="335">
+      <x:c r="A335" t="str">
+        <x:v>COMP_CELEBRITY_CRUISES</x:v>
+      </x:c>
+      <x:c r="B335" t="str">
+        <x:v>Celebrity Cruises</x:v>
+      </x:c>
+      <x:c r="C335" t="str">
+        <x:v>Cruise line</x:v>
+      </x:c>
+      <x:c r="D335" t="str">
+        <x:v>Miami</x:v>
+      </x:c>
+      <x:c r="E335" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="F335" t="str">
+        <x:v>Royal Caribbean Group</x:v>
+      </x:c>
+      <x:c r="G335" t="str">
+        <x:v>Premium ocean cruise</x:v>
+      </x:c>
+      <x:c r="H335" t="str"/>
+      <x:c r="I335" t="str"/>
+      <x:c r="J335" t="str">
+        <x:v>Premium cruise brand.</x:v>
+      </x:c>
+      <x:c r="K335" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L335" t="str">
+        <x:v>SRC133_003</x:v>
+      </x:c>
+      <x:c r="M335" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="336">
+      <x:c r="A336" t="str">
+        <x:v>COMP_SILVERSEA</x:v>
+      </x:c>
+      <x:c r="B336" t="str">
+        <x:v>Silversea Cruises</x:v>
+      </x:c>
+      <x:c r="C336" t="str">
+        <x:v>Cruise line</x:v>
+      </x:c>
+      <x:c r="D336" t="str">
+        <x:v>Monaco</x:v>
+      </x:c>
+      <x:c r="E336" t="str">
+        <x:v>Monaco</x:v>
+      </x:c>
+      <x:c r="F336" t="str">
+        <x:v>Royal Caribbean Group</x:v>
+      </x:c>
+      <x:c r="G336" t="str">
+        <x:v>Luxury and expedition cruise</x:v>
+      </x:c>
+      <x:c r="H336" t="str"/>
+      <x:c r="I336" t="str"/>
+      <x:c r="J336" t="str">
+        <x:v>Luxury and expedition cruise brand.</x:v>
+      </x:c>
+      <x:c r="K336" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L336" t="str">
+        <x:v>SRC133_003</x:v>
+      </x:c>
+      <x:c r="M336" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="337">
+      <x:c r="A337" t="str">
+        <x:v>COMP_CARNIVAL_CORP</x:v>
+      </x:c>
+      <x:c r="B337" t="str">
+        <x:v>Carnival Corporation &amp; plc</x:v>
+      </x:c>
+      <x:c r="C337" t="str">
+        <x:v>Cruise group</x:v>
+      </x:c>
+      <x:c r="D337" t="str">
+        <x:v>Miami</x:v>
+      </x:c>
+      <x:c r="E337" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="F337" t="str">
+        <x:v>Public company</x:v>
+      </x:c>
+      <x:c r="G337" t="str">
+        <x:v>Cruise lines; private destinations</x:v>
+      </x:c>
+      <x:c r="H337" t="str"/>
+      <x:c r="I337" t="str"/>
+      <x:c r="J337" t="str">
+        <x:v>Multi-brand cruise group.</x:v>
+      </x:c>
+      <x:c r="K337" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L337" t="str">
+        <x:v>SRC133_003</x:v>
+      </x:c>
+      <x:c r="M337" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="338">
+      <x:c r="A338" t="str">
+        <x:v>COMP_CARNIVAL_CRUISE</x:v>
+      </x:c>
+      <x:c r="B338" t="str">
+        <x:v>Carnival Cruise Line</x:v>
+      </x:c>
+      <x:c r="C338" t="str">
+        <x:v>Cruise line</x:v>
+      </x:c>
+      <x:c r="D338" t="str">
+        <x:v>Miami</x:v>
+      </x:c>
+      <x:c r="E338" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="F338" t="str">
+        <x:v>Carnival Corporation &amp; plc</x:v>
+      </x:c>
+      <x:c r="G338" t="str">
+        <x:v>Contemporary ocean cruise</x:v>
+      </x:c>
+      <x:c r="H338" t="str"/>
+      <x:c r="I338" t="str"/>
+      <x:c r="J338" t="str">
+        <x:v>Caribbean-focused mass-market cruise brand.</x:v>
+      </x:c>
+      <x:c r="K338" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L338" t="str">
+        <x:v>SRC133_008</x:v>
+      </x:c>
+      <x:c r="M338" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="339">
+      <x:c r="A339" t="str">
+        <x:v>COMP_PRINCESS_CRUISES</x:v>
+      </x:c>
+      <x:c r="B339" t="str">
+        <x:v>Princess Cruises</x:v>
+      </x:c>
+      <x:c r="C339" t="str">
+        <x:v>Cruise line</x:v>
+      </x:c>
+      <x:c r="D339" t="str">
+        <x:v>Santa Clarita</x:v>
+      </x:c>
+      <x:c r="E339" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="F339" t="str">
+        <x:v>Carnival Corporation &amp; plc</x:v>
+      </x:c>
+      <x:c r="G339" t="str">
+        <x:v>Premium ocean cruise</x:v>
+      </x:c>
+      <x:c r="H339" t="str"/>
+      <x:c r="I339" t="str"/>
+      <x:c r="J339" t="str">
+        <x:v>Global premium cruise brand.</x:v>
+      </x:c>
+      <x:c r="K339" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L339" t="str">
+        <x:v>SRC133_003</x:v>
+      </x:c>
+      <x:c r="M339" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="340">
+      <x:c r="A340" t="str">
+        <x:v>COMP_HOLLAND_AMERICA</x:v>
+      </x:c>
+      <x:c r="B340" t="str">
+        <x:v>Holland America Line</x:v>
+      </x:c>
+      <x:c r="C340" t="str">
+        <x:v>Cruise line</x:v>
+      </x:c>
+      <x:c r="D340" t="str">
+        <x:v>Seattle</x:v>
+      </x:c>
+      <x:c r="E340" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="F340" t="str">
+        <x:v>Carnival Corporation &amp; plc</x:v>
+      </x:c>
+      <x:c r="G340" t="str">
+        <x:v>Premium ocean and Alaska cruise</x:v>
+      </x:c>
+      <x:c r="H340" t="str"/>
+      <x:c r="I340" t="str"/>
+      <x:c r="J340" t="str">
+        <x:v>Alaska, Caribbean and global deployment.</x:v>
+      </x:c>
+      <x:c r="K340" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L340" t="str">
+        <x:v>SRC133_003</x:v>
+      </x:c>
+      <x:c r="M340" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="341">
+      <x:c r="A341" t="str">
+        <x:v>COMP_NCLH</x:v>
+      </x:c>
+      <x:c r="B341" t="str">
+        <x:v>Norwegian Cruise Line Holdings</x:v>
+      </x:c>
+      <x:c r="C341" t="str">
+        <x:v>Cruise group</x:v>
+      </x:c>
+      <x:c r="D341" t="str">
+        <x:v>Miami</x:v>
+      </x:c>
+      <x:c r="E341" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="F341" t="str">
+        <x:v>Public company</x:v>
+      </x:c>
+      <x:c r="G341" t="str">
+        <x:v>Cruise lines; private destinations</x:v>
+      </x:c>
+      <x:c r="H341" t="str"/>
+      <x:c r="I341" t="str"/>
+      <x:c r="J341" t="str">
+        <x:v>Parent of Norwegian Cruise Line, Oceania Cruises and Regent Seven Seas Cruises.</x:v>
+      </x:c>
+      <x:c r="K341" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L341" t="str">
+        <x:v>SRC133_003</x:v>
+      </x:c>
+      <x:c r="M341" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="342">
+      <x:c r="A342" t="str">
+        <x:v>COMP_NCL</x:v>
+      </x:c>
+      <x:c r="B342" t="str">
+        <x:v>Norwegian Cruise Line</x:v>
+      </x:c>
+      <x:c r="C342" t="str">
+        <x:v>Cruise line</x:v>
+      </x:c>
+      <x:c r="D342" t="str">
+        <x:v>Miami</x:v>
+      </x:c>
+      <x:c r="E342" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="F342" t="str">
+        <x:v>Norwegian Cruise Line Holdings</x:v>
+      </x:c>
+      <x:c r="G342" t="str">
+        <x:v>Ocean cruise; private destinations</x:v>
+      </x:c>
+      <x:c r="H342" t="str"/>
+      <x:c r="I342" t="str"/>
+      <x:c r="J342" t="str">
+        <x:v>Global cruise brand with Caribbean private-destination exposure.</x:v>
+      </x:c>
+      <x:c r="K342" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L342" t="str">
+        <x:v>SRC133_009</x:v>
+      </x:c>
+      <x:c r="M342" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="343">
+      <x:c r="A343" t="str">
+        <x:v>COMP_OCEANIA</x:v>
+      </x:c>
+      <x:c r="B343" t="str">
+        <x:v>Oceania Cruises</x:v>
+      </x:c>
+      <x:c r="C343" t="str">
+        <x:v>Cruise line</x:v>
+      </x:c>
+      <x:c r="D343" t="str">
+        <x:v>Miami</x:v>
+      </x:c>
+      <x:c r="E343" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="F343" t="str">
+        <x:v>Norwegian Cruise Line Holdings</x:v>
+      </x:c>
+      <x:c r="G343" t="str">
+        <x:v>Upper-premium ocean cruise</x:v>
+      </x:c>
+      <x:c r="H343" t="str"/>
+      <x:c r="I343" t="str"/>
+      <x:c r="J343" t="str">
+        <x:v>Destination-focused upper-premium cruise brand.</x:v>
+      </x:c>
+      <x:c r="K343" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L343" t="str">
+        <x:v>SRC133_003</x:v>
+      </x:c>
+      <x:c r="M343" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="344">
+      <x:c r="A344" t="str">
+        <x:v>COMP_REGENT_SEVEN_SEAS</x:v>
+      </x:c>
+      <x:c r="B344" t="str">
+        <x:v>Regent Seven Seas Cruises</x:v>
+      </x:c>
+      <x:c r="C344" t="str">
+        <x:v>Cruise line</x:v>
+      </x:c>
+      <x:c r="D344" t="str">
+        <x:v>Miami</x:v>
+      </x:c>
+      <x:c r="E344" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="F344" t="str">
+        <x:v>Norwegian Cruise Line Holdings</x:v>
+      </x:c>
+      <x:c r="G344" t="str">
+        <x:v>Luxury ocean cruise</x:v>
+      </x:c>
+      <x:c r="H344" t="str"/>
+      <x:c r="I344" t="str"/>
+      <x:c r="J344" t="str">
+        <x:v>Luxury all-inclusive cruise brand.</x:v>
+      </x:c>
+      <x:c r="K344" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L344" t="str">
+        <x:v>SRC133_003</x:v>
+      </x:c>
+      <x:c r="M344" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="345">
+      <x:c r="A345" t="str">
+        <x:v>COMP_DISNEY_CRUISE</x:v>
+      </x:c>
+      <x:c r="B345" t="str">
+        <x:v>Disney Cruise Line</x:v>
+      </x:c>
+      <x:c r="C345" t="str">
+        <x:v>Cruise line</x:v>
+      </x:c>
+      <x:c r="D345" t="str">
+        <x:v>Celebration</x:v>
+      </x:c>
+      <x:c r="E345" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="F345" t="str">
+        <x:v>The Walt Disney Company</x:v>
+      </x:c>
+      <x:c r="G345" t="str">
+        <x:v>Family ocean cruise; private destinations</x:v>
+      </x:c>
+      <x:c r="H345" t="str"/>
+      <x:c r="I345" t="str"/>
+      <x:c r="J345" t="str">
+        <x:v>Operates Castaway Cay and Lookout Cay calls.</x:v>
+      </x:c>
+      <x:c r="K345" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L345" t="str">
+        <x:v>SRC133_010</x:v>
+      </x:c>
+      <x:c r="M345" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="346">
+      <x:c r="A346" t="str">
+        <x:v>COMP_VIRGIN_VOYAGES</x:v>
+      </x:c>
+      <x:c r="B346" t="str">
+        <x:v>Virgin Voyages</x:v>
+      </x:c>
+      <x:c r="C346" t="str">
+        <x:v>Cruise line</x:v>
+      </x:c>
+      <x:c r="D346" t="str">
+        <x:v>Plantation</x:v>
+      </x:c>
+      <x:c r="E346" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="F346" t="str">
+        <x:v>Private</x:v>
+      </x:c>
+      <x:c r="G346" t="str">
+        <x:v>Adults-only ocean cruise; partner beach club</x:v>
+      </x:c>
+      <x:c r="H346" t="str"/>
+      <x:c r="I346" t="str"/>
+      <x:c r="J346" t="str">
+        <x:v>Caribbean and Mediterranean deployment.</x:v>
+      </x:c>
+      <x:c r="K346" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L346" t="str">
+        <x:v>SRC133_003</x:v>
+      </x:c>
+      <x:c r="M346" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="347">
+      <x:c r="A347" t="str">
+        <x:v>ORG_NISGAA_NATION</x:v>
+      </x:c>
+      <x:c r="B347" t="str">
+        <x:v>Nisg̱a'a Nation</x:v>
+      </x:c>
+      <x:c r="C347" t="str">
+        <x:v>Indigenous government</x:v>
+      </x:c>
+      <x:c r="D347" t="str"/>
+      <x:c r="E347" t="str">
+        <x:v>Canada</x:v>
+      </x:c>
+      <x:c r="F347" t="str">
+        <x:v>Self-government</x:v>
+      </x:c>
+      <x:c r="G347" t="str">
+        <x:v>Government; economic development</x:v>
+      </x:c>
+      <x:c r="H347" t="str"/>
+      <x:c r="I347" t="str"/>
+      <x:c r="J347" t="str">
+        <x:v>Named participant in the reported Stewart port opening.</x:v>
+      </x:c>
+      <x:c r="K347" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L347" t="str">
+        <x:v>SRC133_002</x:v>
+      </x:c>
+      <x:c r="M347" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="348">
+      <x:c r="A348" t="str">
+        <x:v>ORG_TAHLTAN_NATION</x:v>
+      </x:c>
+      <x:c r="B348" t="str">
+        <x:v>Tahltan Nation</x:v>
+      </x:c>
+      <x:c r="C348" t="str">
+        <x:v>Indigenous nation</x:v>
+      </x:c>
+      <x:c r="D348" t="str"/>
+      <x:c r="E348" t="str">
+        <x:v>Canada</x:v>
+      </x:c>
+      <x:c r="F348" t="str">
+        <x:v>Indigenous nation</x:v>
+      </x:c>
+      <x:c r="G348" t="str">
+        <x:v>Government; economic development</x:v>
+      </x:c>
+      <x:c r="H348" t="str"/>
+      <x:c r="I348" t="str"/>
+      <x:c r="J348" t="str">
+        <x:v>Named participant in the reported Stewart port opening.</x:v>
+      </x:c>
+      <x:c r="K348" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L348" t="str">
+        <x:v>SRC133_002</x:v>
+      </x:c>
+      <x:c r="M348" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -50239,6 +50973,384 @@
       </x:c>
       <x:c r="E1900"/>
       <x:c r="F1900" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1901">
+      <x:c r="A1901" t="str">
+        <x:v>COMP_PENINSULA</x:v>
+      </x:c>
+      <x:c r="B1901" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1901" t="str">
+        <x:v>Peninsula</x:v>
+      </x:c>
+      <x:c r="D1901" t="str">
+        <x:v>Gibraltar</x:v>
+      </x:c>
+      <x:c r="E1901" t="str"/>
+      <x:c r="F1901" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1902">
+      <x:c r="A1902" t="str">
+        <x:v>COMP_HERCULES_TANKER</x:v>
+      </x:c>
+      <x:c r="B1902" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1902" t="str">
+        <x:v>Hercules Tanker Management</x:v>
+      </x:c>
+      <x:c r="D1902" t="str">
+        <x:v>Gibraltar</x:v>
+      </x:c>
+      <x:c r="E1902" t="str"/>
+      <x:c r="F1902" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1903">
+      <x:c r="A1903" t="str">
+        <x:v>COMP_SAFEEN_MARINE</x:v>
+      </x:c>
+      <x:c r="B1903" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1903" t="str">
+        <x:v>SAFEEN Marine Services</x:v>
+      </x:c>
+      <x:c r="D1903" t="str">
+        <x:v>United Arab Emirates</x:v>
+      </x:c>
+      <x:c r="E1903" t="str"/>
+      <x:c r="F1903" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1904">
+      <x:c r="A1904" t="str">
+        <x:v>COMP_SAFEEN_OFFSHORE</x:v>
+      </x:c>
+      <x:c r="B1904" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1904" t="str">
+        <x:v>SAFEEN Offshore</x:v>
+      </x:c>
+      <x:c r="D1904" t="str">
+        <x:v>United Arab Emirates</x:v>
+      </x:c>
+      <x:c r="E1904" t="str"/>
+      <x:c r="F1904" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1905">
+      <x:c r="A1905" t="str">
+        <x:v>COMP_ROYAL_CARIBBEAN_GROUP</x:v>
+      </x:c>
+      <x:c r="B1905" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1905" t="str">
+        <x:v>Royal Caribbean Group</x:v>
+      </x:c>
+      <x:c r="D1905" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="E1905" t="str"/>
+      <x:c r="F1905" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1906">
+      <x:c r="A1906" t="str">
+        <x:v>COMP_ROYAL_CARIBBEAN_INTL</x:v>
+      </x:c>
+      <x:c r="B1906" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1906" t="str">
+        <x:v>Royal Caribbean International</x:v>
+      </x:c>
+      <x:c r="D1906" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="E1906" t="str"/>
+      <x:c r="F1906" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1907">
+      <x:c r="A1907" t="str">
+        <x:v>COMP_CELEBRITY_CRUISES</x:v>
+      </x:c>
+      <x:c r="B1907" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1907" t="str">
+        <x:v>Celebrity Cruises</x:v>
+      </x:c>
+      <x:c r="D1907" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="E1907" t="str"/>
+      <x:c r="F1907" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1908">
+      <x:c r="A1908" t="str">
+        <x:v>COMP_SILVERSEA</x:v>
+      </x:c>
+      <x:c r="B1908" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1908" t="str">
+        <x:v>Silversea Cruises</x:v>
+      </x:c>
+      <x:c r="D1908" t="str">
+        <x:v>Monaco</x:v>
+      </x:c>
+      <x:c r="E1908" t="str"/>
+      <x:c r="F1908" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1909">
+      <x:c r="A1909" t="str">
+        <x:v>COMP_CARNIVAL_CORP</x:v>
+      </x:c>
+      <x:c r="B1909" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1909" t="str">
+        <x:v>Carnival Corporation &amp; plc</x:v>
+      </x:c>
+      <x:c r="D1909" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="E1909" t="str"/>
+      <x:c r="F1909" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1910">
+      <x:c r="A1910" t="str">
+        <x:v>COMP_CARNIVAL_CRUISE</x:v>
+      </x:c>
+      <x:c r="B1910" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1910" t="str">
+        <x:v>Carnival Cruise Line</x:v>
+      </x:c>
+      <x:c r="D1910" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="E1910" t="str"/>
+      <x:c r="F1910" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1911">
+      <x:c r="A1911" t="str">
+        <x:v>COMP_PRINCESS_CRUISES</x:v>
+      </x:c>
+      <x:c r="B1911" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1911" t="str">
+        <x:v>Princess Cruises</x:v>
+      </x:c>
+      <x:c r="D1911" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="E1911" t="str"/>
+      <x:c r="F1911" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1912">
+      <x:c r="A1912" t="str">
+        <x:v>COMP_HOLLAND_AMERICA</x:v>
+      </x:c>
+      <x:c r="B1912" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1912" t="str">
+        <x:v>Holland America Line</x:v>
+      </x:c>
+      <x:c r="D1912" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="E1912" t="str"/>
+      <x:c r="F1912" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1913">
+      <x:c r="A1913" t="str">
+        <x:v>COMP_NCLH</x:v>
+      </x:c>
+      <x:c r="B1913" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1913" t="str">
+        <x:v>Norwegian Cruise Line Holdings</x:v>
+      </x:c>
+      <x:c r="D1913" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="E1913" t="str"/>
+      <x:c r="F1913" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1914">
+      <x:c r="A1914" t="str">
+        <x:v>COMP_NCL</x:v>
+      </x:c>
+      <x:c r="B1914" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1914" t="str">
+        <x:v>Norwegian Cruise Line</x:v>
+      </x:c>
+      <x:c r="D1914" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="E1914" t="str"/>
+      <x:c r="F1914" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1915">
+      <x:c r="A1915" t="str">
+        <x:v>COMP_OCEANIA</x:v>
+      </x:c>
+      <x:c r="B1915" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1915" t="str">
+        <x:v>Oceania Cruises</x:v>
+      </x:c>
+      <x:c r="D1915" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="E1915" t="str"/>
+      <x:c r="F1915" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1916">
+      <x:c r="A1916" t="str">
+        <x:v>COMP_REGENT_SEVEN_SEAS</x:v>
+      </x:c>
+      <x:c r="B1916" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1916" t="str">
+        <x:v>Regent Seven Seas Cruises</x:v>
+      </x:c>
+      <x:c r="D1916" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="E1916" t="str"/>
+      <x:c r="F1916" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1917">
+      <x:c r="A1917" t="str">
+        <x:v>COMP_DISNEY_CRUISE</x:v>
+      </x:c>
+      <x:c r="B1917" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1917" t="str">
+        <x:v>Disney Cruise Line</x:v>
+      </x:c>
+      <x:c r="D1917" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="E1917" t="str"/>
+      <x:c r="F1917" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1918">
+      <x:c r="A1918" t="str">
+        <x:v>COMP_VIRGIN_VOYAGES</x:v>
+      </x:c>
+      <x:c r="B1918" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1918" t="str">
+        <x:v>Virgin Voyages</x:v>
+      </x:c>
+      <x:c r="D1918" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="E1918" t="str"/>
+      <x:c r="F1918" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1919">
+      <x:c r="A1919" t="str">
+        <x:v>ORG_NISGAA_NATION</x:v>
+      </x:c>
+      <x:c r="B1919" t="str">
+        <x:v>Organization</x:v>
+      </x:c>
+      <x:c r="C1919" t="str">
+        <x:v>Nisg̱a'a Nation</x:v>
+      </x:c>
+      <x:c r="D1919" t="str">
+        <x:v>Canada</x:v>
+      </x:c>
+      <x:c r="E1919" t="str"/>
+      <x:c r="F1919" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1920">
+      <x:c r="A1920" t="str">
+        <x:v>ORG_TAHLTAN_NATION</x:v>
+      </x:c>
+      <x:c r="B1920" t="str">
+        <x:v>Organization</x:v>
+      </x:c>
+      <x:c r="C1920" t="str">
+        <x:v>Tahltan Nation</x:v>
+      </x:c>
+      <x:c r="D1920" t="str">
+        <x:v>Canada</x:v>
+      </x:c>
+      <x:c r="E1920" t="str"/>
+      <x:c r="F1920" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1921">
+      <x:c r="A1921" t="str">
+        <x:v>PORT_STEWART_BC</x:v>
+      </x:c>
+      <x:c r="B1921" t="str">
+        <x:v>Port</x:v>
+      </x:c>
+      <x:c r="C1921" t="str">
+        <x:v>Port of Stewart</x:v>
+      </x:c>
+      <x:c r="D1921" t="str">
+        <x:v>Canada</x:v>
+      </x:c>
+      <x:c r="E1921" t="str"/>
+      <x:c r="F1921" t="str">
         <x:v>Active</x:v>
       </x:c>
     </x:row>
@@ -54476,6 +55588,374 @@
       </x:c>
       <x:c r="G183" t="str">
         <x:v>SRC132_004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="184">
+      <x:c r="A184" t="str">
+        <x:v>REL133_001</x:v>
+      </x:c>
+      <x:c r="B184" t="str">
+        <x:v>COMP_SAFEEN_MARINE</x:v>
+      </x:c>
+      <x:c r="C184" t="str">
+        <x:v>PART_OF</x:v>
+      </x:c>
+      <x:c r="D184" t="str">
+        <x:v>COMP_ADPORTS</x:v>
+      </x:c>
+      <x:c r="E184" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="F184" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G184" t="str">
+        <x:v>SRC133_006</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="185">
+      <x:c r="A185" t="str">
+        <x:v>REL133_002</x:v>
+      </x:c>
+      <x:c r="B185" t="str">
+        <x:v>COMP_SAFEEN_OFFSHORE</x:v>
+      </x:c>
+      <x:c r="C185" t="str">
+        <x:v>PART_OF</x:v>
+      </x:c>
+      <x:c r="D185" t="str">
+        <x:v>COMP_ADPORTS</x:v>
+      </x:c>
+      <x:c r="E185" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="F185" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G185" t="str">
+        <x:v>SRC133_004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="186">
+      <x:c r="A186" t="str">
+        <x:v>REL133_003</x:v>
+      </x:c>
+      <x:c r="B186" t="str">
+        <x:v>COMP_SAFEEN_MARINE</x:v>
+      </x:c>
+      <x:c r="C186" t="str">
+        <x:v>GROUP_ECOSYSTEM_LINK</x:v>
+      </x:c>
+      <x:c r="D186" t="str">
+        <x:v>COMP_NOATUM_MARITIME</x:v>
+      </x:c>
+      <x:c r="E186" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="F186" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G186" t="str">
+        <x:v>SRC133_006</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="187">
+      <x:c r="A187" t="str">
+        <x:v>REL133_004</x:v>
+      </x:c>
+      <x:c r="B187" t="str">
+        <x:v>COMP_SAFEEN_OFFSHORE</x:v>
+      </x:c>
+      <x:c r="C187" t="str">
+        <x:v>GROUP_ECOSYSTEM_LINK</x:v>
+      </x:c>
+      <x:c r="D187" t="str">
+        <x:v>COMP_NOATUM_MARITIME</x:v>
+      </x:c>
+      <x:c r="E187" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="F187" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G187" t="str">
+        <x:v>SRC133_004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="188">
+      <x:c r="A188" t="str">
+        <x:v>REL133_005</x:v>
+      </x:c>
+      <x:c r="B188" t="str">
+        <x:v>COMP_HERCULES_TANKER</x:v>
+      </x:c>
+      <x:c r="C188" t="str">
+        <x:v>SISTER_COMPANY_OF</x:v>
+      </x:c>
+      <x:c r="D188" t="str">
+        <x:v>COMP_PENINSULA</x:v>
+      </x:c>
+      <x:c r="E188" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F188" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G188" t="str">
+        <x:v>SRC133_001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="189">
+      <x:c r="A189" t="str">
+        <x:v>REL133_006</x:v>
+      </x:c>
+      <x:c r="B189" t="str">
+        <x:v>COMP_ROYAL_CARIBBEAN_INTL</x:v>
+      </x:c>
+      <x:c r="C189" t="str">
+        <x:v>BRAND_OF</x:v>
+      </x:c>
+      <x:c r="D189" t="str">
+        <x:v>COMP_ROYAL_CARIBBEAN_GROUP</x:v>
+      </x:c>
+      <x:c r="E189" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="F189" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G189" t="str">
+        <x:v>SRC133_003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="190">
+      <x:c r="A190" t="str">
+        <x:v>REL133_007</x:v>
+      </x:c>
+      <x:c r="B190" t="str">
+        <x:v>COMP_CELEBRITY_CRUISES</x:v>
+      </x:c>
+      <x:c r="C190" t="str">
+        <x:v>BRAND_OF</x:v>
+      </x:c>
+      <x:c r="D190" t="str">
+        <x:v>COMP_ROYAL_CARIBBEAN_GROUP</x:v>
+      </x:c>
+      <x:c r="E190" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="F190" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G190" t="str">
+        <x:v>SRC133_003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="191">
+      <x:c r="A191" t="str">
+        <x:v>REL133_008</x:v>
+      </x:c>
+      <x:c r="B191" t="str">
+        <x:v>COMP_SILVERSEA</x:v>
+      </x:c>
+      <x:c r="C191" t="str">
+        <x:v>BRAND_OF</x:v>
+      </x:c>
+      <x:c r="D191" t="str">
+        <x:v>COMP_ROYAL_CARIBBEAN_GROUP</x:v>
+      </x:c>
+      <x:c r="E191" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="F191" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G191" t="str">
+        <x:v>SRC133_003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="192">
+      <x:c r="A192" t="str">
+        <x:v>REL133_009</x:v>
+      </x:c>
+      <x:c r="B192" t="str">
+        <x:v>COMP_CARNIVAL_CRUISE</x:v>
+      </x:c>
+      <x:c r="C192" t="str">
+        <x:v>BRAND_OF</x:v>
+      </x:c>
+      <x:c r="D192" t="str">
+        <x:v>COMP_CARNIVAL_CORP</x:v>
+      </x:c>
+      <x:c r="E192" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="F192" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G192" t="str">
+        <x:v>SRC133_003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="193">
+      <x:c r="A193" t="str">
+        <x:v>REL133_010</x:v>
+      </x:c>
+      <x:c r="B193" t="str">
+        <x:v>COMP_PRINCESS_CRUISES</x:v>
+      </x:c>
+      <x:c r="C193" t="str">
+        <x:v>BRAND_OF</x:v>
+      </x:c>
+      <x:c r="D193" t="str">
+        <x:v>COMP_CARNIVAL_CORP</x:v>
+      </x:c>
+      <x:c r="E193" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="F193" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G193" t="str">
+        <x:v>SRC133_003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="194">
+      <x:c r="A194" t="str">
+        <x:v>REL133_011</x:v>
+      </x:c>
+      <x:c r="B194" t="str">
+        <x:v>COMP_HOLLAND_AMERICA</x:v>
+      </x:c>
+      <x:c r="C194" t="str">
+        <x:v>BRAND_OF</x:v>
+      </x:c>
+      <x:c r="D194" t="str">
+        <x:v>COMP_CARNIVAL_CORP</x:v>
+      </x:c>
+      <x:c r="E194" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="F194" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G194" t="str">
+        <x:v>SRC133_003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="195">
+      <x:c r="A195" t="str">
+        <x:v>REL133_012</x:v>
+      </x:c>
+      <x:c r="B195" t="str">
+        <x:v>COMP_NCL</x:v>
+      </x:c>
+      <x:c r="C195" t="str">
+        <x:v>BRAND_OF</x:v>
+      </x:c>
+      <x:c r="D195" t="str">
+        <x:v>COMP_NCLH</x:v>
+      </x:c>
+      <x:c r="E195" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="F195" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G195" t="str">
+        <x:v>SRC133_003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="196">
+      <x:c r="A196" t="str">
+        <x:v>REL133_013</x:v>
+      </x:c>
+      <x:c r="B196" t="str">
+        <x:v>COMP_OCEANIA</x:v>
+      </x:c>
+      <x:c r="C196" t="str">
+        <x:v>BRAND_OF</x:v>
+      </x:c>
+      <x:c r="D196" t="str">
+        <x:v>COMP_NCLH</x:v>
+      </x:c>
+      <x:c r="E196" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="F196" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G196" t="str">
+        <x:v>SRC133_003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="197">
+      <x:c r="A197" t="str">
+        <x:v>REL133_014</x:v>
+      </x:c>
+      <x:c r="B197" t="str">
+        <x:v>COMP_REGENT_SEVEN_SEAS</x:v>
+      </x:c>
+      <x:c r="C197" t="str">
+        <x:v>BRAND_OF</x:v>
+      </x:c>
+      <x:c r="D197" t="str">
+        <x:v>COMP_NCLH</x:v>
+      </x:c>
+      <x:c r="E197" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="F197" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G197" t="str">
+        <x:v>SRC133_003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="198">
+      <x:c r="A198" t="str">
+        <x:v>REL133_015</x:v>
+      </x:c>
+      <x:c r="B198" t="str">
+        <x:v>ORG_NISGAA_NATION</x:v>
+      </x:c>
+      <x:c r="C198" t="str">
+        <x:v>PORT_OPENING_PARTICIPANT</x:v>
+      </x:c>
+      <x:c r="D198" t="str">
+        <x:v>PORT_STEWART_BC</x:v>
+      </x:c>
+      <x:c r="E198" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="F198" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="G198" t="str">
+        <x:v>SRC133_002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="199">
+      <x:c r="A199" t="str">
+        <x:v>REL133_016</x:v>
+      </x:c>
+      <x:c r="B199" t="str">
+        <x:v>ORG_TAHLTAN_NATION</x:v>
+      </x:c>
+      <x:c r="C199" t="str">
+        <x:v>PORT_OPENING_PARTICIPANT</x:v>
+      </x:c>
+      <x:c r="D199" t="str">
+        <x:v>PORT_STEWART_BC</x:v>
+      </x:c>
+      <x:c r="E199" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="F199" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="G199" t="str">
+        <x:v>SRC133_002</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/data/01_core_entities.xlsx
+++ b/data/01_core_entities.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R627e106700f04014"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Companies" sheetId="2" r:id="R11a5ce07f2e542be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Entity Registry" sheetId="3" r:id="R64a8ae53029e482f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="Rc98128ea385c4cca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company System Footprints" sheetId="5" r:id="R2bf7983dabeb4273"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="People" sheetId="6" r:id="Ra06f0f7fd4294e3a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leadership Roles" sheetId="7" r:id="R61052d6f2aff4026"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Dictionary" sheetId="8" r:id="Re4b7b49a94d74484"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runtime Table Crosswalk" sheetId="9" r:id="Rebc31a6bf8f04427"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Queue" sheetId="10" r:id="R4a565c8175164648"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="Rb37989def82644bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Companies" sheetId="2" r:id="R184c1459c4644c19"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Entity Registry" sheetId="3" r:id="R33bea03a7e634286"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="R62e0ee1a7d5143aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company System Footprints" sheetId="5" r:id="Rfe9f2373fc6d41ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="People" sheetId="6" r:id="Ra07bd309a50144a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leadership Roles" sheetId="7" r:id="R952835cb2e3f4268"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Dictionary" sheetId="8" r:id="Rbd831b4914a44535"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runtime Table Crosswalk" sheetId="9" r:id="Rbc72b67751034869"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Queue" sheetId="10" r:id="R11323fac5c4147e1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -15279,6 +15279,298 @@
         <x:v>2026-09-10</x:v>
       </x:c>
     </x:row>
+    <x:row r="349">
+      <x:c r="A349" t="str">
+        <x:v>COMP_HUNTER_GROUP</x:v>
+      </x:c>
+      <x:c r="B349" t="str">
+        <x:v>Hunter Group ASA</x:v>
+      </x:c>
+      <x:c r="C349" t="str">
+        <x:v>Tanker company</x:v>
+      </x:c>
+      <x:c r="D349" t="str">
+        <x:v>Oslo</x:v>
+      </x:c>
+      <x:c r="E349" t="str">
+        <x:v>Norway</x:v>
+      </x:c>
+      <x:c r="F349" t="str">
+        <x:v>Public company</x:v>
+      </x:c>
+      <x:c r="G349" t="str">
+        <x:v>Crude-oil tanker exposure; chartering and rate economics</x:v>
+      </x:c>
+      <x:c r="H349" t="str"/>
+      <x:c r="I349" t="str"/>
+      <x:c r="J349" t="str">
+        <x:v>Rate-dispute claimant; current fleet and ownership detail queued for verification.</x:v>
+      </x:c>
+      <x:c r="K349" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L349" t="str">
+        <x:v>SRC134_003</x:v>
+      </x:c>
+      <x:c r="M349" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="350">
+      <x:c r="A350" t="str">
+        <x:v>COMP_MERCURIA</x:v>
+      </x:c>
+      <x:c r="B350" t="str">
+        <x:v>Mercuria Energy Group</x:v>
+      </x:c>
+      <x:c r="C350" t="str">
+        <x:v>Commodity trading company</x:v>
+      </x:c>
+      <x:c r="D350" t="str">
+        <x:v>Geneva</x:v>
+      </x:c>
+      <x:c r="E350" t="str">
+        <x:v>Switzerland</x:v>
+      </x:c>
+      <x:c r="F350" t="str">
+        <x:v>Private</x:v>
+      </x:c>
+      <x:c r="G350" t="str">
+        <x:v>Energy trading; shipping; commodities</x:v>
+      </x:c>
+      <x:c r="H350" t="str"/>
+      <x:c r="I350" t="str"/>
+      <x:c r="J350" t="str">
+        <x:v>Reported in earlier Hunter disclosure as counterparty; current article does not independently name the customer.</x:v>
+      </x:c>
+      <x:c r="K350" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L350" t="str">
+        <x:v>SRC134_003</x:v>
+      </x:c>
+      <x:c r="M350" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="351">
+      <x:c r="A351" t="str">
+        <x:v>COMP_MSC_SHIPMANAGEMENT</x:v>
+      </x:c>
+      <x:c r="B351" t="str">
+        <x:v>MSC Shipmanagement Limited</x:v>
+      </x:c>
+      <x:c r="C351" t="str">
+        <x:v>Ship management company</x:v>
+      </x:c>
+      <x:c r="D351" t="str">
+        <x:v>Limassol</x:v>
+      </x:c>
+      <x:c r="E351" t="str">
+        <x:v>Cyprus</x:v>
+      </x:c>
+      <x:c r="F351" t="str">
+        <x:v>MSC Group</x:v>
+      </x:c>
+      <x:c r="G351" t="str">
+        <x:v>Technical management; crewing; vessel operations</x:v>
+      </x:c>
+      <x:c r="H351" t="str"/>
+      <x:c r="I351" t="str"/>
+      <x:c r="J351" t="str">
+        <x:v>Defendant in MSC SAMIRA III oily-waste case.</x:v>
+      </x:c>
+      <x:c r="K351" t="str">
+        <x:v>Active / probation</x:v>
+      </x:c>
+      <x:c r="L351" t="str">
+        <x:v>SRC134_005</x:v>
+      </x:c>
+      <x:c r="M351" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="352">
+      <x:c r="A352" t="str">
+        <x:v>COMP_HONG_KONG_SPIRIT</x:v>
+      </x:c>
+      <x:c r="B352" t="str">
+        <x:v>Hong Kong Spirit Shipping and Trading Ltd</x:v>
+      </x:c>
+      <x:c r="C352" t="str">
+        <x:v>Shipowning company</x:v>
+      </x:c>
+      <x:c r="D352" t="str"/>
+      <x:c r="E352" t="str">
+        <x:v>Hong Kong</x:v>
+      </x:c>
+      <x:c r="F352" t="str">
+        <x:v>Private / MSC-linked vessel owner</x:v>
+      </x:c>
+      <x:c r="G352" t="str">
+        <x:v>Ship ownership</x:v>
+      </x:c>
+      <x:c r="H352" t="str"/>
+      <x:c r="I352" t="str"/>
+      <x:c r="J352" t="str">
+        <x:v>Owner of MSC SAMIRA III in reported U.S. pollution case.</x:v>
+      </x:c>
+      <x:c r="K352" t="str">
+        <x:v>Active / probation</x:v>
+      </x:c>
+      <x:c r="L352" t="str">
+        <x:v>SRC134_005</x:v>
+      </x:c>
+      <x:c r="M352" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="353">
+      <x:c r="A353" t="str">
+        <x:v>COMP_NOVATEK</x:v>
+      </x:c>
+      <x:c r="B353" t="str">
+        <x:v>PAO NOVATEK</x:v>
+      </x:c>
+      <x:c r="C353" t="str">
+        <x:v>Energy company</x:v>
+      </x:c>
+      <x:c r="D353" t="str">
+        <x:v>Tarko-Sale</x:v>
+      </x:c>
+      <x:c r="E353" t="str">
+        <x:v>Russia</x:v>
+      </x:c>
+      <x:c r="F353" t="str">
+        <x:v>Public company</x:v>
+      </x:c>
+      <x:c r="G353" t="str">
+        <x:v>Natural gas; LNG; Arctic energy infrastructure</x:v>
+      </x:c>
+      <x:c r="H353" t="str"/>
+      <x:c r="I353" t="str"/>
+      <x:c r="J353" t="str">
+        <x:v>Leads Arctic LNG 2 with a reported 60% interest.</x:v>
+      </x:c>
+      <x:c r="K353" t="str">
+        <x:v>Active / sanctions exposed</x:v>
+      </x:c>
+      <x:c r="L353" t="str">
+        <x:v>SRC134_008</x:v>
+      </x:c>
+      <x:c r="M353" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="354">
+      <x:c r="A354" t="str">
+        <x:v>COMP_ARCTIC_LNG2</x:v>
+      </x:c>
+      <x:c r="B354" t="str">
+        <x:v>Arctic LNG 2 LLC</x:v>
+      </x:c>
+      <x:c r="C354" t="str">
+        <x:v>LNG project company</x:v>
+      </x:c>
+      <x:c r="D354" t="str"/>
+      <x:c r="E354" t="str">
+        <x:v>Russia</x:v>
+      </x:c>
+      <x:c r="F354" t="str">
+        <x:v>NOVATEK-led consortium</x:v>
+      </x:c>
+      <x:c r="G354" t="str">
+        <x:v>LNG production; Arctic export project</x:v>
+      </x:c>
+      <x:c r="H354" t="str"/>
+      <x:c r="I354" t="str"/>
+      <x:c r="J354" t="str">
+        <x:v>Planned 19.8 million tonnes per year; deliveries complicated by sanctions.</x:v>
+      </x:c>
+      <x:c r="K354" t="str">
+        <x:v>Active / constrained</x:v>
+      </x:c>
+      <x:c r="L354" t="str">
+        <x:v>SRC134_008</x:v>
+      </x:c>
+      <x:c r="M354" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="355">
+      <x:c r="A355" t="str">
+        <x:v>COMP_HANWHA_OCEAN</x:v>
+      </x:c>
+      <x:c r="B355" t="str">
+        <x:v>Hanwha Ocean</x:v>
+      </x:c>
+      <x:c r="C355" t="str">
+        <x:v>Shipbuilder</x:v>
+      </x:c>
+      <x:c r="D355" t="str">
+        <x:v>Geoje</x:v>
+      </x:c>
+      <x:c r="E355" t="str">
+        <x:v>South Korea</x:v>
+      </x:c>
+      <x:c r="F355" t="str">
+        <x:v>Hanwha Group</x:v>
+      </x:c>
+      <x:c r="G355" t="str">
+        <x:v>Commercial and naval shipbuilding; offshore</x:v>
+      </x:c>
+      <x:c r="H355" t="str"/>
+      <x:c r="I355" t="str"/>
+      <x:c r="J355" t="str">
+        <x:v>Contract counterparty in Arctic LNG 2 Arc7 carrier dispute.</x:v>
+      </x:c>
+      <x:c r="K355" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L355" t="str">
+        <x:v>SRC134_008</x:v>
+      </x:c>
+      <x:c r="M355" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="356">
+      <x:c r="A356" t="str">
+        <x:v>COMP_SOVCOMFLOT</x:v>
+      </x:c>
+      <x:c r="B356" t="str">
+        <x:v>Sovcomflot</x:v>
+      </x:c>
+      <x:c r="C356" t="str">
+        <x:v>Shipping company</x:v>
+      </x:c>
+      <x:c r="D356" t="str">
+        <x:v>Saint Petersburg</x:v>
+      </x:c>
+      <x:c r="E356" t="str">
+        <x:v>Russia</x:v>
+      </x:c>
+      <x:c r="F356" t="str">
+        <x:v>Russian state controlled</x:v>
+      </x:c>
+      <x:c r="G356" t="str">
+        <x:v>Energy shipping; ice-class tankers; LNG carriers</x:v>
+      </x:c>
+      <x:c r="H356" t="str"/>
+      <x:c r="I356" t="str"/>
+      <x:c r="J356" t="str">
+        <x:v>Three Hanwha Arc7 LNG-carrier orders were reported canceled due to sanctions.</x:v>
+      </x:c>
+      <x:c r="K356" t="str">
+        <x:v>Active / sanctions exposed</x:v>
+      </x:c>
+      <x:c r="L356" t="str">
+        <x:v>SRC134_008</x:v>
+      </x:c>
+      <x:c r="M356" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -51352,6 +51644,316 @@
       <x:c r="E1921" t="str"/>
       <x:c r="F1921" t="str">
         <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1922">
+      <x:c r="A1922" t="str">
+        <x:v>COMP_HUNTER_GROUP</x:v>
+      </x:c>
+      <x:c r="B1922" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1922" t="str">
+        <x:v>Hunter Group ASA</x:v>
+      </x:c>
+      <x:c r="D1922" t="str">
+        <x:v>Norway</x:v>
+      </x:c>
+      <x:c r="E1922" t="str"/>
+      <x:c r="F1922" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1923">
+      <x:c r="A1923" t="str">
+        <x:v>COMP_MERCURIA</x:v>
+      </x:c>
+      <x:c r="B1923" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1923" t="str">
+        <x:v>Mercuria Energy Group</x:v>
+      </x:c>
+      <x:c r="D1923" t="str">
+        <x:v>Switzerland</x:v>
+      </x:c>
+      <x:c r="E1923" t="str"/>
+      <x:c r="F1923" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1924">
+      <x:c r="A1924" t="str">
+        <x:v>COMP_MSC_SHIPMANAGEMENT</x:v>
+      </x:c>
+      <x:c r="B1924" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1924" t="str">
+        <x:v>MSC Shipmanagement Limited</x:v>
+      </x:c>
+      <x:c r="D1924" t="str">
+        <x:v>Cyprus</x:v>
+      </x:c>
+      <x:c r="E1924" t="str"/>
+      <x:c r="F1924" t="str">
+        <x:v>Active / probation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1925">
+      <x:c r="A1925" t="str">
+        <x:v>COMP_HONG_KONG_SPIRIT</x:v>
+      </x:c>
+      <x:c r="B1925" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1925" t="str">
+        <x:v>Hong Kong Spirit Shipping and Trading Ltd</x:v>
+      </x:c>
+      <x:c r="D1925" t="str">
+        <x:v>Hong Kong</x:v>
+      </x:c>
+      <x:c r="E1925" t="str"/>
+      <x:c r="F1925" t="str">
+        <x:v>Active / probation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1926">
+      <x:c r="A1926" t="str">
+        <x:v>COMP_NOVATEK</x:v>
+      </x:c>
+      <x:c r="B1926" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1926" t="str">
+        <x:v>PAO NOVATEK</x:v>
+      </x:c>
+      <x:c r="D1926" t="str">
+        <x:v>Russia</x:v>
+      </x:c>
+      <x:c r="E1926" t="str"/>
+      <x:c r="F1926" t="str">
+        <x:v>Active / sanctions exposed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1927">
+      <x:c r="A1927" t="str">
+        <x:v>COMP_ARCTIC_LNG2</x:v>
+      </x:c>
+      <x:c r="B1927" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1927" t="str">
+        <x:v>Arctic LNG 2 LLC</x:v>
+      </x:c>
+      <x:c r="D1927" t="str">
+        <x:v>Russia</x:v>
+      </x:c>
+      <x:c r="E1927" t="str"/>
+      <x:c r="F1927" t="str">
+        <x:v>Active / constrained</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1928">
+      <x:c r="A1928" t="str">
+        <x:v>COMP_HANWHA_OCEAN</x:v>
+      </x:c>
+      <x:c r="B1928" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1928" t="str">
+        <x:v>Hanwha Ocean</x:v>
+      </x:c>
+      <x:c r="D1928" t="str">
+        <x:v>South Korea</x:v>
+      </x:c>
+      <x:c r="E1928" t="str"/>
+      <x:c r="F1928" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1929">
+      <x:c r="A1929" t="str">
+        <x:v>COMP_SOVCOMFLOT</x:v>
+      </x:c>
+      <x:c r="B1929" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1929" t="str">
+        <x:v>Sovcomflot</x:v>
+      </x:c>
+      <x:c r="D1929" t="str">
+        <x:v>Russia</x:v>
+      </x:c>
+      <x:c r="E1929" t="str"/>
+      <x:c r="F1929" t="str">
+        <x:v>Active / sanctions exposed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1930">
+      <x:c r="A1930" t="str">
+        <x:v>ORG_MARAD</x:v>
+      </x:c>
+      <x:c r="B1930" t="str">
+        <x:v>U.S. Maritime Administration</x:v>
+      </x:c>
+      <x:c r="C1930" t="str">
+        <x:v>Government agency</x:v>
+      </x:c>
+      <x:c r="D1930" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="E1930" t="str">
+        <x:v>ORG_US_DOT</x:v>
+      </x:c>
+      <x:c r="F1930" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1931">
+      <x:c r="A1931" t="str">
+        <x:v>ORG_USCG</x:v>
+      </x:c>
+      <x:c r="B1931" t="str">
+        <x:v>United States Coast Guard</x:v>
+      </x:c>
+      <x:c r="C1931" t="str">
+        <x:v>Government agency</x:v>
+      </x:c>
+      <x:c r="D1931" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="E1931" t="str">
+        <x:v>ORG_US_DHS</x:v>
+      </x:c>
+      <x:c r="F1931" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1932">
+      <x:c r="A1932" t="str">
+        <x:v>ORG_UMICH_NAME</x:v>
+      </x:c>
+      <x:c r="B1932" t="str">
+        <x:v>University of Michigan Department of Naval Architecture and Marine Engineering</x:v>
+      </x:c>
+      <x:c r="C1932" t="str">
+        <x:v>Education institution</x:v>
+      </x:c>
+      <x:c r="D1932" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="E1932" t="str"/>
+      <x:c r="F1932" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1933">
+      <x:c r="A1933" t="str">
+        <x:v>ORG_NW_MARITIME_CENTER</x:v>
+      </x:c>
+      <x:c r="B1933" t="str">
+        <x:v>Northwest Maritime Center</x:v>
+      </x:c>
+      <x:c r="C1933" t="str">
+        <x:v>Education institution</x:v>
+      </x:c>
+      <x:c r="D1933" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="E1933" t="str"/>
+      <x:c r="F1933" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1934">
+      <x:c r="A1934" t="str">
+        <x:v>ORG_CHAPMAN_SEAMANSHIP</x:v>
+      </x:c>
+      <x:c r="B1934" t="str">
+        <x:v>Chapman School of Seamanship</x:v>
+      </x:c>
+      <x:c r="C1934" t="str">
+        <x:v>Education institution</x:v>
+      </x:c>
+      <x:c r="D1934" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="E1934" t="str"/>
+      <x:c r="F1934" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1935">
+      <x:c r="A1935" t="str">
+        <x:v>ORG_BUNKER_HILL_CC</x:v>
+      </x:c>
+      <x:c r="B1935" t="str">
+        <x:v>Bunker Hill Community College</x:v>
+      </x:c>
+      <x:c r="C1935" t="str">
+        <x:v>Education institution</x:v>
+      </x:c>
+      <x:c r="D1935" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="E1935" t="str"/>
+      <x:c r="F1935" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1936">
+      <x:c r="A1936" t="str">
+        <x:v>ORG_WEBB_INSTITUTE</x:v>
+      </x:c>
+      <x:c r="B1936" t="str">
+        <x:v>Webb Institute</x:v>
+      </x:c>
+      <x:c r="C1936" t="str">
+        <x:v>Education institution</x:v>
+      </x:c>
+      <x:c r="D1936" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="E1936" t="str"/>
+      <x:c r="F1936" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1937">
+      <x:c r="A1937" t="str">
+        <x:v>VES_MSC_SAMIRA_III</x:v>
+      </x:c>
+      <x:c r="B1937" t="str">
+        <x:v>Vessel</x:v>
+      </x:c>
+      <x:c r="C1937" t="str">
+        <x:v>MSC SAMIRA III</x:v>
+      </x:c>
+      <x:c r="D1937" t="str"/>
+      <x:c r="E1937" t="str"/>
+      <x:c r="F1937" t="str">
+        <x:v>Active / compliance case</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1938">
+      <x:c r="A1938" t="str">
+        <x:v>ASSET_ARCTIC_LNG2</x:v>
+      </x:c>
+      <x:c r="B1938" t="str">
+        <x:v>Energy asset</x:v>
+      </x:c>
+      <x:c r="C1938" t="str">
+        <x:v>Arctic LNG 2</x:v>
+      </x:c>
+      <x:c r="D1938" t="str">
+        <x:v>Russia</x:v>
+      </x:c>
+      <x:c r="E1938" t="str">
+        <x:v>COMP_ARCTIC_LNG2</x:v>
+      </x:c>
+      <x:c r="F1938" t="str">
+        <x:v>Operating / sanctions constrained</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -55956,6 +56558,236 @@
       </x:c>
       <x:c r="G199" t="str">
         <x:v>SRC133_002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="200">
+      <x:c r="A200" t="str">
+        <x:v>REL134_001</x:v>
+      </x:c>
+      <x:c r="B200" t="str">
+        <x:v>COMP_NOVATEK</x:v>
+      </x:c>
+      <x:c r="C200" t="str">
+        <x:v>CONTROLS_60_PERCENT</x:v>
+      </x:c>
+      <x:c r="D200" t="str">
+        <x:v>COMP_ARCTIC_LNG2</x:v>
+      </x:c>
+      <x:c r="E200" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+      <x:c r="F200" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G200" t="str">
+        <x:v>SRC134_008</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="201">
+      <x:c r="A201" t="str">
+        <x:v>REL134_002</x:v>
+      </x:c>
+      <x:c r="B201" t="str">
+        <x:v>COMP_HANWHA_OCEAN</x:v>
+      </x:c>
+      <x:c r="C201" t="str">
+        <x:v>PART_OF</x:v>
+      </x:c>
+      <x:c r="D201" t="str">
+        <x:v>COMP_HANWHA_GROUP</x:v>
+      </x:c>
+      <x:c r="E201" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+      <x:c r="F201" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G201" t="str">
+        <x:v>SRC134_008</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="202">
+      <x:c r="A202" t="str">
+        <x:v>REL134_003</x:v>
+      </x:c>
+      <x:c r="B202" t="str">
+        <x:v>COMP_MSC_SHIPMANAGEMENT</x:v>
+      </x:c>
+      <x:c r="C202" t="str">
+        <x:v>PART_OF</x:v>
+      </x:c>
+      <x:c r="D202" t="str">
+        <x:v>COMP_MSC</x:v>
+      </x:c>
+      <x:c r="E202" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+      <x:c r="F202" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="G202" t="str">
+        <x:v>SRC134_005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="203">
+      <x:c r="A203" t="str">
+        <x:v>REL134_004</x:v>
+      </x:c>
+      <x:c r="B203" t="str">
+        <x:v>COMP_HONG_KONG_SPIRIT</x:v>
+      </x:c>
+      <x:c r="C203" t="str">
+        <x:v>OWNS</x:v>
+      </x:c>
+      <x:c r="D203" t="str">
+        <x:v>VES_MSC_SAMIRA_III</x:v>
+      </x:c>
+      <x:c r="E203" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+      <x:c r="F203" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G203" t="str">
+        <x:v>SRC134_005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="204">
+      <x:c r="A204" t="str">
+        <x:v>REL134_005</x:v>
+      </x:c>
+      <x:c r="B204" t="str">
+        <x:v>COMP_MSC_SHIPMANAGEMENT</x:v>
+      </x:c>
+      <x:c r="C204" t="str">
+        <x:v>MANAGES</x:v>
+      </x:c>
+      <x:c r="D204" t="str">
+        <x:v>VES_MSC_SAMIRA_III</x:v>
+      </x:c>
+      <x:c r="E204" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+      <x:c r="F204" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G204" t="str">
+        <x:v>SRC134_005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="205">
+      <x:c r="A205" t="str">
+        <x:v>REL134_006</x:v>
+      </x:c>
+      <x:c r="B205" t="str">
+        <x:v>ORG_MARAD</x:v>
+      </x:c>
+      <x:c r="C205" t="str">
+        <x:v>DESIGNATES</x:v>
+      </x:c>
+      <x:c r="D205" t="str">
+        <x:v>ORG_UMICH_NAME</x:v>
+      </x:c>
+      <x:c r="E205" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+      <x:c r="F205" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G205" t="str">
+        <x:v>SRC134_006</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="206">
+      <x:c r="A206" t="str">
+        <x:v>REL134_007</x:v>
+      </x:c>
+      <x:c r="B206" t="str">
+        <x:v>ORG_MARAD</x:v>
+      </x:c>
+      <x:c r="C206" t="str">
+        <x:v>DESIGNATES</x:v>
+      </x:c>
+      <x:c r="D206" t="str">
+        <x:v>ORG_NW_MARITIME_CENTER</x:v>
+      </x:c>
+      <x:c r="E206" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+      <x:c r="F206" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G206" t="str">
+        <x:v>SRC134_006</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="207">
+      <x:c r="A207" t="str">
+        <x:v>REL134_008</x:v>
+      </x:c>
+      <x:c r="B207" t="str">
+        <x:v>ORG_MARAD</x:v>
+      </x:c>
+      <x:c r="C207" t="str">
+        <x:v>DESIGNATES</x:v>
+      </x:c>
+      <x:c r="D207" t="str">
+        <x:v>ORG_CHAPMAN_SEAMANSHIP</x:v>
+      </x:c>
+      <x:c r="E207" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+      <x:c r="F207" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G207" t="str">
+        <x:v>SRC134_006</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="208">
+      <x:c r="A208" t="str">
+        <x:v>REL134_009</x:v>
+      </x:c>
+      <x:c r="B208" t="str">
+        <x:v>ORG_MARAD</x:v>
+      </x:c>
+      <x:c r="C208" t="str">
+        <x:v>DESIGNATES</x:v>
+      </x:c>
+      <x:c r="D208" t="str">
+        <x:v>ORG_BUNKER_HILL_CC</x:v>
+      </x:c>
+      <x:c r="E208" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+      <x:c r="F208" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G208" t="str">
+        <x:v>SRC134_006</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="209">
+      <x:c r="A209" t="str">
+        <x:v>REL134_010</x:v>
+      </x:c>
+      <x:c r="B209" t="str">
+        <x:v>ORG_MARAD</x:v>
+      </x:c>
+      <x:c r="C209" t="str">
+        <x:v>DESIGNATES</x:v>
+      </x:c>
+      <x:c r="D209" t="str">
+        <x:v>ORG_WEBB_INSTITUTE</x:v>
+      </x:c>
+      <x:c r="E209" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+      <x:c r="F209" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G209" t="str">
+        <x:v>SRC134_006</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/data/01_core_entities.xlsx
+++ b/data/01_core_entities.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="Rb37989def82644bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Companies" sheetId="2" r:id="R184c1459c4644c19"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Entity Registry" sheetId="3" r:id="R33bea03a7e634286"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="R62e0ee1a7d5143aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company System Footprints" sheetId="5" r:id="Rfe9f2373fc6d41ee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="People" sheetId="6" r:id="Ra07bd309a50144a2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leadership Roles" sheetId="7" r:id="R952835cb2e3f4268"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Dictionary" sheetId="8" r:id="Rbd831b4914a44535"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runtime Table Crosswalk" sheetId="9" r:id="Rbc72b67751034869"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Queue" sheetId="10" r:id="R11323fac5c4147e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="Re8ac93b3fa9343a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Companies" sheetId="2" r:id="R12f25b390fee4071"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Entity Registry" sheetId="3" r:id="Re6c5abd1b5bf4fce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="Re4380abb995e4ab6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company System Footprints" sheetId="5" r:id="R65485c304fa2439d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="People" sheetId="6" r:id="R545031dff29b4c89"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leadership Roles" sheetId="7" r:id="R8574f17fca4a4dd1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Dictionary" sheetId="8" r:id="Redb10853f487491b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runtime Table Crosswalk" sheetId="9" r:id="R3cde6f52116b4297"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Queue" sheetId="10" r:id="R0d46f725a0c44c5f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -15571,6 +15571,80 @@
         <x:v>2026-09-10</x:v>
       </x:c>
     </x:row>
+    <x:row r="357">
+      <x:c r="A357" t="str">
+        <x:v>COMP_SIAMGAS</x:v>
+      </x:c>
+      <x:c r="B357" t="str">
+        <x:v>Siamgas and Petrochemicals Public Company Limited</x:v>
+      </x:c>
+      <x:c r="C357" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="D357" t="str">
+        <x:v>Bangkok</x:v>
+      </x:c>
+      <x:c r="E357" t="str">
+        <x:v>Thailand</x:v>
+      </x:c>
+      <x:c r="F357" t="str">
+        <x:v>Public / SET-listed</x:v>
+      </x:c>
+      <x:c r="G357" t="str">
+        <x:v>Energy; LPG terminals; marine transport; logistics infrastructure</x:v>
+      </x:c>
+      <x:c r="H357"/>
+      <x:c r="I357"/>
+      <x:c r="J357" t="str">
+        <x:v>Regional energy and terminal network across Thailand and East Asia</x:v>
+      </x:c>
+      <x:c r="K357" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L357" t="str">
+        <x:v>SRC_0391</x:v>
+      </x:c>
+      <x:c r="M357" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="358">
+      <x:c r="A358" t="str">
+        <x:v>COMP_SUKSAWAT_TERMINAL</x:v>
+      </x:c>
+      <x:c r="B358" t="str">
+        <x:v>Suksawat Terminal Co.</x:v>
+      </x:c>
+      <x:c r="C358" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="D358" t="str">
+        <x:v>Samut Prakan</x:v>
+      </x:c>
+      <x:c r="E358" t="str">
+        <x:v>Thailand</x:v>
+      </x:c>
+      <x:c r="F358" t="str">
+        <x:v>Operating company associated with Suksawat Terminal</x:v>
+      </x:c>
+      <x:c r="G358" t="str">
+        <x:v>River terminal operations; containers; barge connectivity</x:v>
+      </x:c>
+      <x:c r="H358"/>
+      <x:c r="I358"/>
+      <x:c r="J358" t="str">
+        <x:v>Operates Suksawat Terminal on the Chao Phraya River</x:v>
+      </x:c>
+      <x:c r="K358" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L358" t="str">
+        <x:v>SRC_0381</x:v>
+      </x:c>
+      <x:c r="M358" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -56788,6 +56862,75 @@
       </x:c>
       <x:c r="G209" t="str">
         <x:v>SRC134_006</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="210">
+      <x:c r="A210" t="str">
+        <x:v>REL_00209</x:v>
+      </x:c>
+      <x:c r="B210" t="str">
+        <x:v>COMP_SUKSAWAT_TERMINAL</x:v>
+      </x:c>
+      <x:c r="C210" t="str">
+        <x:v>PART_OF</x:v>
+      </x:c>
+      <x:c r="D210" t="str">
+        <x:v>COMP_SIAMGAS</x:v>
+      </x:c>
+      <x:c r="E210" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="F210" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="G210" t="str">
+        <x:v>SRC_0381</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="211">
+      <x:c r="A211" t="str">
+        <x:v>REL_00210</x:v>
+      </x:c>
+      <x:c r="B211" t="str">
+        <x:v>COMP_GULFTAINER</x:v>
+      </x:c>
+      <x:c r="C211" t="str">
+        <x:v>INVESTS_IN</x:v>
+      </x:c>
+      <x:c r="D211" t="str">
+        <x:v>COMP_SUKSAWAT_TERMINAL</x:v>
+      </x:c>
+      <x:c r="E211" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F211" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G211" t="str">
+        <x:v>SRC_0380</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="212">
+      <x:c r="A212" t="str">
+        <x:v>REL_00211</x:v>
+      </x:c>
+      <x:c r="B212" t="str">
+        <x:v>COMP_SIAMGAS</x:v>
+      </x:c>
+      <x:c r="C212" t="str">
+        <x:v>OWNS</x:v>
+      </x:c>
+      <x:c r="D212" t="str">
+        <x:v>COMP_SUKSAWAT_TERMINAL</x:v>
+      </x:c>
+      <x:c r="E212" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="F212" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G212" t="str">
+        <x:v>SRC_0381</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/data/01_core_entities.xlsx
+++ b/data/01_core_entities.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="Re8ac93b3fa9343a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Companies" sheetId="2" r:id="R12f25b390fee4071"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Entity Registry" sheetId="3" r:id="Re6c5abd1b5bf4fce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="Re4380abb995e4ab6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company System Footprints" sheetId="5" r:id="R65485c304fa2439d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="People" sheetId="6" r:id="R545031dff29b4c89"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leadership Roles" sheetId="7" r:id="R8574f17fca4a4dd1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Dictionary" sheetId="8" r:id="Redb10853f487491b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runtime Table Crosswalk" sheetId="9" r:id="R3cde6f52116b4297"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Queue" sheetId="10" r:id="R0d46f725a0c44c5f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R7d062aa7ee07468e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Companies" sheetId="2" r:id="R7371cb5a9d9f4696"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Entity Registry" sheetId="3" r:id="Rb020c9b19f714c08"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="Re3bbfc014fa34363"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company System Footprints" sheetId="5" r:id="R426e10cf73a246dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="People" sheetId="6" r:id="R34732f6d2b2640ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leadership Roles" sheetId="7" r:id="Rae09b58618374047"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Dictionary" sheetId="8" r:id="R9db3b2bcaa964c56"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runtime Table Crosswalk" sheetId="9" r:id="R1cb96d478f1949bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Queue" sheetId="10" r:id="R7804cf86454e4ab7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -15645,6 +15645,144 @@
         <x:v>2026-09-10</x:v>
       </x:c>
     </x:row>
+    <x:row r="359">
+      <x:c r="A359" s="14" t="str">
+        <x:v>COMP_GASLOG</x:v>
+      </x:c>
+      <x:c r="B359" s="14" t="str">
+        <x:v>GasLog Ltd</x:v>
+      </x:c>
+      <x:c r="C359" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="D359" s="14" t="str">
+        <x:v>Piraeus</x:v>
+      </x:c>
+      <x:c r="E359" s="14" t="str">
+        <x:v>Greece</x:v>
+      </x:c>
+      <x:c r="F359" s="14" t="str">
+        <x:v>Publicly listed group / shipping company</x:v>
+      </x:c>
+      <x:c r="G359" s="14" t="str">
+        <x:v>LNG shipping; vessel management</x:v>
+      </x:c>
+      <x:c r="H359" s="14"/>
+      <x:c r="I359" s="14"/>
+      <x:c r="J359" s="14" t="str">
+        <x:v>Sample canonical counterparty for PGSA/STSs and LNG security exposure</x:v>
+      </x:c>
+      <x:c r="K359" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L359" s="14" t="str">
+        <x:v>SRC_SEC_GASLOG</x:v>
+      </x:c>
+      <x:c r="M359" s="14" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="360">
+      <x:c r="A360" s="14" t="str">
+        <x:v>COMP_CL_GAS_THREE</x:v>
+      </x:c>
+      <x:c r="B360" s="14" t="str">
+        <x:v>CL Gas Three Ltd</x:v>
+      </x:c>
+      <x:c r="C360" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="D360" s="14"/>
+      <x:c r="E360" s="14" t="str">
+        <x:v>Greece / Bermuda-linked vessel structure</x:v>
+      </x:c>
+      <x:c r="F360" s="14" t="str">
+        <x:v>Special-purpose registered owner</x:v>
+      </x:c>
+      <x:c r="G360" s="14" t="str">
+        <x:v>Vessel ownership</x:v>
+      </x:c>
+      <x:c r="H360" s="14"/>
+      <x:c r="I360" s="14"/>
+      <x:c r="J360" s="14" t="str">
+        <x:v>Registered owner associated with GasLog Shanghai; source-reported</x:v>
+      </x:c>
+      <x:c r="K360" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L360" s="14" t="str">
+        <x:v>SRC_SEC_GASLOG</x:v>
+      </x:c>
+      <x:c r="M360" s="14" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="361">
+      <x:c r="A361" s="14" t="str">
+        <x:v>COMP_NAKILAT_HHI1910</x:v>
+      </x:c>
+      <x:c r="B361" s="14" t="str">
+        <x:v>Nakilat HHI 1910 Inc.</x:v>
+      </x:c>
+      <x:c r="C361" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="D361" s="14"/>
+      <x:c r="E361" s="14"/>
+      <x:c r="F361" s="14" t="str">
+        <x:v>Special-purpose vessel owner</x:v>
+      </x:c>
+      <x:c r="G361" s="14" t="str">
+        <x:v>LNG vessel ownership</x:v>
+      </x:c>
+      <x:c r="H361" s="14"/>
+      <x:c r="I361" s="14"/>
+      <x:c r="J361" s="14" t="str">
+        <x:v>Registered owner associated with Al Rekayyat; source-reported</x:v>
+      </x:c>
+      <x:c r="K361" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L361" s="14" t="str">
+        <x:v>SRC_SEC_ALREK</x:v>
+      </x:c>
+      <x:c r="M361" s="14" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="362">
+      <x:c r="A362" s="14" t="str">
+        <x:v>COMP_STASCO_SM</x:v>
+      </x:c>
+      <x:c r="B362" s="14" t="str">
+        <x:v>STASCO Ship Management</x:v>
+      </x:c>
+      <x:c r="C362" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="D362" s="14"/>
+      <x:c r="E362" s="14"/>
+      <x:c r="F362" s="14" t="str">
+        <x:v>Ship manager / operator</x:v>
+      </x:c>
+      <x:c r="G362" s="14" t="str">
+        <x:v>Ship management</x:v>
+      </x:c>
+      <x:c r="H362" s="14"/>
+      <x:c r="I362" s="14"/>
+      <x:c r="J362" s="14" t="str">
+        <x:v>Source-reported operator/manager associated with Al Rekayyat</x:v>
+      </x:c>
+      <x:c r="K362" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L362" s="14" t="str">
+        <x:v>SRC_SEC_ALREK</x:v>
+      </x:c>
+      <x:c r="M362" s="14" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/data/01_core_entities.xlsx
+++ b/data/01_core_entities.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R7d062aa7ee07468e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Companies" sheetId="2" r:id="R7371cb5a9d9f4696"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Entity Registry" sheetId="3" r:id="Rb020c9b19f714c08"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="Re3bbfc014fa34363"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company System Footprints" sheetId="5" r:id="R426e10cf73a246dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="People" sheetId="6" r:id="R34732f6d2b2640ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leadership Roles" sheetId="7" r:id="Rae09b58618374047"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Dictionary" sheetId="8" r:id="R9db3b2bcaa964c56"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runtime Table Crosswalk" sheetId="9" r:id="R1cb96d478f1949bd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Queue" sheetId="10" r:id="R7804cf86454e4ab7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R061ee5595c3740b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Companies" sheetId="2" r:id="R4106de1ffb6841ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Entity Registry" sheetId="3" r:id="Rc419496304df4bb6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="Rb6780bbd90974a26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company System Footprints" sheetId="5" r:id="R9b8de8f6f8ca473b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="People" sheetId="6" r:id="Ra99cd6384d064a66"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leadership Roles" sheetId="7" r:id="Re9ba9c40ae0f4b3c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Dictionary" sheetId="8" r:id="Rf4c7ac1294fc46fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runtime Table Crosswalk" sheetId="9" r:id="R489cfb8069614929"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Queue" sheetId="10" r:id="Rd2b472657e234114"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -14547,36 +14547,36 @@
     </x:row>
     <x:row r="329">
       <x:c r="A329" t="str">
-        <x:v>COMP_PENINSULA</x:v>
+        <x:v>COMP_VALE</x:v>
       </x:c>
       <x:c r="B329" t="str">
-        <x:v>Peninsula</x:v>
+        <x:v>Vale</x:v>
       </x:c>
       <x:c r="C329" t="str">
-        <x:v>Marine fuel supplier</x:v>
+        <x:v>Mining company</x:v>
       </x:c>
       <x:c r="D329" t="str">
-        <x:v>Gibraltar</x:v>
+        <x:v>Rio de Janeiro</x:v>
       </x:c>
       <x:c r="E329" t="str">
-        <x:v>Gibraltar</x:v>
+        <x:v>Brazil</x:v>
       </x:c>
       <x:c r="F329" t="str">
-        <x:v>Private</x:v>
+        <x:v>Public company</x:v>
       </x:c>
       <x:c r="G329" t="str">
-        <x:v>Marine fuel supply; bunker tanker chartering</x:v>
-      </x:c>
-      <x:c r="H329" t="str"/>
-      <x:c r="I329" t="str"/>
+        <x:v>Iron ore; mining; logistics; long-term shipping contracts</x:v>
+      </x:c>
+      <x:c r="H329"/>
+      <x:c r="I329"/>
       <x:c r="J329" t="str">
-        <x:v>Charterer of HERCULES STAR.</x:v>
+        <x:v>Major global iron-ore cargo owner</x:v>
       </x:c>
       <x:c r="K329" t="str">
         <x:v>Active</x:v>
       </x:c>
       <x:c r="L329" t="str">
-        <x:v>SRC133_001</x:v>
+        <x:v>SRC260910_005</x:v>
       </x:c>
       <x:c r="M329" t="str">
         <x:v>2026-09-10</x:v>
@@ -14584,34 +14584,36 @@
     </x:row>
     <x:row r="330">
       <x:c r="A330" t="str">
-        <x:v>COMP_HERCULES_TANKER</x:v>
+        <x:v>COMP_SAUDI_ARAMCO</x:v>
       </x:c>
       <x:c r="B330" t="str">
-        <x:v>Hercules Tanker Management</x:v>
+        <x:v>Saudi Aramco</x:v>
       </x:c>
       <x:c r="C330" t="str">
-        <x:v>Tanker management company</x:v>
-      </x:c>
-      <x:c r="D330" t="str"/>
+        <x:v>Integrated energy company</x:v>
+      </x:c>
+      <x:c r="D330" t="str">
+        <x:v>Dhahran</x:v>
+      </x:c>
       <x:c r="E330" t="str">
-        <x:v>Gibraltar</x:v>
+        <x:v>Saudi Arabia</x:v>
       </x:c>
       <x:c r="F330" t="str">
-        <x:v>Sister company to Peninsula</x:v>
+        <x:v>Saudi state-controlled</x:v>
       </x:c>
       <x:c r="G330" t="str">
-        <x:v>Bunker tanker provision; tanker management</x:v>
-      </x:c>
-      <x:c r="H330" t="str"/>
-      <x:c r="I330" t="str"/>
+        <x:v>Oil; gas; refining; terminals; energy infrastructure</x:v>
+      </x:c>
+      <x:c r="H330"/>
+      <x:c r="I330"/>
       <x:c r="J330" t="str">
-        <x:v>Provides HERCULES STAR to Peninsula under charter.</x:v>
+        <x:v>Jazan refinery and Red Sea energy infrastructure exposure</x:v>
       </x:c>
       <x:c r="K330" t="str">
         <x:v>Active</x:v>
       </x:c>
       <x:c r="L330" t="str">
-        <x:v>SRC133_001</x:v>
+        <x:v>SRC260910_001</x:v>
       </x:c>
       <x:c r="M330" t="str">
         <x:v>2026-09-10</x:v>
@@ -14619,36 +14621,36 @@
     </x:row>
     <x:row r="331">
       <x:c r="A331" t="str">
-        <x:v>COMP_SAFEEN_MARINE</x:v>
+        <x:v>COMP_COCHIN_SHIPYARD</x:v>
       </x:c>
       <x:c r="B331" t="str">
-        <x:v>SAFEEN Marine Services</x:v>
+        <x:v>Cochin Shipyard</x:v>
       </x:c>
       <x:c r="C331" t="str">
-        <x:v>Maritime services company</x:v>
+        <x:v>Shipbuilder / repair company</x:v>
       </x:c>
       <x:c r="D331" t="str">
-        <x:v>Abu Dhabi</x:v>
+        <x:v>Kochi</x:v>
       </x:c>
       <x:c r="E331" t="str">
-        <x:v>United Arab Emirates</x:v>
+        <x:v>India</x:v>
       </x:c>
       <x:c r="F331" t="str">
-        <x:v>AD Ports Group</x:v>
+        <x:v>Government-controlled listed company</x:v>
       </x:c>
       <x:c r="G331" t="str">
-        <x:v>Towage; harbour craft; pilotage; marine services</x:v>
-      </x:c>
-      <x:c r="H331" t="str"/>
-      <x:c r="I331" t="str"/>
+        <x:v>Shipbuilding; ship repair; offshore engineering</x:v>
+      </x:c>
+      <x:c r="H331"/>
+      <x:c r="I331"/>
       <x:c r="J331" t="str">
-        <x:v>AD Ports maritime-services fleet, linked to Noatum through the group operating ecosystem.</x:v>
+        <x:v>International Ship Repair Facility at Willingdon Island</x:v>
       </x:c>
       <x:c r="K331" t="str">
         <x:v>Active</x:v>
       </x:c>
       <x:c r="L331" t="str">
-        <x:v>SRC133_006</x:v>
+        <x:v>SRC260910_003</x:v>
       </x:c>
       <x:c r="M331" t="str">
         <x:v>2026-09-10</x:v>
@@ -14656,36 +14658,36 @@
     </x:row>
     <x:row r="332">
       <x:c r="A332" t="str">
-        <x:v>COMP_SAFEEN_OFFSHORE</x:v>
+        <x:v>COMP_DRYDOCKS_WORLD</x:v>
       </x:c>
       <x:c r="B332" t="str">
-        <x:v>SAFEEN Offshore</x:v>
+        <x:v>Drydocks World</x:v>
       </x:c>
       <x:c r="C332" t="str">
-        <x:v>Offshore services business</x:v>
+        <x:v>Ship repair / offshore engineering company</x:v>
       </x:c>
       <x:c r="D332" t="str">
-        <x:v>Abu Dhabi</x:v>
+        <x:v>Dubai</x:v>
       </x:c>
       <x:c r="E332" t="str">
         <x:v>United Arab Emirates</x:v>
       </x:c>
       <x:c r="F332" t="str">
-        <x:v>AD Ports Group</x:v>
+        <x:v>DP World group</x:v>
       </x:c>
       <x:c r="G332" t="str">
-        <x:v>Offshore support; subsea; project logistics</x:v>
-      </x:c>
-      <x:c r="H332" t="str"/>
-      <x:c r="I332" t="str"/>
+        <x:v>Ship repair; conversions; offshore fabrication; MRO</x:v>
+      </x:c>
+      <x:c r="H332"/>
+      <x:c r="I332"/>
       <x:c r="J332" t="str">
-        <x:v>Offshore division within the AD Ports maritime cluster.</x:v>
+        <x:v>Operating lead in proposed 50:50 Kochi ISRF venture</x:v>
       </x:c>
       <x:c r="K332" t="str">
         <x:v>Active</x:v>
       </x:c>
       <x:c r="L332" t="str">
-        <x:v>SRC133_004</x:v>
+        <x:v>SRC260910_003</x:v>
       </x:c>
       <x:c r="M332" t="str">
         <x:v>2026-09-10</x:v>
@@ -14693,36 +14695,34 @@
     </x:row>
     <x:row r="333">
       <x:c r="A333" t="str">
-        <x:v>COMP_ROYAL_CARIBBEAN_GROUP</x:v>
+        <x:v>COMP_CHAOPHAYA_TERMINAL</x:v>
       </x:c>
       <x:c r="B333" t="str">
-        <x:v>Royal Caribbean Group</x:v>
+        <x:v>Chaophaya Terminal International</x:v>
       </x:c>
       <x:c r="C333" t="str">
-        <x:v>Cruise group</x:v>
-      </x:c>
-      <x:c r="D333" t="str">
-        <x:v>Miami</x:v>
-      </x:c>
+        <x:v>Terminal operator</x:v>
+      </x:c>
+      <x:c r="D333"/>
       <x:c r="E333" t="str">
-        <x:v>United States</x:v>
+        <x:v>Thailand</x:v>
       </x:c>
       <x:c r="F333" t="str">
-        <x:v>Public company</x:v>
+        <x:v>Private / operator</x:v>
       </x:c>
       <x:c r="G333" t="str">
-        <x:v>Cruise lines; private destinations</x:v>
-      </x:c>
-      <x:c r="H333" t="str"/>
-      <x:c r="I333" t="str"/>
+        <x:v>Container terminal operations</x:v>
+      </x:c>
+      <x:c r="H333"/>
+      <x:c r="I333"/>
       <x:c r="J333" t="str">
-        <x:v>Parent of Royal Caribbean International, Celebrity Cruises and Silversea.</x:v>
+        <x:v>Operator of Songkhla container terminal</x:v>
       </x:c>
       <x:c r="K333" t="str">
         <x:v>Active</x:v>
       </x:c>
       <x:c r="L333" t="str">
-        <x:v>SRC133_003</x:v>
+        <x:v>SRC260910_009</x:v>
       </x:c>
       <x:c r="M333" t="str">
         <x:v>2026-09-10</x:v>
@@ -14730,36 +14730,36 @@
     </x:row>
     <x:row r="334">
       <x:c r="A334" t="str">
-        <x:v>COMP_ROYAL_CARIBBEAN_INTL</x:v>
+        <x:v>COMP_PORTS_AMERICA_CHES</x:v>
       </x:c>
       <x:c r="B334" t="str">
-        <x:v>Royal Caribbean International</x:v>
+        <x:v>Ports America Chesapeake</x:v>
       </x:c>
       <x:c r="C334" t="str">
-        <x:v>Cruise line</x:v>
+        <x:v>Terminal operator</x:v>
       </x:c>
       <x:c r="D334" t="str">
-        <x:v>Miami</x:v>
+        <x:v>Baltimore</x:v>
       </x:c>
       <x:c r="E334" t="str">
         <x:v>United States</x:v>
       </x:c>
       <x:c r="F334" t="str">
-        <x:v>Royal Caribbean Group</x:v>
+        <x:v>Ports America platform</x:v>
       </x:c>
       <x:c r="G334" t="str">
-        <x:v>Ocean cruise; private destinations</x:v>
-      </x:c>
-      <x:c r="H334" t="str"/>
-      <x:c r="I334" t="str"/>
+        <x:v>Container terminal operations; intermodal</x:v>
+      </x:c>
+      <x:c r="H334"/>
+      <x:c r="I334"/>
       <x:c r="J334" t="str">
-        <x:v>Large-ship global cruise brand with major Caribbean deployment.</x:v>
+        <x:v>Operates Seagirt Marine Terminal</x:v>
       </x:c>
       <x:c r="K334" t="str">
         <x:v>Active</x:v>
       </x:c>
       <x:c r="L334" t="str">
-        <x:v>SRC133_007</x:v>
+        <x:v>SRC260910_013</x:v>
       </x:c>
       <x:c r="M334" t="str">
         <x:v>2026-09-10</x:v>
@@ -14767,36 +14767,34 @@
     </x:row>
     <x:row r="335">
       <x:c r="A335" t="str">
-        <x:v>COMP_CELEBRITY_CRUISES</x:v>
+        <x:v>COMP_FREY_COMMODITIES</x:v>
       </x:c>
       <x:c r="B335" t="str">
-        <x:v>Celebrity Cruises</x:v>
+        <x:v>Frey Commodities</x:v>
       </x:c>
       <x:c r="C335" t="str">
-        <x:v>Cruise line</x:v>
-      </x:c>
-      <x:c r="D335" t="str">
-        <x:v>Miami</x:v>
-      </x:c>
+        <x:v>Agricultural commodities company</x:v>
+      </x:c>
+      <x:c r="D335"/>
       <x:c r="E335" t="str">
         <x:v>United States</x:v>
       </x:c>
       <x:c r="F335" t="str">
-        <x:v>Royal Caribbean Group</x:v>
+        <x:v>Private</x:v>
       </x:c>
       <x:c r="G335" t="str">
-        <x:v>Premium ocean cruise</x:v>
-      </x:c>
-      <x:c r="H335" t="str"/>
-      <x:c r="I335" t="str"/>
+        <x:v>Grain; agricultural exports; logistics</x:v>
+      </x:c>
+      <x:c r="H335"/>
+      <x:c r="I335"/>
       <x:c r="J335" t="str">
-        <x:v>Premium cruise brand.</x:v>
+        <x:v>Partner in Baltimore on-dock grain transloading facility</x:v>
       </x:c>
       <x:c r="K335" t="str">
         <x:v>Active</x:v>
       </x:c>
       <x:c r="L335" t="str">
-        <x:v>SRC133_003</x:v>
+        <x:v>SRC260910_013</x:v>
       </x:c>
       <x:c r="M335" t="str">
         <x:v>2026-09-10</x:v>
@@ -14804,36 +14802,34 @@
     </x:row>
     <x:row r="336">
       <x:c r="A336" t="str">
-        <x:v>COMP_SILVERSEA</x:v>
+        <x:v>COMP_GUOYOU_RESOURCES</x:v>
       </x:c>
       <x:c r="B336" t="str">
-        <x:v>Silversea Cruises</x:v>
+        <x:v>Guo You Resources Group</x:v>
       </x:c>
       <x:c r="C336" t="str">
-        <x:v>Cruise line</x:v>
-      </x:c>
-      <x:c r="D336" t="str">
-        <x:v>Monaco</x:v>
-      </x:c>
+        <x:v>Infrastructure / resources developer</x:v>
+      </x:c>
+      <x:c r="D336"/>
       <x:c r="E336" t="str">
-        <x:v>Monaco</x:v>
+        <x:v>China</x:v>
       </x:c>
       <x:c r="F336" t="str">
-        <x:v>Royal Caribbean Group</x:v>
+        <x:v>Private / project developer</x:v>
       </x:c>
       <x:c r="G336" t="str">
-        <x:v>Luxury and expedition cruise</x:v>
-      </x:c>
-      <x:c r="H336" t="str"/>
-      <x:c r="I336" t="str"/>
+        <x:v>Port; logistics; resources infrastructure</x:v>
+      </x:c>
+      <x:c r="H336"/>
+      <x:c r="I336"/>
       <x:c r="J336" t="str">
-        <x:v>Luxury and expedition cruise brand.</x:v>
+        <x:v>Leading Kazakhstan Caspian hub project</x:v>
       </x:c>
       <x:c r="K336" t="str">
         <x:v>Active</x:v>
       </x:c>
       <x:c r="L336" t="str">
-        <x:v>SRC133_003</x:v>
+        <x:v>SRC260910_014</x:v>
       </x:c>
       <x:c r="M336" t="str">
         <x:v>2026-09-10</x:v>
@@ -14841,36 +14837,36 @@
     </x:row>
     <x:row r="337">
       <x:c r="A337" t="str">
-        <x:v>COMP_CARNIVAL_CORP</x:v>
+        <x:v>COMP_ASIAN_TERMINALS</x:v>
       </x:c>
       <x:c r="B337" t="str">
-        <x:v>Carnival Corporation &amp; plc</x:v>
+        <x:v>Asian Terminals Inc</x:v>
       </x:c>
       <x:c r="C337" t="str">
-        <x:v>Cruise group</x:v>
+        <x:v>Terminal operator</x:v>
       </x:c>
       <x:c r="D337" t="str">
-        <x:v>Miami</x:v>
+        <x:v>Manila</x:v>
       </x:c>
       <x:c r="E337" t="str">
-        <x:v>United States</x:v>
+        <x:v>Philippines</x:v>
       </x:c>
       <x:c r="F337" t="str">
-        <x:v>Public company</x:v>
+        <x:v>Listed / DP World-linked operator</x:v>
       </x:c>
       <x:c r="G337" t="str">
-        <x:v>Cruise lines; private destinations</x:v>
-      </x:c>
-      <x:c r="H337" t="str"/>
-      <x:c r="I337" t="str"/>
+        <x:v>Ports; container terminals; logistics</x:v>
+      </x:c>
+      <x:c r="H337"/>
+      <x:c r="I337"/>
       <x:c r="J337" t="str">
-        <x:v>Multi-brand cruise group.</x:v>
+        <x:v>Manila South Harbour operator and investment partner</x:v>
       </x:c>
       <x:c r="K337" t="str">
         <x:v>Active</x:v>
       </x:c>
       <x:c r="L337" t="str">
-        <x:v>SRC133_003</x:v>
+        <x:v>SRC260910_016</x:v>
       </x:c>
       <x:c r="M337" t="str">
         <x:v>2026-09-10</x:v>
@@ -14878,36 +14874,36 @@
     </x:row>
     <x:row r="338">
       <x:c r="A338" t="str">
-        <x:v>COMP_CARNIVAL_CRUISE</x:v>
+        <x:v>COMP_GULFCAP_AFRICA</x:v>
       </x:c>
       <x:c r="B338" t="str">
-        <x:v>Carnival Cruise Line</x:v>
+        <x:v>GulfCap Africa</x:v>
       </x:c>
       <x:c r="C338" t="str">
-        <x:v>Cruise line</x:v>
+        <x:v>Investment / development company</x:v>
       </x:c>
       <x:c r="D338" t="str">
-        <x:v>Miami</x:v>
+        <x:v>Nairobi</x:v>
       </x:c>
       <x:c r="E338" t="str">
-        <x:v>United States</x:v>
+        <x:v>Kenya</x:v>
       </x:c>
       <x:c r="F338" t="str">
-        <x:v>Carnival Corporation &amp; plc</x:v>
+        <x:v>Private</x:v>
       </x:c>
       <x:c r="G338" t="str">
-        <x:v>Contemporary ocean cruise</x:v>
-      </x:c>
-      <x:c r="H338" t="str"/>
-      <x:c r="I338" t="str"/>
+        <x:v>Industrial parks; logistics; development</x:v>
+      </x:c>
+      <x:c r="H338"/>
+      <x:c r="I338"/>
       <x:c r="J338" t="str">
-        <x:v>Caribbean-focused mass-market cruise brand.</x:v>
+        <x:v>Mombasa Industrial Park joint-venture partner with DP World</x:v>
       </x:c>
       <x:c r="K338" t="str">
         <x:v>Active</x:v>
       </x:c>
       <x:c r="L338" t="str">
-        <x:v>SRC133_008</x:v>
+        <x:v>SRC260910_017</x:v>
       </x:c>
       <x:c r="M338" t="str">
         <x:v>2026-09-10</x:v>
@@ -14915,36 +14911,36 @@
     </x:row>
     <x:row r="339">
       <x:c r="A339" t="str">
-        <x:v>COMP_PRINCESS_CRUISES</x:v>
+        <x:v>COMP_ADANI_PORTS</x:v>
       </x:c>
       <x:c r="B339" t="str">
-        <x:v>Princess Cruises</x:v>
+        <x:v>Adani Ports and Special Economic Zone</x:v>
       </x:c>
       <x:c r="C339" t="str">
-        <x:v>Cruise line</x:v>
+        <x:v>Port operator</x:v>
       </x:c>
       <x:c r="D339" t="str">
-        <x:v>Santa Clarita</x:v>
+        <x:v>Ahmedabad</x:v>
       </x:c>
       <x:c r="E339" t="str">
-        <x:v>United States</x:v>
+        <x:v>India</x:v>
       </x:c>
       <x:c r="F339" t="str">
-        <x:v>Carnival Corporation &amp; plc</x:v>
+        <x:v>Adani Group</x:v>
       </x:c>
       <x:c r="G339" t="str">
-        <x:v>Premium ocean cruise</x:v>
-      </x:c>
-      <x:c r="H339" t="str"/>
-      <x:c r="I339" t="str"/>
+        <x:v>Ports; terminals; logistics; SEZs</x:v>
+      </x:c>
+      <x:c r="H339"/>
+      <x:c r="I339"/>
       <x:c r="J339" t="str">
-        <x:v>Global premium cruise brand.</x:v>
+        <x:v>30-year Paradip CQ-I/CQ-II berth concession</x:v>
       </x:c>
       <x:c r="K339" t="str">
         <x:v>Active</x:v>
       </x:c>
       <x:c r="L339" t="str">
-        <x:v>SRC133_003</x:v>
+        <x:v>SRC260910_018</x:v>
       </x:c>
       <x:c r="M339" t="str">
         <x:v>2026-09-10</x:v>
@@ -14952,36 +14948,36 @@
     </x:row>
     <x:row r="340">
       <x:c r="A340" t="str">
-        <x:v>COMP_HOLLAND_AMERICA</x:v>
+        <x:v>COMP_ODFJELL_DRILLING</x:v>
       </x:c>
       <x:c r="B340" t="str">
-        <x:v>Holland America Line</x:v>
+        <x:v>Odfjell Drilling</x:v>
       </x:c>
       <x:c r="C340" t="str">
-        <x:v>Cruise line</x:v>
+        <x:v>Offshore drilling contractor</x:v>
       </x:c>
       <x:c r="D340" t="str">
-        <x:v>Seattle</x:v>
+        <x:v>Bergen</x:v>
       </x:c>
       <x:c r="E340" t="str">
-        <x:v>United States</x:v>
+        <x:v>Norway</x:v>
       </x:c>
       <x:c r="F340" t="str">
-        <x:v>Carnival Corporation &amp; plc</x:v>
+        <x:v>Listed company</x:v>
       </x:c>
       <x:c r="G340" t="str">
-        <x:v>Premium ocean and Alaska cruise</x:v>
-      </x:c>
-      <x:c r="H340" t="str"/>
-      <x:c r="I340" t="str"/>
+        <x:v>Semisubmersible drilling; offshore services</x:v>
+      </x:c>
+      <x:c r="H340"/>
+      <x:c r="I340"/>
       <x:c r="J340" t="str">
-        <x:v>Alaska, Caribbean and global deployment.</x:v>
+        <x:v>Deepsea Bergen contract backlog</x:v>
       </x:c>
       <x:c r="K340" t="str">
         <x:v>Active</x:v>
       </x:c>
       <x:c r="L340" t="str">
-        <x:v>SRC133_003</x:v>
+        <x:v>SRC260910_019</x:v>
       </x:c>
       <x:c r="M340" t="str">
         <x:v>2026-09-10</x:v>
@@ -14989,36 +14985,36 @@
     </x:row>
     <x:row r="341">
       <x:c r="A341" t="str">
-        <x:v>COMP_NCLH</x:v>
+        <x:v>COMP_VAR_ENERGI</x:v>
       </x:c>
       <x:c r="B341" t="str">
-        <x:v>Norwegian Cruise Line Holdings</x:v>
+        <x:v>Vår Energi</x:v>
       </x:c>
       <x:c r="C341" t="str">
-        <x:v>Cruise group</x:v>
+        <x:v>Energy company</x:v>
       </x:c>
       <x:c r="D341" t="str">
-        <x:v>Miami</x:v>
+        <x:v>Sandnes</x:v>
       </x:c>
       <x:c r="E341" t="str">
-        <x:v>United States</x:v>
+        <x:v>Norway</x:v>
       </x:c>
       <x:c r="F341" t="str">
-        <x:v>Public company</x:v>
+        <x:v>Listed / Eni-linked ownership</x:v>
       </x:c>
       <x:c r="G341" t="str">
-        <x:v>Cruise lines; private destinations</x:v>
-      </x:c>
-      <x:c r="H341" t="str"/>
-      <x:c r="I341" t="str"/>
+        <x:v>Upstream oil and gas</x:v>
+      </x:c>
+      <x:c r="H341"/>
+      <x:c r="I341"/>
       <x:c r="J341" t="str">
-        <x:v>Parent of Norwegian Cruise Line, Oceania Cruises and Regent Seven Seas Cruises.</x:v>
+        <x:v>Customer for Deepsea Bergen drilling contract</x:v>
       </x:c>
       <x:c r="K341" t="str">
         <x:v>Active</x:v>
       </x:c>
       <x:c r="L341" t="str">
-        <x:v>SRC133_003</x:v>
+        <x:v>SRC260910_019</x:v>
       </x:c>
       <x:c r="M341" t="str">
         <x:v>2026-09-10</x:v>
@@ -15026,36 +15022,36 @@
     </x:row>
     <x:row r="342">
       <x:c r="A342" t="str">
-        <x:v>COMP_NCL</x:v>
+        <x:v>COMP_ALAM_MARITIM</x:v>
       </x:c>
       <x:c r="B342" t="str">
-        <x:v>Norwegian Cruise Line</x:v>
+        <x:v>Alam Maritim Resources</x:v>
       </x:c>
       <x:c r="C342" t="str">
-        <x:v>Cruise line</x:v>
+        <x:v>Offshore vessel owner / services company</x:v>
       </x:c>
       <x:c r="D342" t="str">
-        <x:v>Miami</x:v>
+        <x:v>Kuala Lumpur</x:v>
       </x:c>
       <x:c r="E342" t="str">
-        <x:v>United States</x:v>
+        <x:v>Malaysia</x:v>
       </x:c>
       <x:c r="F342" t="str">
-        <x:v>Norwegian Cruise Line Holdings</x:v>
+        <x:v>Listed company</x:v>
       </x:c>
       <x:c r="G342" t="str">
-        <x:v>Ocean cruise; private destinations</x:v>
-      </x:c>
-      <x:c r="H342" t="str"/>
-      <x:c r="I342" t="str"/>
+        <x:v>Offshore support vessels; subsea services</x:v>
+      </x:c>
+      <x:c r="H342"/>
+      <x:c r="I342"/>
       <x:c r="J342" t="str">
-        <x:v>Global cruise brand with Caribbean private-destination exposure.</x:v>
+        <x:v>Charter-rate fraud case involving CEO</x:v>
       </x:c>
       <x:c r="K342" t="str">
         <x:v>Active</x:v>
       </x:c>
       <x:c r="L342" t="str">
-        <x:v>SRC133_009</x:v>
+        <x:v>SRC260910_020</x:v>
       </x:c>
       <x:c r="M342" t="str">
         <x:v>2026-09-10</x:v>
@@ -15063,36 +15059,36 @@
     </x:row>
     <x:row r="343">
       <x:c r="A343" t="str">
-        <x:v>COMP_OCEANIA</x:v>
+        <x:v>COMP_ERNST_RUSS</x:v>
       </x:c>
       <x:c r="B343" t="str">
-        <x:v>Oceania Cruises</x:v>
+        <x:v>Ernst Russ</x:v>
       </x:c>
       <x:c r="C343" t="str">
-        <x:v>Cruise line</x:v>
+        <x:v>Shipowner / maritime investment company</x:v>
       </x:c>
       <x:c r="D343" t="str">
-        <x:v>Miami</x:v>
+        <x:v>Hamburg</x:v>
       </x:c>
       <x:c r="E343" t="str">
-        <x:v>United States</x:v>
+        <x:v>Germany</x:v>
       </x:c>
       <x:c r="F343" t="str">
-        <x:v>Norwegian Cruise Line Holdings</x:v>
+        <x:v>Listed company</x:v>
       </x:c>
       <x:c r="G343" t="str">
-        <x:v>Upper-premium ocean cruise</x:v>
-      </x:c>
-      <x:c r="H343" t="str"/>
-      <x:c r="I343" t="str"/>
+        <x:v>Containerships; product/chemical tankers; maritime assets</x:v>
+      </x:c>
+      <x:c r="H343"/>
+      <x:c r="I343"/>
       <x:c r="J343" t="str">
-        <x:v>Destination-focused upper-premium cruise brand.</x:v>
+        <x:v>Expanding tanker fleet; Cargill-backed charters</x:v>
       </x:c>
       <x:c r="K343" t="str">
         <x:v>Active</x:v>
       </x:c>
       <x:c r="L343" t="str">
-        <x:v>SRC133_003</x:v>
+        <x:v>SRC260910_021</x:v>
       </x:c>
       <x:c r="M343" t="str">
         <x:v>2026-09-10</x:v>
@@ -15100,36 +15096,36 @@
     </x:row>
     <x:row r="344">
       <x:c r="A344" t="str">
-        <x:v>COMP_REGENT_SEVEN_SEAS</x:v>
+        <x:v>COMP_CARGILL</x:v>
       </x:c>
       <x:c r="B344" t="str">
-        <x:v>Regent Seven Seas Cruises</x:v>
+        <x:v>Cargill</x:v>
       </x:c>
       <x:c r="C344" t="str">
-        <x:v>Cruise line</x:v>
+        <x:v>Commodities and logistics company</x:v>
       </x:c>
       <x:c r="D344" t="str">
-        <x:v>Miami</x:v>
+        <x:v>Minnetonka</x:v>
       </x:c>
       <x:c r="E344" t="str">
         <x:v>United States</x:v>
       </x:c>
       <x:c r="F344" t="str">
-        <x:v>Norwegian Cruise Line Holdings</x:v>
+        <x:v>Private</x:v>
       </x:c>
       <x:c r="G344" t="str">
-        <x:v>Luxury ocean cruise</x:v>
-      </x:c>
-      <x:c r="H344" t="str"/>
-      <x:c r="I344" t="str"/>
+        <x:v>Agriculture; commodities; freight; chartering</x:v>
+      </x:c>
+      <x:c r="H344"/>
+      <x:c r="I344"/>
       <x:c r="J344" t="str">
-        <x:v>Luxury all-inclusive cruise brand.</x:v>
+        <x:v>Charterer of Ernst Russ tanker pair</x:v>
       </x:c>
       <x:c r="K344" t="str">
         <x:v>Active</x:v>
       </x:c>
       <x:c r="L344" t="str">
-        <x:v>SRC133_003</x:v>
+        <x:v>SRC260910_021</x:v>
       </x:c>
       <x:c r="M344" t="str">
         <x:v>2026-09-10</x:v>
@@ -15137,649 +15133,36 @@
     </x:row>
     <x:row r="345">
       <x:c r="A345" t="str">
-        <x:v>COMP_DISNEY_CRUISE</x:v>
+        <x:v>COMP_SAFE_BULKERS</x:v>
       </x:c>
       <x:c r="B345" t="str">
-        <x:v>Disney Cruise Line</x:v>
+        <x:v>Safe Bulkers</x:v>
       </x:c>
       <x:c r="C345" t="str">
-        <x:v>Cruise line</x:v>
-      </x:c>
-      <x:c r="D345" t="str">
-        <x:v>Celebration</x:v>
-      </x:c>
+        <x:v>Dry-bulk shipowner</x:v>
+      </x:c>
+      <x:c r="D345"/>
       <x:c r="E345" t="str">
-        <x:v>United States</x:v>
+        <x:v>Global</x:v>
       </x:c>
       <x:c r="F345" t="str">
-        <x:v>The Walt Disney Company</x:v>
+        <x:v>Listed company</x:v>
       </x:c>
       <x:c r="G345" t="str">
-        <x:v>Family ocean cruise; private destinations</x:v>
-      </x:c>
-      <x:c r="H345" t="str"/>
-      <x:c r="I345" t="str"/>
+        <x:v>Dry-bulk shipping; fleet investment</x:v>
+      </x:c>
+      <x:c r="H345"/>
+      <x:c r="I345"/>
       <x:c r="J345" t="str">
-        <x:v>Operates Castaway Cay and Lookout Cay calls.</x:v>
+        <x:v>2026 capital raise for fleet expansion</x:v>
       </x:c>
       <x:c r="K345" t="str">
         <x:v>Active</x:v>
       </x:c>
       <x:c r="L345" t="str">
-        <x:v>SRC133_010</x:v>
+        <x:v>SRC260910_023</x:v>
       </x:c>
       <x:c r="M345" t="str">
-        <x:v>2026-09-10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="346">
-      <x:c r="A346" t="str">
-        <x:v>COMP_VIRGIN_VOYAGES</x:v>
-      </x:c>
-      <x:c r="B346" t="str">
-        <x:v>Virgin Voyages</x:v>
-      </x:c>
-      <x:c r="C346" t="str">
-        <x:v>Cruise line</x:v>
-      </x:c>
-      <x:c r="D346" t="str">
-        <x:v>Plantation</x:v>
-      </x:c>
-      <x:c r="E346" t="str">
-        <x:v>United States</x:v>
-      </x:c>
-      <x:c r="F346" t="str">
-        <x:v>Private</x:v>
-      </x:c>
-      <x:c r="G346" t="str">
-        <x:v>Adults-only ocean cruise; partner beach club</x:v>
-      </x:c>
-      <x:c r="H346" t="str"/>
-      <x:c r="I346" t="str"/>
-      <x:c r="J346" t="str">
-        <x:v>Caribbean and Mediterranean deployment.</x:v>
-      </x:c>
-      <x:c r="K346" t="str">
-        <x:v>Active</x:v>
-      </x:c>
-      <x:c r="L346" t="str">
-        <x:v>SRC133_003</x:v>
-      </x:c>
-      <x:c r="M346" t="str">
-        <x:v>2026-09-10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="347">
-      <x:c r="A347" t="str">
-        <x:v>ORG_NISGAA_NATION</x:v>
-      </x:c>
-      <x:c r="B347" t="str">
-        <x:v>Nisg̱a'a Nation</x:v>
-      </x:c>
-      <x:c r="C347" t="str">
-        <x:v>Indigenous government</x:v>
-      </x:c>
-      <x:c r="D347" t="str"/>
-      <x:c r="E347" t="str">
-        <x:v>Canada</x:v>
-      </x:c>
-      <x:c r="F347" t="str">
-        <x:v>Self-government</x:v>
-      </x:c>
-      <x:c r="G347" t="str">
-        <x:v>Government; economic development</x:v>
-      </x:c>
-      <x:c r="H347" t="str"/>
-      <x:c r="I347" t="str"/>
-      <x:c r="J347" t="str">
-        <x:v>Named participant in the reported Stewart port opening.</x:v>
-      </x:c>
-      <x:c r="K347" t="str">
-        <x:v>Active</x:v>
-      </x:c>
-      <x:c r="L347" t="str">
-        <x:v>SRC133_002</x:v>
-      </x:c>
-      <x:c r="M347" t="str">
-        <x:v>2026-09-10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="348">
-      <x:c r="A348" t="str">
-        <x:v>ORG_TAHLTAN_NATION</x:v>
-      </x:c>
-      <x:c r="B348" t="str">
-        <x:v>Tahltan Nation</x:v>
-      </x:c>
-      <x:c r="C348" t="str">
-        <x:v>Indigenous nation</x:v>
-      </x:c>
-      <x:c r="D348" t="str"/>
-      <x:c r="E348" t="str">
-        <x:v>Canada</x:v>
-      </x:c>
-      <x:c r="F348" t="str">
-        <x:v>Indigenous nation</x:v>
-      </x:c>
-      <x:c r="G348" t="str">
-        <x:v>Government; economic development</x:v>
-      </x:c>
-      <x:c r="H348" t="str"/>
-      <x:c r="I348" t="str"/>
-      <x:c r="J348" t="str">
-        <x:v>Named participant in the reported Stewart port opening.</x:v>
-      </x:c>
-      <x:c r="K348" t="str">
-        <x:v>Active</x:v>
-      </x:c>
-      <x:c r="L348" t="str">
-        <x:v>SRC133_002</x:v>
-      </x:c>
-      <x:c r="M348" t="str">
-        <x:v>2026-09-10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="349">
-      <x:c r="A349" t="str">
-        <x:v>COMP_HUNTER_GROUP</x:v>
-      </x:c>
-      <x:c r="B349" t="str">
-        <x:v>Hunter Group ASA</x:v>
-      </x:c>
-      <x:c r="C349" t="str">
-        <x:v>Tanker company</x:v>
-      </x:c>
-      <x:c r="D349" t="str">
-        <x:v>Oslo</x:v>
-      </x:c>
-      <x:c r="E349" t="str">
-        <x:v>Norway</x:v>
-      </x:c>
-      <x:c r="F349" t="str">
-        <x:v>Public company</x:v>
-      </x:c>
-      <x:c r="G349" t="str">
-        <x:v>Crude-oil tanker exposure; chartering and rate economics</x:v>
-      </x:c>
-      <x:c r="H349" t="str"/>
-      <x:c r="I349" t="str"/>
-      <x:c r="J349" t="str">
-        <x:v>Rate-dispute claimant; current fleet and ownership detail queued for verification.</x:v>
-      </x:c>
-      <x:c r="K349" t="str">
-        <x:v>Active</x:v>
-      </x:c>
-      <x:c r="L349" t="str">
-        <x:v>SRC134_003</x:v>
-      </x:c>
-      <x:c r="M349" t="str">
-        <x:v>2026-09-10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="350">
-      <x:c r="A350" t="str">
-        <x:v>COMP_MERCURIA</x:v>
-      </x:c>
-      <x:c r="B350" t="str">
-        <x:v>Mercuria Energy Group</x:v>
-      </x:c>
-      <x:c r="C350" t="str">
-        <x:v>Commodity trading company</x:v>
-      </x:c>
-      <x:c r="D350" t="str">
-        <x:v>Geneva</x:v>
-      </x:c>
-      <x:c r="E350" t="str">
-        <x:v>Switzerland</x:v>
-      </x:c>
-      <x:c r="F350" t="str">
-        <x:v>Private</x:v>
-      </x:c>
-      <x:c r="G350" t="str">
-        <x:v>Energy trading; shipping; commodities</x:v>
-      </x:c>
-      <x:c r="H350" t="str"/>
-      <x:c r="I350" t="str"/>
-      <x:c r="J350" t="str">
-        <x:v>Reported in earlier Hunter disclosure as counterparty; current article does not independently name the customer.</x:v>
-      </x:c>
-      <x:c r="K350" t="str">
-        <x:v>Active</x:v>
-      </x:c>
-      <x:c r="L350" t="str">
-        <x:v>SRC134_003</x:v>
-      </x:c>
-      <x:c r="M350" t="str">
-        <x:v>2026-09-10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="351">
-      <x:c r="A351" t="str">
-        <x:v>COMP_MSC_SHIPMANAGEMENT</x:v>
-      </x:c>
-      <x:c r="B351" t="str">
-        <x:v>MSC Shipmanagement Limited</x:v>
-      </x:c>
-      <x:c r="C351" t="str">
-        <x:v>Ship management company</x:v>
-      </x:c>
-      <x:c r="D351" t="str">
-        <x:v>Limassol</x:v>
-      </x:c>
-      <x:c r="E351" t="str">
-        <x:v>Cyprus</x:v>
-      </x:c>
-      <x:c r="F351" t="str">
-        <x:v>MSC Group</x:v>
-      </x:c>
-      <x:c r="G351" t="str">
-        <x:v>Technical management; crewing; vessel operations</x:v>
-      </x:c>
-      <x:c r="H351" t="str"/>
-      <x:c r="I351" t="str"/>
-      <x:c r="J351" t="str">
-        <x:v>Defendant in MSC SAMIRA III oily-waste case.</x:v>
-      </x:c>
-      <x:c r="K351" t="str">
-        <x:v>Active / probation</x:v>
-      </x:c>
-      <x:c r="L351" t="str">
-        <x:v>SRC134_005</x:v>
-      </x:c>
-      <x:c r="M351" t="str">
-        <x:v>2026-09-10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="352">
-      <x:c r="A352" t="str">
-        <x:v>COMP_HONG_KONG_SPIRIT</x:v>
-      </x:c>
-      <x:c r="B352" t="str">
-        <x:v>Hong Kong Spirit Shipping and Trading Ltd</x:v>
-      </x:c>
-      <x:c r="C352" t="str">
-        <x:v>Shipowning company</x:v>
-      </x:c>
-      <x:c r="D352" t="str"/>
-      <x:c r="E352" t="str">
-        <x:v>Hong Kong</x:v>
-      </x:c>
-      <x:c r="F352" t="str">
-        <x:v>Private / MSC-linked vessel owner</x:v>
-      </x:c>
-      <x:c r="G352" t="str">
-        <x:v>Ship ownership</x:v>
-      </x:c>
-      <x:c r="H352" t="str"/>
-      <x:c r="I352" t="str"/>
-      <x:c r="J352" t="str">
-        <x:v>Owner of MSC SAMIRA III in reported U.S. pollution case.</x:v>
-      </x:c>
-      <x:c r="K352" t="str">
-        <x:v>Active / probation</x:v>
-      </x:c>
-      <x:c r="L352" t="str">
-        <x:v>SRC134_005</x:v>
-      </x:c>
-      <x:c r="M352" t="str">
-        <x:v>2026-09-10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="353">
-      <x:c r="A353" t="str">
-        <x:v>COMP_NOVATEK</x:v>
-      </x:c>
-      <x:c r="B353" t="str">
-        <x:v>PAO NOVATEK</x:v>
-      </x:c>
-      <x:c r="C353" t="str">
-        <x:v>Energy company</x:v>
-      </x:c>
-      <x:c r="D353" t="str">
-        <x:v>Tarko-Sale</x:v>
-      </x:c>
-      <x:c r="E353" t="str">
-        <x:v>Russia</x:v>
-      </x:c>
-      <x:c r="F353" t="str">
-        <x:v>Public company</x:v>
-      </x:c>
-      <x:c r="G353" t="str">
-        <x:v>Natural gas; LNG; Arctic energy infrastructure</x:v>
-      </x:c>
-      <x:c r="H353" t="str"/>
-      <x:c r="I353" t="str"/>
-      <x:c r="J353" t="str">
-        <x:v>Leads Arctic LNG 2 with a reported 60% interest.</x:v>
-      </x:c>
-      <x:c r="K353" t="str">
-        <x:v>Active / sanctions exposed</x:v>
-      </x:c>
-      <x:c r="L353" t="str">
-        <x:v>SRC134_008</x:v>
-      </x:c>
-      <x:c r="M353" t="str">
-        <x:v>2026-09-10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="354">
-      <x:c r="A354" t="str">
-        <x:v>COMP_ARCTIC_LNG2</x:v>
-      </x:c>
-      <x:c r="B354" t="str">
-        <x:v>Arctic LNG 2 LLC</x:v>
-      </x:c>
-      <x:c r="C354" t="str">
-        <x:v>LNG project company</x:v>
-      </x:c>
-      <x:c r="D354" t="str"/>
-      <x:c r="E354" t="str">
-        <x:v>Russia</x:v>
-      </x:c>
-      <x:c r="F354" t="str">
-        <x:v>NOVATEK-led consortium</x:v>
-      </x:c>
-      <x:c r="G354" t="str">
-        <x:v>LNG production; Arctic export project</x:v>
-      </x:c>
-      <x:c r="H354" t="str"/>
-      <x:c r="I354" t="str"/>
-      <x:c r="J354" t="str">
-        <x:v>Planned 19.8 million tonnes per year; deliveries complicated by sanctions.</x:v>
-      </x:c>
-      <x:c r="K354" t="str">
-        <x:v>Active / constrained</x:v>
-      </x:c>
-      <x:c r="L354" t="str">
-        <x:v>SRC134_008</x:v>
-      </x:c>
-      <x:c r="M354" t="str">
-        <x:v>2026-09-10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="355">
-      <x:c r="A355" t="str">
-        <x:v>COMP_HANWHA_OCEAN</x:v>
-      </x:c>
-      <x:c r="B355" t="str">
-        <x:v>Hanwha Ocean</x:v>
-      </x:c>
-      <x:c r="C355" t="str">
-        <x:v>Shipbuilder</x:v>
-      </x:c>
-      <x:c r="D355" t="str">
-        <x:v>Geoje</x:v>
-      </x:c>
-      <x:c r="E355" t="str">
-        <x:v>South Korea</x:v>
-      </x:c>
-      <x:c r="F355" t="str">
-        <x:v>Hanwha Group</x:v>
-      </x:c>
-      <x:c r="G355" t="str">
-        <x:v>Commercial and naval shipbuilding; offshore</x:v>
-      </x:c>
-      <x:c r="H355" t="str"/>
-      <x:c r="I355" t="str"/>
-      <x:c r="J355" t="str">
-        <x:v>Contract counterparty in Arctic LNG 2 Arc7 carrier dispute.</x:v>
-      </x:c>
-      <x:c r="K355" t="str">
-        <x:v>Active</x:v>
-      </x:c>
-      <x:c r="L355" t="str">
-        <x:v>SRC134_008</x:v>
-      </x:c>
-      <x:c r="M355" t="str">
-        <x:v>2026-09-10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="356">
-      <x:c r="A356" t="str">
-        <x:v>COMP_SOVCOMFLOT</x:v>
-      </x:c>
-      <x:c r="B356" t="str">
-        <x:v>Sovcomflot</x:v>
-      </x:c>
-      <x:c r="C356" t="str">
-        <x:v>Shipping company</x:v>
-      </x:c>
-      <x:c r="D356" t="str">
-        <x:v>Saint Petersburg</x:v>
-      </x:c>
-      <x:c r="E356" t="str">
-        <x:v>Russia</x:v>
-      </x:c>
-      <x:c r="F356" t="str">
-        <x:v>Russian state controlled</x:v>
-      </x:c>
-      <x:c r="G356" t="str">
-        <x:v>Energy shipping; ice-class tankers; LNG carriers</x:v>
-      </x:c>
-      <x:c r="H356" t="str"/>
-      <x:c r="I356" t="str"/>
-      <x:c r="J356" t="str">
-        <x:v>Three Hanwha Arc7 LNG-carrier orders were reported canceled due to sanctions.</x:v>
-      </x:c>
-      <x:c r="K356" t="str">
-        <x:v>Active / sanctions exposed</x:v>
-      </x:c>
-      <x:c r="L356" t="str">
-        <x:v>SRC134_008</x:v>
-      </x:c>
-      <x:c r="M356" t="str">
-        <x:v>2026-09-10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="357">
-      <x:c r="A357" t="str">
-        <x:v>COMP_SIAMGAS</x:v>
-      </x:c>
-      <x:c r="B357" t="str">
-        <x:v>Siamgas and Petrochemicals Public Company Limited</x:v>
-      </x:c>
-      <x:c r="C357" t="str">
-        <x:v>Company</x:v>
-      </x:c>
-      <x:c r="D357" t="str">
-        <x:v>Bangkok</x:v>
-      </x:c>
-      <x:c r="E357" t="str">
-        <x:v>Thailand</x:v>
-      </x:c>
-      <x:c r="F357" t="str">
-        <x:v>Public / SET-listed</x:v>
-      </x:c>
-      <x:c r="G357" t="str">
-        <x:v>Energy; LPG terminals; marine transport; logistics infrastructure</x:v>
-      </x:c>
-      <x:c r="H357"/>
-      <x:c r="I357"/>
-      <x:c r="J357" t="str">
-        <x:v>Regional energy and terminal network across Thailand and East Asia</x:v>
-      </x:c>
-      <x:c r="K357" t="str">
-        <x:v>Active</x:v>
-      </x:c>
-      <x:c r="L357" t="str">
-        <x:v>SRC_0391</x:v>
-      </x:c>
-      <x:c r="M357" t="str">
-        <x:v>2026-09-10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="358">
-      <x:c r="A358" t="str">
-        <x:v>COMP_SUKSAWAT_TERMINAL</x:v>
-      </x:c>
-      <x:c r="B358" t="str">
-        <x:v>Suksawat Terminal Co.</x:v>
-      </x:c>
-      <x:c r="C358" t="str">
-        <x:v>Company</x:v>
-      </x:c>
-      <x:c r="D358" t="str">
-        <x:v>Samut Prakan</x:v>
-      </x:c>
-      <x:c r="E358" t="str">
-        <x:v>Thailand</x:v>
-      </x:c>
-      <x:c r="F358" t="str">
-        <x:v>Operating company associated with Suksawat Terminal</x:v>
-      </x:c>
-      <x:c r="G358" t="str">
-        <x:v>River terminal operations; containers; barge connectivity</x:v>
-      </x:c>
-      <x:c r="H358"/>
-      <x:c r="I358"/>
-      <x:c r="J358" t="str">
-        <x:v>Operates Suksawat Terminal on the Chao Phraya River</x:v>
-      </x:c>
-      <x:c r="K358" t="str">
-        <x:v>Active</x:v>
-      </x:c>
-      <x:c r="L358" t="str">
-        <x:v>SRC_0381</x:v>
-      </x:c>
-      <x:c r="M358" t="str">
-        <x:v>2026-09-10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="359">
-      <x:c r="A359" s="14" t="str">
-        <x:v>COMP_GASLOG</x:v>
-      </x:c>
-      <x:c r="B359" s="14" t="str">
-        <x:v>GasLog Ltd</x:v>
-      </x:c>
-      <x:c r="C359" s="14" t="str">
-        <x:v>Company</x:v>
-      </x:c>
-      <x:c r="D359" s="14" t="str">
-        <x:v>Piraeus</x:v>
-      </x:c>
-      <x:c r="E359" s="14" t="str">
-        <x:v>Greece</x:v>
-      </x:c>
-      <x:c r="F359" s="14" t="str">
-        <x:v>Publicly listed group / shipping company</x:v>
-      </x:c>
-      <x:c r="G359" s="14" t="str">
-        <x:v>LNG shipping; vessel management</x:v>
-      </x:c>
-      <x:c r="H359" s="14"/>
-      <x:c r="I359" s="14"/>
-      <x:c r="J359" s="14" t="str">
-        <x:v>Sample canonical counterparty for PGSA/STSs and LNG security exposure</x:v>
-      </x:c>
-      <x:c r="K359" s="14" t="str">
-        <x:v>Active</x:v>
-      </x:c>
-      <x:c r="L359" s="14" t="str">
-        <x:v>SRC_SEC_GASLOG</x:v>
-      </x:c>
-      <x:c r="M359" s="14" t="str">
-        <x:v>2026-09-10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="360">
-      <x:c r="A360" s="14" t="str">
-        <x:v>COMP_CL_GAS_THREE</x:v>
-      </x:c>
-      <x:c r="B360" s="14" t="str">
-        <x:v>CL Gas Three Ltd</x:v>
-      </x:c>
-      <x:c r="C360" s="14" t="str">
-        <x:v>Company</x:v>
-      </x:c>
-      <x:c r="D360" s="14"/>
-      <x:c r="E360" s="14" t="str">
-        <x:v>Greece / Bermuda-linked vessel structure</x:v>
-      </x:c>
-      <x:c r="F360" s="14" t="str">
-        <x:v>Special-purpose registered owner</x:v>
-      </x:c>
-      <x:c r="G360" s="14" t="str">
-        <x:v>Vessel ownership</x:v>
-      </x:c>
-      <x:c r="H360" s="14"/>
-      <x:c r="I360" s="14"/>
-      <x:c r="J360" s="14" t="str">
-        <x:v>Registered owner associated with GasLog Shanghai; source-reported</x:v>
-      </x:c>
-      <x:c r="K360" s="14" t="str">
-        <x:v>Active</x:v>
-      </x:c>
-      <x:c r="L360" s="14" t="str">
-        <x:v>SRC_SEC_GASLOG</x:v>
-      </x:c>
-      <x:c r="M360" s="14" t="str">
-        <x:v>2026-09-10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="361">
-      <x:c r="A361" s="14" t="str">
-        <x:v>COMP_NAKILAT_HHI1910</x:v>
-      </x:c>
-      <x:c r="B361" s="14" t="str">
-        <x:v>Nakilat HHI 1910 Inc.</x:v>
-      </x:c>
-      <x:c r="C361" s="14" t="str">
-        <x:v>Company</x:v>
-      </x:c>
-      <x:c r="D361" s="14"/>
-      <x:c r="E361" s="14"/>
-      <x:c r="F361" s="14" t="str">
-        <x:v>Special-purpose vessel owner</x:v>
-      </x:c>
-      <x:c r="G361" s="14" t="str">
-        <x:v>LNG vessel ownership</x:v>
-      </x:c>
-      <x:c r="H361" s="14"/>
-      <x:c r="I361" s="14"/>
-      <x:c r="J361" s="14" t="str">
-        <x:v>Registered owner associated with Al Rekayyat; source-reported</x:v>
-      </x:c>
-      <x:c r="K361" s="14" t="str">
-        <x:v>Active</x:v>
-      </x:c>
-      <x:c r="L361" s="14" t="str">
-        <x:v>SRC_SEC_ALREK</x:v>
-      </x:c>
-      <x:c r="M361" s="14" t="str">
-        <x:v>2026-09-10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="362">
-      <x:c r="A362" s="14" t="str">
-        <x:v>COMP_STASCO_SM</x:v>
-      </x:c>
-      <x:c r="B362" s="14" t="str">
-        <x:v>STASCO Ship Management</x:v>
-      </x:c>
-      <x:c r="C362" s="14" t="str">
-        <x:v>Company</x:v>
-      </x:c>
-      <x:c r="D362" s="14"/>
-      <x:c r="E362" s="14"/>
-      <x:c r="F362" s="14" t="str">
-        <x:v>Ship manager / operator</x:v>
-      </x:c>
-      <x:c r="G362" s="14" t="str">
-        <x:v>Ship management</x:v>
-      </x:c>
-      <x:c r="H362" s="14"/>
-      <x:c r="I362" s="14"/>
-      <x:c r="J362" s="14" t="str">
-        <x:v>Source-reported operator/manager associated with Al Rekayyat</x:v>
-      </x:c>
-      <x:c r="K362" s="14" t="str">
-        <x:v>Active</x:v>
-      </x:c>
-      <x:c r="L362" s="14" t="str">
-        <x:v>SRC_SEC_ALREK</x:v>
-      </x:c>
-      <x:c r="M362" s="14" t="str">
         <x:v>2026-09-10</x:v>
       </x:c>
     </x:row>
@@ -51478,694 +50861,6 @@
       <x:c r="E1900"/>
       <x:c r="F1900" t="str">
         <x:v>Active</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1901">
-      <x:c r="A1901" t="str">
-        <x:v>COMP_PENINSULA</x:v>
-      </x:c>
-      <x:c r="B1901" t="str">
-        <x:v>Company</x:v>
-      </x:c>
-      <x:c r="C1901" t="str">
-        <x:v>Peninsula</x:v>
-      </x:c>
-      <x:c r="D1901" t="str">
-        <x:v>Gibraltar</x:v>
-      </x:c>
-      <x:c r="E1901" t="str"/>
-      <x:c r="F1901" t="str">
-        <x:v>Active</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1902">
-      <x:c r="A1902" t="str">
-        <x:v>COMP_HERCULES_TANKER</x:v>
-      </x:c>
-      <x:c r="B1902" t="str">
-        <x:v>Company</x:v>
-      </x:c>
-      <x:c r="C1902" t="str">
-        <x:v>Hercules Tanker Management</x:v>
-      </x:c>
-      <x:c r="D1902" t="str">
-        <x:v>Gibraltar</x:v>
-      </x:c>
-      <x:c r="E1902" t="str"/>
-      <x:c r="F1902" t="str">
-        <x:v>Active</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1903">
-      <x:c r="A1903" t="str">
-        <x:v>COMP_SAFEEN_MARINE</x:v>
-      </x:c>
-      <x:c r="B1903" t="str">
-        <x:v>Company</x:v>
-      </x:c>
-      <x:c r="C1903" t="str">
-        <x:v>SAFEEN Marine Services</x:v>
-      </x:c>
-      <x:c r="D1903" t="str">
-        <x:v>United Arab Emirates</x:v>
-      </x:c>
-      <x:c r="E1903" t="str"/>
-      <x:c r="F1903" t="str">
-        <x:v>Active</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1904">
-      <x:c r="A1904" t="str">
-        <x:v>COMP_SAFEEN_OFFSHORE</x:v>
-      </x:c>
-      <x:c r="B1904" t="str">
-        <x:v>Company</x:v>
-      </x:c>
-      <x:c r="C1904" t="str">
-        <x:v>SAFEEN Offshore</x:v>
-      </x:c>
-      <x:c r="D1904" t="str">
-        <x:v>United Arab Emirates</x:v>
-      </x:c>
-      <x:c r="E1904" t="str"/>
-      <x:c r="F1904" t="str">
-        <x:v>Active</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1905">
-      <x:c r="A1905" t="str">
-        <x:v>COMP_ROYAL_CARIBBEAN_GROUP</x:v>
-      </x:c>
-      <x:c r="B1905" t="str">
-        <x:v>Company</x:v>
-      </x:c>
-      <x:c r="C1905" t="str">
-        <x:v>Royal Caribbean Group</x:v>
-      </x:c>
-      <x:c r="D1905" t="str">
-        <x:v>United States</x:v>
-      </x:c>
-      <x:c r="E1905" t="str"/>
-      <x:c r="F1905" t="str">
-        <x:v>Active</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1906">
-      <x:c r="A1906" t="str">
-        <x:v>COMP_ROYAL_CARIBBEAN_INTL</x:v>
-      </x:c>
-      <x:c r="B1906" t="str">
-        <x:v>Company</x:v>
-      </x:c>
-      <x:c r="C1906" t="str">
-        <x:v>Royal Caribbean International</x:v>
-      </x:c>
-      <x:c r="D1906" t="str">
-        <x:v>United States</x:v>
-      </x:c>
-      <x:c r="E1906" t="str"/>
-      <x:c r="F1906" t="str">
-        <x:v>Active</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1907">
-      <x:c r="A1907" t="str">
-        <x:v>COMP_CELEBRITY_CRUISES</x:v>
-      </x:c>
-      <x:c r="B1907" t="str">
-        <x:v>Company</x:v>
-      </x:c>
-      <x:c r="C1907" t="str">
-        <x:v>Celebrity Cruises</x:v>
-      </x:c>
-      <x:c r="D1907" t="str">
-        <x:v>United States</x:v>
-      </x:c>
-      <x:c r="E1907" t="str"/>
-      <x:c r="F1907" t="str">
-        <x:v>Active</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1908">
-      <x:c r="A1908" t="str">
-        <x:v>COMP_SILVERSEA</x:v>
-      </x:c>
-      <x:c r="B1908" t="str">
-        <x:v>Company</x:v>
-      </x:c>
-      <x:c r="C1908" t="str">
-        <x:v>Silversea Cruises</x:v>
-      </x:c>
-      <x:c r="D1908" t="str">
-        <x:v>Monaco</x:v>
-      </x:c>
-      <x:c r="E1908" t="str"/>
-      <x:c r="F1908" t="str">
-        <x:v>Active</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1909">
-      <x:c r="A1909" t="str">
-        <x:v>COMP_CARNIVAL_CORP</x:v>
-      </x:c>
-      <x:c r="B1909" t="str">
-        <x:v>Company</x:v>
-      </x:c>
-      <x:c r="C1909" t="str">
-        <x:v>Carnival Corporation &amp; plc</x:v>
-      </x:c>
-      <x:c r="D1909" t="str">
-        <x:v>United States</x:v>
-      </x:c>
-      <x:c r="E1909" t="str"/>
-      <x:c r="F1909" t="str">
-        <x:v>Active</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1910">
-      <x:c r="A1910" t="str">
-        <x:v>COMP_CARNIVAL_CRUISE</x:v>
-      </x:c>
-      <x:c r="B1910" t="str">
-        <x:v>Company</x:v>
-      </x:c>
-      <x:c r="C1910" t="str">
-        <x:v>Carnival Cruise Line</x:v>
-      </x:c>
-      <x:c r="D1910" t="str">
-        <x:v>United States</x:v>
-      </x:c>
-      <x:c r="E1910" t="str"/>
-      <x:c r="F1910" t="str">
-        <x:v>Active</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1911">
-      <x:c r="A1911" t="str">
-        <x:v>COMP_PRINCESS_CRUISES</x:v>
-      </x:c>
-      <x:c r="B1911" t="str">
-        <x:v>Company</x:v>
-      </x:c>
-      <x:c r="C1911" t="str">
-        <x:v>Princess Cruises</x:v>
-      </x:c>
-      <x:c r="D1911" t="str">
-        <x:v>United States</x:v>
-      </x:c>
-      <x:c r="E1911" t="str"/>
-      <x:c r="F1911" t="str">
-        <x:v>Active</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1912">
-      <x:c r="A1912" t="str">
-        <x:v>COMP_HOLLAND_AMERICA</x:v>
-      </x:c>
-      <x:c r="B1912" t="str">
-        <x:v>Company</x:v>
-      </x:c>
-      <x:c r="C1912" t="str">
-        <x:v>Holland America Line</x:v>
-      </x:c>
-      <x:c r="D1912" t="str">
-        <x:v>United States</x:v>
-      </x:c>
-      <x:c r="E1912" t="str"/>
-      <x:c r="F1912" t="str">
-        <x:v>Active</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1913">
-      <x:c r="A1913" t="str">
-        <x:v>COMP_NCLH</x:v>
-      </x:c>
-      <x:c r="B1913" t="str">
-        <x:v>Company</x:v>
-      </x:c>
-      <x:c r="C1913" t="str">
-        <x:v>Norwegian Cruise Line Holdings</x:v>
-      </x:c>
-      <x:c r="D1913" t="str">
-        <x:v>United States</x:v>
-      </x:c>
-      <x:c r="E1913" t="str"/>
-      <x:c r="F1913" t="str">
-        <x:v>Active</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1914">
-      <x:c r="A1914" t="str">
-        <x:v>COMP_NCL</x:v>
-      </x:c>
-      <x:c r="B1914" t="str">
-        <x:v>Company</x:v>
-      </x:c>
-      <x:c r="C1914" t="str">
-        <x:v>Norwegian Cruise Line</x:v>
-      </x:c>
-      <x:c r="D1914" t="str">
-        <x:v>United States</x:v>
-      </x:c>
-      <x:c r="E1914" t="str"/>
-      <x:c r="F1914" t="str">
-        <x:v>Active</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1915">
-      <x:c r="A1915" t="str">
-        <x:v>COMP_OCEANIA</x:v>
-      </x:c>
-      <x:c r="B1915" t="str">
-        <x:v>Company</x:v>
-      </x:c>
-      <x:c r="C1915" t="str">
-        <x:v>Oceania Cruises</x:v>
-      </x:c>
-      <x:c r="D1915" t="str">
-        <x:v>United States</x:v>
-      </x:c>
-      <x:c r="E1915" t="str"/>
-      <x:c r="F1915" t="str">
-        <x:v>Active</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1916">
-      <x:c r="A1916" t="str">
-        <x:v>COMP_REGENT_SEVEN_SEAS</x:v>
-      </x:c>
-      <x:c r="B1916" t="str">
-        <x:v>Company</x:v>
-      </x:c>
-      <x:c r="C1916" t="str">
-        <x:v>Regent Seven Seas Cruises</x:v>
-      </x:c>
-      <x:c r="D1916" t="str">
-        <x:v>United States</x:v>
-      </x:c>
-      <x:c r="E1916" t="str"/>
-      <x:c r="F1916" t="str">
-        <x:v>Active</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1917">
-      <x:c r="A1917" t="str">
-        <x:v>COMP_DISNEY_CRUISE</x:v>
-      </x:c>
-      <x:c r="B1917" t="str">
-        <x:v>Company</x:v>
-      </x:c>
-      <x:c r="C1917" t="str">
-        <x:v>Disney Cruise Line</x:v>
-      </x:c>
-      <x:c r="D1917" t="str">
-        <x:v>United States</x:v>
-      </x:c>
-      <x:c r="E1917" t="str"/>
-      <x:c r="F1917" t="str">
-        <x:v>Active</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1918">
-      <x:c r="A1918" t="str">
-        <x:v>COMP_VIRGIN_VOYAGES</x:v>
-      </x:c>
-      <x:c r="B1918" t="str">
-        <x:v>Company</x:v>
-      </x:c>
-      <x:c r="C1918" t="str">
-        <x:v>Virgin Voyages</x:v>
-      </x:c>
-      <x:c r="D1918" t="str">
-        <x:v>United States</x:v>
-      </x:c>
-      <x:c r="E1918" t="str"/>
-      <x:c r="F1918" t="str">
-        <x:v>Active</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1919">
-      <x:c r="A1919" t="str">
-        <x:v>ORG_NISGAA_NATION</x:v>
-      </x:c>
-      <x:c r="B1919" t="str">
-        <x:v>Organization</x:v>
-      </x:c>
-      <x:c r="C1919" t="str">
-        <x:v>Nisg̱a'a Nation</x:v>
-      </x:c>
-      <x:c r="D1919" t="str">
-        <x:v>Canada</x:v>
-      </x:c>
-      <x:c r="E1919" t="str"/>
-      <x:c r="F1919" t="str">
-        <x:v>Active</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1920">
-      <x:c r="A1920" t="str">
-        <x:v>ORG_TAHLTAN_NATION</x:v>
-      </x:c>
-      <x:c r="B1920" t="str">
-        <x:v>Organization</x:v>
-      </x:c>
-      <x:c r="C1920" t="str">
-        <x:v>Tahltan Nation</x:v>
-      </x:c>
-      <x:c r="D1920" t="str">
-        <x:v>Canada</x:v>
-      </x:c>
-      <x:c r="E1920" t="str"/>
-      <x:c r="F1920" t="str">
-        <x:v>Active</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1921">
-      <x:c r="A1921" t="str">
-        <x:v>PORT_STEWART_BC</x:v>
-      </x:c>
-      <x:c r="B1921" t="str">
-        <x:v>Port</x:v>
-      </x:c>
-      <x:c r="C1921" t="str">
-        <x:v>Port of Stewart</x:v>
-      </x:c>
-      <x:c r="D1921" t="str">
-        <x:v>Canada</x:v>
-      </x:c>
-      <x:c r="E1921" t="str"/>
-      <x:c r="F1921" t="str">
-        <x:v>Active</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1922">
-      <x:c r="A1922" t="str">
-        <x:v>COMP_HUNTER_GROUP</x:v>
-      </x:c>
-      <x:c r="B1922" t="str">
-        <x:v>Company</x:v>
-      </x:c>
-      <x:c r="C1922" t="str">
-        <x:v>Hunter Group ASA</x:v>
-      </x:c>
-      <x:c r="D1922" t="str">
-        <x:v>Norway</x:v>
-      </x:c>
-      <x:c r="E1922" t="str"/>
-      <x:c r="F1922" t="str">
-        <x:v>Active</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1923">
-      <x:c r="A1923" t="str">
-        <x:v>COMP_MERCURIA</x:v>
-      </x:c>
-      <x:c r="B1923" t="str">
-        <x:v>Company</x:v>
-      </x:c>
-      <x:c r="C1923" t="str">
-        <x:v>Mercuria Energy Group</x:v>
-      </x:c>
-      <x:c r="D1923" t="str">
-        <x:v>Switzerland</x:v>
-      </x:c>
-      <x:c r="E1923" t="str"/>
-      <x:c r="F1923" t="str">
-        <x:v>Active</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1924">
-      <x:c r="A1924" t="str">
-        <x:v>COMP_MSC_SHIPMANAGEMENT</x:v>
-      </x:c>
-      <x:c r="B1924" t="str">
-        <x:v>Company</x:v>
-      </x:c>
-      <x:c r="C1924" t="str">
-        <x:v>MSC Shipmanagement Limited</x:v>
-      </x:c>
-      <x:c r="D1924" t="str">
-        <x:v>Cyprus</x:v>
-      </x:c>
-      <x:c r="E1924" t="str"/>
-      <x:c r="F1924" t="str">
-        <x:v>Active / probation</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1925">
-      <x:c r="A1925" t="str">
-        <x:v>COMP_HONG_KONG_SPIRIT</x:v>
-      </x:c>
-      <x:c r="B1925" t="str">
-        <x:v>Company</x:v>
-      </x:c>
-      <x:c r="C1925" t="str">
-        <x:v>Hong Kong Spirit Shipping and Trading Ltd</x:v>
-      </x:c>
-      <x:c r="D1925" t="str">
-        <x:v>Hong Kong</x:v>
-      </x:c>
-      <x:c r="E1925" t="str"/>
-      <x:c r="F1925" t="str">
-        <x:v>Active / probation</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1926">
-      <x:c r="A1926" t="str">
-        <x:v>COMP_NOVATEK</x:v>
-      </x:c>
-      <x:c r="B1926" t="str">
-        <x:v>Company</x:v>
-      </x:c>
-      <x:c r="C1926" t="str">
-        <x:v>PAO NOVATEK</x:v>
-      </x:c>
-      <x:c r="D1926" t="str">
-        <x:v>Russia</x:v>
-      </x:c>
-      <x:c r="E1926" t="str"/>
-      <x:c r="F1926" t="str">
-        <x:v>Active / sanctions exposed</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1927">
-      <x:c r="A1927" t="str">
-        <x:v>COMP_ARCTIC_LNG2</x:v>
-      </x:c>
-      <x:c r="B1927" t="str">
-        <x:v>Company</x:v>
-      </x:c>
-      <x:c r="C1927" t="str">
-        <x:v>Arctic LNG 2 LLC</x:v>
-      </x:c>
-      <x:c r="D1927" t="str">
-        <x:v>Russia</x:v>
-      </x:c>
-      <x:c r="E1927" t="str"/>
-      <x:c r="F1927" t="str">
-        <x:v>Active / constrained</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1928">
-      <x:c r="A1928" t="str">
-        <x:v>COMP_HANWHA_OCEAN</x:v>
-      </x:c>
-      <x:c r="B1928" t="str">
-        <x:v>Company</x:v>
-      </x:c>
-      <x:c r="C1928" t="str">
-        <x:v>Hanwha Ocean</x:v>
-      </x:c>
-      <x:c r="D1928" t="str">
-        <x:v>South Korea</x:v>
-      </x:c>
-      <x:c r="E1928" t="str"/>
-      <x:c r="F1928" t="str">
-        <x:v>Active</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1929">
-      <x:c r="A1929" t="str">
-        <x:v>COMP_SOVCOMFLOT</x:v>
-      </x:c>
-      <x:c r="B1929" t="str">
-        <x:v>Company</x:v>
-      </x:c>
-      <x:c r="C1929" t="str">
-        <x:v>Sovcomflot</x:v>
-      </x:c>
-      <x:c r="D1929" t="str">
-        <x:v>Russia</x:v>
-      </x:c>
-      <x:c r="E1929" t="str"/>
-      <x:c r="F1929" t="str">
-        <x:v>Active / sanctions exposed</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1930">
-      <x:c r="A1930" t="str">
-        <x:v>ORG_MARAD</x:v>
-      </x:c>
-      <x:c r="B1930" t="str">
-        <x:v>U.S. Maritime Administration</x:v>
-      </x:c>
-      <x:c r="C1930" t="str">
-        <x:v>Government agency</x:v>
-      </x:c>
-      <x:c r="D1930" t="str">
-        <x:v>United States</x:v>
-      </x:c>
-      <x:c r="E1930" t="str">
-        <x:v>ORG_US_DOT</x:v>
-      </x:c>
-      <x:c r="F1930" t="str">
-        <x:v>Active</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1931">
-      <x:c r="A1931" t="str">
-        <x:v>ORG_USCG</x:v>
-      </x:c>
-      <x:c r="B1931" t="str">
-        <x:v>United States Coast Guard</x:v>
-      </x:c>
-      <x:c r="C1931" t="str">
-        <x:v>Government agency</x:v>
-      </x:c>
-      <x:c r="D1931" t="str">
-        <x:v>United States</x:v>
-      </x:c>
-      <x:c r="E1931" t="str">
-        <x:v>ORG_US_DHS</x:v>
-      </x:c>
-      <x:c r="F1931" t="str">
-        <x:v>Active</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1932">
-      <x:c r="A1932" t="str">
-        <x:v>ORG_UMICH_NAME</x:v>
-      </x:c>
-      <x:c r="B1932" t="str">
-        <x:v>University of Michigan Department of Naval Architecture and Marine Engineering</x:v>
-      </x:c>
-      <x:c r="C1932" t="str">
-        <x:v>Education institution</x:v>
-      </x:c>
-      <x:c r="D1932" t="str">
-        <x:v>United States</x:v>
-      </x:c>
-      <x:c r="E1932" t="str"/>
-      <x:c r="F1932" t="str">
-        <x:v>Active</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1933">
-      <x:c r="A1933" t="str">
-        <x:v>ORG_NW_MARITIME_CENTER</x:v>
-      </x:c>
-      <x:c r="B1933" t="str">
-        <x:v>Northwest Maritime Center</x:v>
-      </x:c>
-      <x:c r="C1933" t="str">
-        <x:v>Education institution</x:v>
-      </x:c>
-      <x:c r="D1933" t="str">
-        <x:v>United States</x:v>
-      </x:c>
-      <x:c r="E1933" t="str"/>
-      <x:c r="F1933" t="str">
-        <x:v>Active</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1934">
-      <x:c r="A1934" t="str">
-        <x:v>ORG_CHAPMAN_SEAMANSHIP</x:v>
-      </x:c>
-      <x:c r="B1934" t="str">
-        <x:v>Chapman School of Seamanship</x:v>
-      </x:c>
-      <x:c r="C1934" t="str">
-        <x:v>Education institution</x:v>
-      </x:c>
-      <x:c r="D1934" t="str">
-        <x:v>United States</x:v>
-      </x:c>
-      <x:c r="E1934" t="str"/>
-      <x:c r="F1934" t="str">
-        <x:v>Active</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1935">
-      <x:c r="A1935" t="str">
-        <x:v>ORG_BUNKER_HILL_CC</x:v>
-      </x:c>
-      <x:c r="B1935" t="str">
-        <x:v>Bunker Hill Community College</x:v>
-      </x:c>
-      <x:c r="C1935" t="str">
-        <x:v>Education institution</x:v>
-      </x:c>
-      <x:c r="D1935" t="str">
-        <x:v>United States</x:v>
-      </x:c>
-      <x:c r="E1935" t="str"/>
-      <x:c r="F1935" t="str">
-        <x:v>Active</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1936">
-      <x:c r="A1936" t="str">
-        <x:v>ORG_WEBB_INSTITUTE</x:v>
-      </x:c>
-      <x:c r="B1936" t="str">
-        <x:v>Webb Institute</x:v>
-      </x:c>
-      <x:c r="C1936" t="str">
-        <x:v>Education institution</x:v>
-      </x:c>
-      <x:c r="D1936" t="str">
-        <x:v>United States</x:v>
-      </x:c>
-      <x:c r="E1936" t="str"/>
-      <x:c r="F1936" t="str">
-        <x:v>Active</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1937">
-      <x:c r="A1937" t="str">
-        <x:v>VES_MSC_SAMIRA_III</x:v>
-      </x:c>
-      <x:c r="B1937" t="str">
-        <x:v>Vessel</x:v>
-      </x:c>
-      <x:c r="C1937" t="str">
-        <x:v>MSC SAMIRA III</x:v>
-      </x:c>
-      <x:c r="D1937" t="str"/>
-      <x:c r="E1937" t="str"/>
-      <x:c r="F1937" t="str">
-        <x:v>Active / compliance case</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1938">
-      <x:c r="A1938" t="str">
-        <x:v>ASSET_ARCTIC_LNG2</x:v>
-      </x:c>
-      <x:c r="B1938" t="str">
-        <x:v>Energy asset</x:v>
-      </x:c>
-      <x:c r="C1938" t="str">
-        <x:v>Arctic LNG 2</x:v>
-      </x:c>
-      <x:c r="D1938" t="str">
-        <x:v>Russia</x:v>
-      </x:c>
-      <x:c r="E1938" t="str">
-        <x:v>COMP_ARCTIC_LNG2</x:v>
-      </x:c>
-      <x:c r="F1938" t="str">
-        <x:v>Operating / sanctions constrained</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -56402,673 +55097,6 @@
       </x:c>
       <x:c r="G183" t="str">
         <x:v>SRC132_004</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="184">
-      <x:c r="A184" t="str">
-        <x:v>REL133_001</x:v>
-      </x:c>
-      <x:c r="B184" t="str">
-        <x:v>COMP_SAFEEN_MARINE</x:v>
-      </x:c>
-      <x:c r="C184" t="str">
-        <x:v>PART_OF</x:v>
-      </x:c>
-      <x:c r="D184" t="str">
-        <x:v>COMP_ADPORTS</x:v>
-      </x:c>
-      <x:c r="E184" t="str">
-        <x:v>2026-09-10</x:v>
-      </x:c>
-      <x:c r="F184" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="G184" t="str">
-        <x:v>SRC133_006</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="185">
-      <x:c r="A185" t="str">
-        <x:v>REL133_002</x:v>
-      </x:c>
-      <x:c r="B185" t="str">
-        <x:v>COMP_SAFEEN_OFFSHORE</x:v>
-      </x:c>
-      <x:c r="C185" t="str">
-        <x:v>PART_OF</x:v>
-      </x:c>
-      <x:c r="D185" t="str">
-        <x:v>COMP_ADPORTS</x:v>
-      </x:c>
-      <x:c r="E185" t="str">
-        <x:v>2026-09-10</x:v>
-      </x:c>
-      <x:c r="F185" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="G185" t="str">
-        <x:v>SRC133_004</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="186">
-      <x:c r="A186" t="str">
-        <x:v>REL133_003</x:v>
-      </x:c>
-      <x:c r="B186" t="str">
-        <x:v>COMP_SAFEEN_MARINE</x:v>
-      </x:c>
-      <x:c r="C186" t="str">
-        <x:v>GROUP_ECOSYSTEM_LINK</x:v>
-      </x:c>
-      <x:c r="D186" t="str">
-        <x:v>COMP_NOATUM_MARITIME</x:v>
-      </x:c>
-      <x:c r="E186" t="str">
-        <x:v>2026-09-10</x:v>
-      </x:c>
-      <x:c r="F186" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="G186" t="str">
-        <x:v>SRC133_006</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="187">
-      <x:c r="A187" t="str">
-        <x:v>REL133_004</x:v>
-      </x:c>
-      <x:c r="B187" t="str">
-        <x:v>COMP_SAFEEN_OFFSHORE</x:v>
-      </x:c>
-      <x:c r="C187" t="str">
-        <x:v>GROUP_ECOSYSTEM_LINK</x:v>
-      </x:c>
-      <x:c r="D187" t="str">
-        <x:v>COMP_NOATUM_MARITIME</x:v>
-      </x:c>
-      <x:c r="E187" t="str">
-        <x:v>2026-09-10</x:v>
-      </x:c>
-      <x:c r="F187" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="G187" t="str">
-        <x:v>SRC133_004</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="188">
-      <x:c r="A188" t="str">
-        <x:v>REL133_005</x:v>
-      </x:c>
-      <x:c r="B188" t="str">
-        <x:v>COMP_HERCULES_TANKER</x:v>
-      </x:c>
-      <x:c r="C188" t="str">
-        <x:v>SISTER_COMPANY_OF</x:v>
-      </x:c>
-      <x:c r="D188" t="str">
-        <x:v>COMP_PENINSULA</x:v>
-      </x:c>
-      <x:c r="E188" t="str">
-        <x:v>2026-09-09</x:v>
-      </x:c>
-      <x:c r="F188" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="G188" t="str">
-        <x:v>SRC133_001</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="189">
-      <x:c r="A189" t="str">
-        <x:v>REL133_006</x:v>
-      </x:c>
-      <x:c r="B189" t="str">
-        <x:v>COMP_ROYAL_CARIBBEAN_INTL</x:v>
-      </x:c>
-      <x:c r="C189" t="str">
-        <x:v>BRAND_OF</x:v>
-      </x:c>
-      <x:c r="D189" t="str">
-        <x:v>COMP_ROYAL_CARIBBEAN_GROUP</x:v>
-      </x:c>
-      <x:c r="E189" t="str">
-        <x:v>2026-09-10</x:v>
-      </x:c>
-      <x:c r="F189" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="G189" t="str">
-        <x:v>SRC133_003</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="190">
-      <x:c r="A190" t="str">
-        <x:v>REL133_007</x:v>
-      </x:c>
-      <x:c r="B190" t="str">
-        <x:v>COMP_CELEBRITY_CRUISES</x:v>
-      </x:c>
-      <x:c r="C190" t="str">
-        <x:v>BRAND_OF</x:v>
-      </x:c>
-      <x:c r="D190" t="str">
-        <x:v>COMP_ROYAL_CARIBBEAN_GROUP</x:v>
-      </x:c>
-      <x:c r="E190" t="str">
-        <x:v>2026-09-10</x:v>
-      </x:c>
-      <x:c r="F190" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="G190" t="str">
-        <x:v>SRC133_003</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="191">
-      <x:c r="A191" t="str">
-        <x:v>REL133_008</x:v>
-      </x:c>
-      <x:c r="B191" t="str">
-        <x:v>COMP_SILVERSEA</x:v>
-      </x:c>
-      <x:c r="C191" t="str">
-        <x:v>BRAND_OF</x:v>
-      </x:c>
-      <x:c r="D191" t="str">
-        <x:v>COMP_ROYAL_CARIBBEAN_GROUP</x:v>
-      </x:c>
-      <x:c r="E191" t="str">
-        <x:v>2026-09-10</x:v>
-      </x:c>
-      <x:c r="F191" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="G191" t="str">
-        <x:v>SRC133_003</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="192">
-      <x:c r="A192" t="str">
-        <x:v>REL133_009</x:v>
-      </x:c>
-      <x:c r="B192" t="str">
-        <x:v>COMP_CARNIVAL_CRUISE</x:v>
-      </x:c>
-      <x:c r="C192" t="str">
-        <x:v>BRAND_OF</x:v>
-      </x:c>
-      <x:c r="D192" t="str">
-        <x:v>COMP_CARNIVAL_CORP</x:v>
-      </x:c>
-      <x:c r="E192" t="str">
-        <x:v>2026-09-10</x:v>
-      </x:c>
-      <x:c r="F192" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="G192" t="str">
-        <x:v>SRC133_003</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="193">
-      <x:c r="A193" t="str">
-        <x:v>REL133_010</x:v>
-      </x:c>
-      <x:c r="B193" t="str">
-        <x:v>COMP_PRINCESS_CRUISES</x:v>
-      </x:c>
-      <x:c r="C193" t="str">
-        <x:v>BRAND_OF</x:v>
-      </x:c>
-      <x:c r="D193" t="str">
-        <x:v>COMP_CARNIVAL_CORP</x:v>
-      </x:c>
-      <x:c r="E193" t="str">
-        <x:v>2026-09-10</x:v>
-      </x:c>
-      <x:c r="F193" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="G193" t="str">
-        <x:v>SRC133_003</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="194">
-      <x:c r="A194" t="str">
-        <x:v>REL133_011</x:v>
-      </x:c>
-      <x:c r="B194" t="str">
-        <x:v>COMP_HOLLAND_AMERICA</x:v>
-      </x:c>
-      <x:c r="C194" t="str">
-        <x:v>BRAND_OF</x:v>
-      </x:c>
-      <x:c r="D194" t="str">
-        <x:v>COMP_CARNIVAL_CORP</x:v>
-      </x:c>
-      <x:c r="E194" t="str">
-        <x:v>2026-09-10</x:v>
-      </x:c>
-      <x:c r="F194" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="G194" t="str">
-        <x:v>SRC133_003</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="195">
-      <x:c r="A195" t="str">
-        <x:v>REL133_012</x:v>
-      </x:c>
-      <x:c r="B195" t="str">
-        <x:v>COMP_NCL</x:v>
-      </x:c>
-      <x:c r="C195" t="str">
-        <x:v>BRAND_OF</x:v>
-      </x:c>
-      <x:c r="D195" t="str">
-        <x:v>COMP_NCLH</x:v>
-      </x:c>
-      <x:c r="E195" t="str">
-        <x:v>2026-09-10</x:v>
-      </x:c>
-      <x:c r="F195" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="G195" t="str">
-        <x:v>SRC133_003</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="196">
-      <x:c r="A196" t="str">
-        <x:v>REL133_013</x:v>
-      </x:c>
-      <x:c r="B196" t="str">
-        <x:v>COMP_OCEANIA</x:v>
-      </x:c>
-      <x:c r="C196" t="str">
-        <x:v>BRAND_OF</x:v>
-      </x:c>
-      <x:c r="D196" t="str">
-        <x:v>COMP_NCLH</x:v>
-      </x:c>
-      <x:c r="E196" t="str">
-        <x:v>2026-09-10</x:v>
-      </x:c>
-      <x:c r="F196" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="G196" t="str">
-        <x:v>SRC133_003</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="197">
-      <x:c r="A197" t="str">
-        <x:v>REL133_014</x:v>
-      </x:c>
-      <x:c r="B197" t="str">
-        <x:v>COMP_REGENT_SEVEN_SEAS</x:v>
-      </x:c>
-      <x:c r="C197" t="str">
-        <x:v>BRAND_OF</x:v>
-      </x:c>
-      <x:c r="D197" t="str">
-        <x:v>COMP_NCLH</x:v>
-      </x:c>
-      <x:c r="E197" t="str">
-        <x:v>2026-09-10</x:v>
-      </x:c>
-      <x:c r="F197" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="G197" t="str">
-        <x:v>SRC133_003</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="198">
-      <x:c r="A198" t="str">
-        <x:v>REL133_015</x:v>
-      </x:c>
-      <x:c r="B198" t="str">
-        <x:v>ORG_NISGAA_NATION</x:v>
-      </x:c>
-      <x:c r="C198" t="str">
-        <x:v>PORT_OPENING_PARTICIPANT</x:v>
-      </x:c>
-      <x:c r="D198" t="str">
-        <x:v>PORT_STEWART_BC</x:v>
-      </x:c>
-      <x:c r="E198" t="str">
-        <x:v>2026-09-10</x:v>
-      </x:c>
-      <x:c r="F198" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-      <x:c r="G198" t="str">
-        <x:v>SRC133_002</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="199">
-      <x:c r="A199" t="str">
-        <x:v>REL133_016</x:v>
-      </x:c>
-      <x:c r="B199" t="str">
-        <x:v>ORG_TAHLTAN_NATION</x:v>
-      </x:c>
-      <x:c r="C199" t="str">
-        <x:v>PORT_OPENING_PARTICIPANT</x:v>
-      </x:c>
-      <x:c r="D199" t="str">
-        <x:v>PORT_STEWART_BC</x:v>
-      </x:c>
-      <x:c r="E199" t="str">
-        <x:v>2026-09-10</x:v>
-      </x:c>
-      <x:c r="F199" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-      <x:c r="G199" t="str">
-        <x:v>SRC133_002</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="200">
-      <x:c r="A200" t="str">
-        <x:v>REL134_001</x:v>
-      </x:c>
-      <x:c r="B200" t="str">
-        <x:v>COMP_NOVATEK</x:v>
-      </x:c>
-      <x:c r="C200" t="str">
-        <x:v>CONTROLS_60_PERCENT</x:v>
-      </x:c>
-      <x:c r="D200" t="str">
-        <x:v>COMP_ARCTIC_LNG2</x:v>
-      </x:c>
-      <x:c r="E200" t="str">
-        <x:v>2026-09-08</x:v>
-      </x:c>
-      <x:c r="F200" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="G200" t="str">
-        <x:v>SRC134_008</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="201">
-      <x:c r="A201" t="str">
-        <x:v>REL134_002</x:v>
-      </x:c>
-      <x:c r="B201" t="str">
-        <x:v>COMP_HANWHA_OCEAN</x:v>
-      </x:c>
-      <x:c r="C201" t="str">
-        <x:v>PART_OF</x:v>
-      </x:c>
-      <x:c r="D201" t="str">
-        <x:v>COMP_HANWHA_GROUP</x:v>
-      </x:c>
-      <x:c r="E201" t="str">
-        <x:v>2026-09-08</x:v>
-      </x:c>
-      <x:c r="F201" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="G201" t="str">
-        <x:v>SRC134_008</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="202">
-      <x:c r="A202" t="str">
-        <x:v>REL134_003</x:v>
-      </x:c>
-      <x:c r="B202" t="str">
-        <x:v>COMP_MSC_SHIPMANAGEMENT</x:v>
-      </x:c>
-      <x:c r="C202" t="str">
-        <x:v>PART_OF</x:v>
-      </x:c>
-      <x:c r="D202" t="str">
-        <x:v>COMP_MSC</x:v>
-      </x:c>
-      <x:c r="E202" t="str">
-        <x:v>2026-09-08</x:v>
-      </x:c>
-      <x:c r="F202" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-      <x:c r="G202" t="str">
-        <x:v>SRC134_005</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="203">
-      <x:c r="A203" t="str">
-        <x:v>REL134_004</x:v>
-      </x:c>
-      <x:c r="B203" t="str">
-        <x:v>COMP_HONG_KONG_SPIRIT</x:v>
-      </x:c>
-      <x:c r="C203" t="str">
-        <x:v>OWNS</x:v>
-      </x:c>
-      <x:c r="D203" t="str">
-        <x:v>VES_MSC_SAMIRA_III</x:v>
-      </x:c>
-      <x:c r="E203" t="str">
-        <x:v>2026-09-08</x:v>
-      </x:c>
-      <x:c r="F203" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="G203" t="str">
-        <x:v>SRC134_005</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="204">
-      <x:c r="A204" t="str">
-        <x:v>REL134_005</x:v>
-      </x:c>
-      <x:c r="B204" t="str">
-        <x:v>COMP_MSC_SHIPMANAGEMENT</x:v>
-      </x:c>
-      <x:c r="C204" t="str">
-        <x:v>MANAGES</x:v>
-      </x:c>
-      <x:c r="D204" t="str">
-        <x:v>VES_MSC_SAMIRA_III</x:v>
-      </x:c>
-      <x:c r="E204" t="str">
-        <x:v>2026-09-08</x:v>
-      </x:c>
-      <x:c r="F204" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="G204" t="str">
-        <x:v>SRC134_005</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="205">
-      <x:c r="A205" t="str">
-        <x:v>REL134_006</x:v>
-      </x:c>
-      <x:c r="B205" t="str">
-        <x:v>ORG_MARAD</x:v>
-      </x:c>
-      <x:c r="C205" t="str">
-        <x:v>DESIGNATES</x:v>
-      </x:c>
-      <x:c r="D205" t="str">
-        <x:v>ORG_UMICH_NAME</x:v>
-      </x:c>
-      <x:c r="E205" t="str">
-        <x:v>2026-09-08</x:v>
-      </x:c>
-      <x:c r="F205" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="G205" t="str">
-        <x:v>SRC134_006</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="206">
-      <x:c r="A206" t="str">
-        <x:v>REL134_007</x:v>
-      </x:c>
-      <x:c r="B206" t="str">
-        <x:v>ORG_MARAD</x:v>
-      </x:c>
-      <x:c r="C206" t="str">
-        <x:v>DESIGNATES</x:v>
-      </x:c>
-      <x:c r="D206" t="str">
-        <x:v>ORG_NW_MARITIME_CENTER</x:v>
-      </x:c>
-      <x:c r="E206" t="str">
-        <x:v>2026-09-08</x:v>
-      </x:c>
-      <x:c r="F206" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="G206" t="str">
-        <x:v>SRC134_006</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="207">
-      <x:c r="A207" t="str">
-        <x:v>REL134_008</x:v>
-      </x:c>
-      <x:c r="B207" t="str">
-        <x:v>ORG_MARAD</x:v>
-      </x:c>
-      <x:c r="C207" t="str">
-        <x:v>DESIGNATES</x:v>
-      </x:c>
-      <x:c r="D207" t="str">
-        <x:v>ORG_CHAPMAN_SEAMANSHIP</x:v>
-      </x:c>
-      <x:c r="E207" t="str">
-        <x:v>2026-09-08</x:v>
-      </x:c>
-      <x:c r="F207" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="G207" t="str">
-        <x:v>SRC134_006</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="208">
-      <x:c r="A208" t="str">
-        <x:v>REL134_009</x:v>
-      </x:c>
-      <x:c r="B208" t="str">
-        <x:v>ORG_MARAD</x:v>
-      </x:c>
-      <x:c r="C208" t="str">
-        <x:v>DESIGNATES</x:v>
-      </x:c>
-      <x:c r="D208" t="str">
-        <x:v>ORG_BUNKER_HILL_CC</x:v>
-      </x:c>
-      <x:c r="E208" t="str">
-        <x:v>2026-09-08</x:v>
-      </x:c>
-      <x:c r="F208" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="G208" t="str">
-        <x:v>SRC134_006</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="209">
-      <x:c r="A209" t="str">
-        <x:v>REL134_010</x:v>
-      </x:c>
-      <x:c r="B209" t="str">
-        <x:v>ORG_MARAD</x:v>
-      </x:c>
-      <x:c r="C209" t="str">
-        <x:v>DESIGNATES</x:v>
-      </x:c>
-      <x:c r="D209" t="str">
-        <x:v>ORG_WEBB_INSTITUTE</x:v>
-      </x:c>
-      <x:c r="E209" t="str">
-        <x:v>2026-09-08</x:v>
-      </x:c>
-      <x:c r="F209" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="G209" t="str">
-        <x:v>SRC134_006</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="210">
-      <x:c r="A210" t="str">
-        <x:v>REL_00209</x:v>
-      </x:c>
-      <x:c r="B210" t="str">
-        <x:v>COMP_SUKSAWAT_TERMINAL</x:v>
-      </x:c>
-      <x:c r="C210" t="str">
-        <x:v>PART_OF</x:v>
-      </x:c>
-      <x:c r="D210" t="str">
-        <x:v>COMP_SIAMGAS</x:v>
-      </x:c>
-      <x:c r="E210" t="str">
-        <x:v>2026-09-10</x:v>
-      </x:c>
-      <x:c r="F210" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-      <x:c r="G210" t="str">
-        <x:v>SRC_0381</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="211">
-      <x:c r="A211" t="str">
-        <x:v>REL_00210</x:v>
-      </x:c>
-      <x:c r="B211" t="str">
-        <x:v>COMP_GULFTAINER</x:v>
-      </x:c>
-      <x:c r="C211" t="str">
-        <x:v>INVESTS_IN</x:v>
-      </x:c>
-      <x:c r="D211" t="str">
-        <x:v>COMP_SUKSAWAT_TERMINAL</x:v>
-      </x:c>
-      <x:c r="E211" t="str">
-        <x:v>2026-09-09</x:v>
-      </x:c>
-      <x:c r="F211" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="G211" t="str">
-        <x:v>SRC_0380</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="212">
-      <x:c r="A212" t="str">
-        <x:v>REL_00211</x:v>
-      </x:c>
-      <x:c r="B212" t="str">
-        <x:v>COMP_SIAMGAS</x:v>
-      </x:c>
-      <x:c r="C212" t="str">
-        <x:v>OWNS</x:v>
-      </x:c>
-      <x:c r="D212" t="str">
-        <x:v>COMP_SUKSAWAT_TERMINAL</x:v>
-      </x:c>
-      <x:c r="E212" t="str">
-        <x:v>2026-09-10</x:v>
-      </x:c>
-      <x:c r="F212" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="G212" t="str">
-        <x:v>SRC_0381</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/data/01_core_entities.xlsx
+++ b/data/01_core_entities.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R061ee5595c3740b3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Companies" sheetId="2" r:id="R4106de1ffb6841ac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Entity Registry" sheetId="3" r:id="Rc419496304df4bb6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="Rb6780bbd90974a26"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company System Footprints" sheetId="5" r:id="R9b8de8f6f8ca473b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="People" sheetId="6" r:id="Ra99cd6384d064a66"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leadership Roles" sheetId="7" r:id="Re9ba9c40ae0f4b3c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Dictionary" sheetId="8" r:id="Rf4c7ac1294fc46fa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runtime Table Crosswalk" sheetId="9" r:id="R489cfb8069614929"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Queue" sheetId="10" r:id="Rd2b472657e234114"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="Rb03c2511d49b4674"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Companies" sheetId="2" r:id="R55dcccb408494e89"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Entity Registry" sheetId="3" r:id="R67fe6e8a6bc84538"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="Recf2a9cdc46a47db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company System Footprints" sheetId="5" r:id="Rbff79eb6eae04b39"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="People" sheetId="6" r:id="Ra55664545cc442a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leadership Roles" sheetId="7" r:id="Rba051f8813ef4fbe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Dictionary" sheetId="8" r:id="Rde785dbf97d2436b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runtime Table Crosswalk" sheetId="9" r:id="R2f793b73ab9a4d8d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Queue" sheetId="10" r:id="R31f435542b714bf9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -15166,6 +15166,113 @@
         <x:v>2026-09-10</x:v>
       </x:c>
     </x:row>
+    <x:row r="346">
+      <x:c r="A346" s="14" t="str">
+        <x:v>COMP_CSSC</x:v>
+      </x:c>
+      <x:c r="B346" s="14" t="str">
+        <x:v>China State Shipbuilding Corporation (CSSC)</x:v>
+      </x:c>
+      <x:c r="C346" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="D346" s="14" t="str">
+        <x:v>Beijing</x:v>
+      </x:c>
+      <x:c r="E346" s="14" t="str">
+        <x:v>China</x:v>
+      </x:c>
+      <x:c r="F346" s="14" t="str">
+        <x:v>State-owned enterprise</x:v>
+      </x:c>
+      <x:c r="G346" s="14" t="str">
+        <x:v>Commercial shipbuilding; naval shipbuilding; ship repair; marine equipment</x:v>
+      </x:c>
+      <x:c r="H346" s="14"/>
+      <x:c r="I346" s="14"/>
+      <x:c r="J346" s="14" t="str">
+        <x:v>Major Chinese shipbuilding group; controls Qingdao Beihai Shipbuilding</x:v>
+      </x:c>
+      <x:c r="K346" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L346" s="14" t="str">
+        <x:v>SRC260911_001</x:v>
+      </x:c>
+      <x:c r="M346" s="14" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="347">
+      <x:c r="A347" s="14" t="str">
+        <x:v>COMP_HUILI_SHIPPING</x:v>
+      </x:c>
+      <x:c r="B347" s="14" t="str">
+        <x:v>Huili Shipping Co Ltd</x:v>
+      </x:c>
+      <x:c r="C347" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="D347" s="14"/>
+      <x:c r="E347" s="14"/>
+      <x:c r="F347" s="14" t="str">
+        <x:v>Private</x:v>
+      </x:c>
+      <x:c r="G347" s="14" t="str">
+        <x:v>Ship owning</x:v>
+      </x:c>
+      <x:c r="H347" s="14"/>
+      <x:c r="I347" s="14"/>
+      <x:c r="J347" s="14" t="str">
+        <x:v>Registered owner of bulk carrier Ocean Melody (IMO 9303065)</x:v>
+      </x:c>
+      <x:c r="K347" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L347" s="14" t="str">
+        <x:v>SRC260911_002</x:v>
+      </x:c>
+      <x:c r="M347" s="14" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="348">
+      <x:c r="A348" s="14" t="str">
+        <x:v>COMP_YUYANGKUNPENG</x:v>
+      </x:c>
+      <x:c r="B348" s="14" t="str">
+        <x:v>Yuyangkunpeng Shanghai Ship Management</x:v>
+      </x:c>
+      <x:c r="C348" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="D348" s="14" t="str">
+        <x:v>Shanghai</x:v>
+      </x:c>
+      <x:c r="E348" s="14" t="str">
+        <x:v>China</x:v>
+      </x:c>
+      <x:c r="F348" s="14" t="str">
+        <x:v>Private</x:v>
+      </x:c>
+      <x:c r="G348" s="14" t="str">
+        <x:v>Ship management; technical / ISM management</x:v>
+      </x:c>
+      <x:c r="H348" s="14"/>
+      <x:c r="I348" s="14"/>
+      <x:c r="J348" s="14" t="str">
+        <x:v>Manager of bulk carrier Ocean Melody (IMO 9303065)</x:v>
+      </x:c>
+      <x:c r="K348" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L348" s="14" t="str">
+        <x:v>SRC260911_001</x:v>
+      </x:c>
+      <x:c r="M348" s="14" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -55097,6 +55204,75 @@
       </x:c>
       <x:c r="G183" t="str">
         <x:v>SRC132_004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="184">
+      <x:c r="A184" s="14" t="str">
+        <x:v>REL_00183</x:v>
+      </x:c>
+      <x:c r="B184" s="14" t="str">
+        <x:v>COMP_CSSC</x:v>
+      </x:c>
+      <x:c r="C184" s="14" t="str">
+        <x:v>CONTROLS</x:v>
+      </x:c>
+      <x:c r="D184" s="14" t="str">
+        <x:v>YARD_QINGDAO_BEIHAI</x:v>
+      </x:c>
+      <x:c r="E184" s="14" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="F184" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G184" s="14" t="str">
+        <x:v>SRC260911_001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="185">
+      <x:c r="A185" s="14" t="str">
+        <x:v>REL_00184</x:v>
+      </x:c>
+      <x:c r="B185" s="14" t="str">
+        <x:v>COMP_HUILI_SHIPPING</x:v>
+      </x:c>
+      <x:c r="C185" s="14" t="str">
+        <x:v>REGISTERED_OWNER_OF</x:v>
+      </x:c>
+      <x:c r="D185" s="14" t="str">
+        <x:v>VESSEL_OCEAN_MELODY</x:v>
+      </x:c>
+      <x:c r="E185" s="14" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="F185" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G185" s="14" t="str">
+        <x:v>SRC260911_002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="186">
+      <x:c r="A186" s="14" t="str">
+        <x:v>REL_00185</x:v>
+      </x:c>
+      <x:c r="B186" s="14" t="str">
+        <x:v>COMP_YUYANGKUNPENG</x:v>
+      </x:c>
+      <x:c r="C186" s="14" t="str">
+        <x:v>MANAGES</x:v>
+      </x:c>
+      <x:c r="D186" s="14" t="str">
+        <x:v>VESSEL_OCEAN_MELODY</x:v>
+      </x:c>
+      <x:c r="E186" s="14" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="F186" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G186" s="14" t="str">
+        <x:v>SRC260911_001</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/data/01_core_entities.xlsx
+++ b/data/01_core_entities.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="Re9d9c77cdc184e7f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Companies" sheetId="2" r:id="Rd4b7f834ddd84f9c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Entity Registry" sheetId="3" r:id="Raf8c3d299b184a64"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="R8d31270898794113"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company System Footprints" sheetId="5" r:id="R8ff95576c9004015"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="People" sheetId="6" r:id="Rf8a6d3e44dc5478c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leadership Roles" sheetId="7" r:id="R97540f9e7330477d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Dictionary" sheetId="8" r:id="R64f4c4fbe494448d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runtime Table Crosswalk" sheetId="9" r:id="R27aacfa279bb4e7c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Queue" sheetId="10" r:id="Rc5aa121d39ac4396"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R80b7ca4feebd4b95"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Companies" sheetId="2" r:id="R6218c4ab656c4fa3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Entity Registry" sheetId="3" r:id="R9bf0aa76f44c4229"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="Rc10fa20347874006"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company System Footprints" sheetId="5" r:id="R9a1d7fe3e940499e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="People" sheetId="6" r:id="R7fbea0f014ae4bf6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leadership Roles" sheetId="7" r:id="R590a2f5e5b0d4c8e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Dictionary" sheetId="8" r:id="R73138469564546e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runtime Table Crosswalk" sheetId="9" r:id="R38705536368f4949"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Queue" sheetId="10" r:id="R423cbdb6e0fa495d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -15569,6 +15569,47 @@
         <x:v>2026-09-11</x:v>
       </x:c>
     </x:row>
+    <x:row r="357">
+      <x:c r="A357" t="str">
+        <x:v>COMP_GRSE</x:v>
+      </x:c>
+      <x:c r="B357" t="str">
+        <x:v>Garden Reach Shipbuilders &amp; Engineers Ltd. (GRSE)</x:v>
+      </x:c>
+      <x:c r="C357" t="str">
+        <x:v>Company / defence public sector shipbuilder</x:v>
+      </x:c>
+      <x:c r="D357" t="str">
+        <x:v>Kolkata</x:v>
+      </x:c>
+      <x:c r="E357" t="str">
+        <x:v>India</x:v>
+      </x:c>
+      <x:c r="F357" t="str">
+        <x:v>Government of India / Ministry of Defence; publicly listed PSU</x:v>
+      </x:c>
+      <x:c r="G357" t="str">
+        <x:v>Naval shipbuilding; research vessels; survey vessels; commercial ships; ship repair; engineering</x:v>
+      </x:c>
+      <x:c r="H357" t="str">
+        <x:v>P R Hari</x:v>
+      </x:c>
+      <x:c r="I357" t="str">
+        <x:v>Chairman &amp; Managing Director</x:v>
+      </x:c>
+      <x:c r="J357" t="str">
+        <x:v>Indian shipbuilder; builder of Yard 3041 ORV and Yard 3058 ARS</x:v>
+      </x:c>
+      <x:c r="K357" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L357" t="str">
+        <x:v>SRC_SAGAR_GRSE_AR2025</x:v>
+      </x:c>
+      <x:c r="M357" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -51370,30 +51411,23 @@
       </x:c>
     </x:row>
     <x:row r="1905">
-      <x:c r="A1905" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">VESSEL_SAGAR_MANTHAN</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B1905" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Research Vessel</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C1905" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ORV Sagar Manthan</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D1905" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">India</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F1905" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Launched</x:t>
-        </x:is>
+      <x:c r="A1905" t="str">
+        <x:v>VESSEL_SAGAR_MANTHAN</x:v>
+      </x:c>
+      <x:c r="B1905" t="str">
+        <x:v>Research Vessel</x:v>
+      </x:c>
+      <x:c r="C1905" t="str">
+        <x:v>ORV Sagar Manthan</x:v>
+      </x:c>
+      <x:c r="D1905" t="str">
+        <x:v>India</x:v>
+      </x:c>
+      <x:c r="E1905" t="str">
+        <x:v>GOV_NCPOR</x:v>
+      </x:c>
+      <x:c r="F1905" t="str">
+        <x:v>Launched / outfitting; delivery scheduled 2028</x:v>
       </x:c>
     </x:row>
     <x:row r="1906">
@@ -51727,6 +51761,180 @@
       <x:c r="E1922"/>
       <x:c r="F1922" t="str">
         <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1923">
+      <x:c r="A1923" t="str">
+        <x:v>GOV_MOES_INDIA</x:v>
+      </x:c>
+      <x:c r="B1923" t="str">
+        <x:v>Government Ministry</x:v>
+      </x:c>
+      <x:c r="C1923" t="str">
+        <x:v>Ministry of Earth Sciences (MoES)</x:v>
+      </x:c>
+      <x:c r="D1923" t="str">
+        <x:v>India</x:v>
+      </x:c>
+      <x:c r="E1923"/>
+      <x:c r="F1923" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1924">
+      <x:c r="A1924" t="str">
+        <x:v>GOV_NCPOR</x:v>
+      </x:c>
+      <x:c r="B1924" t="str">
+        <x:v>Government Research Institute</x:v>
+      </x:c>
+      <x:c r="C1924" t="str">
+        <x:v>National Centre for Polar and Ocean Research (NCPOR)</x:v>
+      </x:c>
+      <x:c r="D1924" t="str">
+        <x:v>India</x:v>
+      </x:c>
+      <x:c r="E1924" t="str">
+        <x:v>GOV_MOES_INDIA</x:v>
+      </x:c>
+      <x:c r="F1924" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1925">
+      <x:c r="A1925" t="str">
+        <x:v>GOV_DRDO_INDIA</x:v>
+      </x:c>
+      <x:c r="B1925" t="str">
+        <x:v>Government R&amp;D Organisation</x:v>
+      </x:c>
+      <x:c r="C1925" t="str">
+        <x:v>Defence Research and Development Organisation (DRDO)</x:v>
+      </x:c>
+      <x:c r="D1925" t="str">
+        <x:v>India</x:v>
+      </x:c>
+      <x:c r="E1925"/>
+      <x:c r="F1925" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1926">
+      <x:c r="A1926" t="str">
+        <x:v>GOV_NPOL</x:v>
+      </x:c>
+      <x:c r="B1926" t="str">
+        <x:v>Government Defence Laboratory</x:v>
+      </x:c>
+      <x:c r="C1926" t="str">
+        <x:v>Naval Physical and Oceanographic Laboratory (NPOL)</x:v>
+      </x:c>
+      <x:c r="D1926" t="str">
+        <x:v>India</x:v>
+      </x:c>
+      <x:c r="E1926" t="str">
+        <x:v>GOV_DRDO_INDIA</x:v>
+      </x:c>
+      <x:c r="F1926" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1927">
+      <x:c r="A1927" t="str">
+        <x:v>PROG_DEEP_OCEAN_MISSION</x:v>
+      </x:c>
+      <x:c r="B1927" t="str">
+        <x:v>Government Programme</x:v>
+      </x:c>
+      <x:c r="C1927" t="str">
+        <x:v>Deep Ocean Mission — Vertical 4 Deep Ocean Survey and Exploration</x:v>
+      </x:c>
+      <x:c r="D1927" t="str">
+        <x:v>India</x:v>
+      </x:c>
+      <x:c r="E1927" t="str">
+        <x:v>GOV_MOES_INDIA</x:v>
+      </x:c>
+      <x:c r="F1927" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1928">
+      <x:c r="A1928" t="str">
+        <x:v>COMP_GRSE</x:v>
+      </x:c>
+      <x:c r="B1928" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1928" t="str">
+        <x:v>Garden Reach Shipbuilders &amp; Engineers Ltd. (GRSE)</x:v>
+      </x:c>
+      <x:c r="D1928" t="str">
+        <x:v>India</x:v>
+      </x:c>
+      <x:c r="E1928"/>
+      <x:c r="F1928" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1929">
+      <x:c r="A1929" t="str">
+        <x:v>YARD_GRSE_RISHI_BANKIM</x:v>
+      </x:c>
+      <x:c r="B1929" t="str">
+        <x:v>Shipyard</x:v>
+      </x:c>
+      <x:c r="C1929" t="str">
+        <x:v>GRSE Rishi Bankim Shipyard</x:v>
+      </x:c>
+      <x:c r="D1929" t="str">
+        <x:v>India</x:v>
+      </x:c>
+      <x:c r="E1929" t="str">
+        <x:v>COMP_GRSE</x:v>
+      </x:c>
+      <x:c r="F1929" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1930">
+      <x:c r="A1930" t="str">
+        <x:v>VESSEL_SAGAR_KANYA</x:v>
+      </x:c>
+      <x:c r="B1930" t="str">
+        <x:v>Vessel</x:v>
+      </x:c>
+      <x:c r="C1930" t="str">
+        <x:v>ORV Sagar Kanya</x:v>
+      </x:c>
+      <x:c r="D1930" t="str">
+        <x:v>India</x:v>
+      </x:c>
+      <x:c r="E1930" t="str">
+        <x:v>GOV_MOES_INDIA</x:v>
+      </x:c>
+      <x:c r="F1930" t="str">
+        <x:v>Operating / gradual replacement planned</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1931">
+      <x:c r="A1931" t="str">
+        <x:v>VESSEL_ARS_3058</x:v>
+      </x:c>
+      <x:c r="B1931" t="str">
+        <x:v>Research Vessel</x:v>
+      </x:c>
+      <x:c r="C1931" t="str">
+        <x:v>Acoustic Research Ship — Yard 3058 (name pending)</x:v>
+      </x:c>
+      <x:c r="D1931" t="str">
+        <x:v>India</x:v>
+      </x:c>
+      <x:c r="E1931" t="str">
+        <x:v>GOV_NPOL</x:v>
+      </x:c>
+      <x:c r="F1931" t="str">
+        <x:v>Under construction</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -56216,6 +56424,121 @@
       </x:c>
       <x:c r="G194" t="str">
         <x:v>SRC_BF_TCP_ANP</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="195">
+      <x:c r="A195" t="str">
+        <x:v>REL_SAGAR_001</x:v>
+      </x:c>
+      <x:c r="B195" t="str">
+        <x:v>GOV_NCPOR</x:v>
+      </x:c>
+      <x:c r="C195" t="str">
+        <x:v>PART_OF</x:v>
+      </x:c>
+      <x:c r="D195" t="str">
+        <x:v>GOV_MOES_INDIA</x:v>
+      </x:c>
+      <x:c r="E195" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="F195" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G195" t="str">
+        <x:v>SRC_SAGAR_PIB_LAUNCH</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="196">
+      <x:c r="A196" t="str">
+        <x:v>REL_SAGAR_002</x:v>
+      </x:c>
+      <x:c r="B196" t="str">
+        <x:v>GOV_NPOL</x:v>
+      </x:c>
+      <x:c r="C196" t="str">
+        <x:v>PART_OF</x:v>
+      </x:c>
+      <x:c r="D196" t="str">
+        <x:v>GOV_DRDO_INDIA</x:v>
+      </x:c>
+      <x:c r="E196" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="F196" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G196" t="str">
+        <x:v>SRC_SAGAR_GRSE_ARS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="197">
+      <x:c r="A197" t="str">
+        <x:v>REL_SAGAR_003</x:v>
+      </x:c>
+      <x:c r="B197" t="str">
+        <x:v>PROG_DEEP_OCEAN_MISSION</x:v>
+      </x:c>
+      <x:c r="C197" t="str">
+        <x:v>ADMINISTERED_BY</x:v>
+      </x:c>
+      <x:c r="D197" t="str">
+        <x:v>GOV_MOES_INDIA</x:v>
+      </x:c>
+      <x:c r="E197" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="F197" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G197" t="str">
+        <x:v>SRC_SAGAR_PIB_LAUNCH</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="198">
+      <x:c r="A198" t="str">
+        <x:v>REL_SAGAR_004</x:v>
+      </x:c>
+      <x:c r="B198" t="str">
+        <x:v>VESSEL_SAGAR_MANTHAN</x:v>
+      </x:c>
+      <x:c r="C198" t="str">
+        <x:v>PROGRAMME_ASSET_OF</x:v>
+      </x:c>
+      <x:c r="D198" t="str">
+        <x:v>PROG_DEEP_OCEAN_MISSION</x:v>
+      </x:c>
+      <x:c r="E198" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="F198" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G198" t="str">
+        <x:v>SRC_SAGAR_PIB_LAUNCH</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="199">
+      <x:c r="A199" t="str">
+        <x:v>REL_SAGAR_005</x:v>
+      </x:c>
+      <x:c r="B199" t="str">
+        <x:v>VESSEL_SAGAR_KANYA</x:v>
+      </x:c>
+      <x:c r="C199" t="str">
+        <x:v>OWNED_BY</x:v>
+      </x:c>
+      <x:c r="D199" t="str">
+        <x:v>GOV_MOES_INDIA</x:v>
+      </x:c>
+      <x:c r="E199" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="F199" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G199" t="str">
+        <x:v>SRC_SAGAR_NCPOR_KANYA_TOW</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/data/01_core_entities.xlsx
+++ b/data/01_core_entities.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R80b7ca4feebd4b95"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Companies" sheetId="2" r:id="R6218c4ab656c4fa3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Entity Registry" sheetId="3" r:id="R9bf0aa76f44c4229"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="Rc10fa20347874006"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company System Footprints" sheetId="5" r:id="R9a1d7fe3e940499e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="People" sheetId="6" r:id="R7fbea0f014ae4bf6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leadership Roles" sheetId="7" r:id="R590a2f5e5b0d4c8e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Dictionary" sheetId="8" r:id="R73138469564546e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runtime Table Crosswalk" sheetId="9" r:id="R38705536368f4949"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Queue" sheetId="10" r:id="R423cbdb6e0fa495d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R635465e91a4b459d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Companies" sheetId="2" r:id="Rdd3a519260724d90"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Entity Registry" sheetId="3" r:id="Ree6ef064f47545d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="R4e22319a1f15423d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company System Footprints" sheetId="5" r:id="R8f59fd0e7fdb4c81"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="People" sheetId="6" r:id="R7ab53c16fd344ef8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leadership Roles" sheetId="7" r:id="R67fecba86df54ffb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Dictionary" sheetId="8" r:id="R0a2d7e5f3811431d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runtime Table Crosswalk" sheetId="9" r:id="R4d6e7faecd374260"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Queue" sheetId="10" r:id="Rba761cdba49446c0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -15610,6 +15610,117 @@
         <x:v>2026-09-11</x:v>
       </x:c>
     </x:row>
+    <x:row r="358">
+      <x:c r="A358" t="str">
+        <x:v>COMP_UKRZALIZNYTSIA</x:v>
+      </x:c>
+      <x:c r="B358" t="str">
+        <x:v>Ukrzaliznytsia (Ukrainian Railways)</x:v>
+      </x:c>
+      <x:c r="C358" t="str">
+        <x:v>National railway company</x:v>
+      </x:c>
+      <x:c r="D358" t="str">
+        <x:v>Kyiv</x:v>
+      </x:c>
+      <x:c r="E358" t="str">
+        <x:v>Ukraine</x:v>
+      </x:c>
+      <x:c r="F358" t="str">
+        <x:v>State-owned</x:v>
+      </x:c>
+      <x:c r="G358" t="str">
+        <x:v>Rail freight; passenger rail; terminals; locomotive and infrastructure operations</x:v>
+      </x:c>
+      <x:c r="H358"/>
+      <x:c r="I358"/>
+      <x:c r="J358" t="str">
+        <x:v>National network and critical freight infrastructure</x:v>
+      </x:c>
+      <x:c r="K358" t="str">
+        <x:v>Active / conflict-exposed</x:v>
+      </x:c>
+      <x:c r="L358" t="str">
+        <x:v>SRC_SEC_006</x:v>
+      </x:c>
+      <x:c r="M358" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="359">
+      <x:c r="A359" t="str">
+        <x:v>COMP_NATS_UK</x:v>
+      </x:c>
+      <x:c r="B359" t="str">
+        <x:v>NATS Holdings / NATS</x:v>
+      </x:c>
+      <x:c r="C359" t="str">
+        <x:v>Air navigation service provider</x:v>
+      </x:c>
+      <x:c r="D359" t="str">
+        <x:v>Fareham</x:v>
+      </x:c>
+      <x:c r="E359" t="str">
+        <x:v>United Kingdom</x:v>
+      </x:c>
+      <x:c r="F359" t="str">
+        <x:v>UK air navigation infrastructure operator</x:v>
+      </x:c>
+      <x:c r="G359" t="str">
+        <x:v>Air traffic control; air navigation services</x:v>
+      </x:c>
+      <x:c r="H359"/>
+      <x:c r="I359"/>
+      <x:c r="J359" t="str">
+        <x:v>Critical national aviation infrastructure</x:v>
+      </x:c>
+      <x:c r="K359" t="str">
+        <x:v>Operating / post-disruption recovery</x:v>
+      </x:c>
+      <x:c r="L359" t="str">
+        <x:v>SRC_SEC_008</x:v>
+      </x:c>
+      <x:c r="M359" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="360">
+      <x:c r="A360" t="str">
+        <x:v>COMP_DOLPHIN_SEATRADE</x:v>
+      </x:c>
+      <x:c r="B360" t="str">
+        <x:v>Dolphin Seatrade</x:v>
+      </x:c>
+      <x:c r="C360" t="str">
+        <x:v>Ship manager</x:v>
+      </x:c>
+      <x:c r="D360" t="str">
+        <x:v>Piraeus</x:v>
+      </x:c>
+      <x:c r="E360" t="str">
+        <x:v>Greece</x:v>
+      </x:c>
+      <x:c r="F360" t="str">
+        <x:v>Private</x:v>
+      </x:c>
+      <x:c r="G360" t="str">
+        <x:v>Ship management; general cargo / dry bulk</x:v>
+      </x:c>
+      <x:c r="H360"/>
+      <x:c r="I360"/>
+      <x:c r="J360" t="str">
+        <x:v>Manager of GLAMOR (IMO 9177961) in Sep 2026 piracy incident</x:v>
+      </x:c>
+      <x:c r="K360" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L360" t="str">
+        <x:v>SRC_SEC_003</x:v>
+      </x:c>
+      <x:c r="M360" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -51935,6 +52046,152 @@
       </x:c>
       <x:c r="F1931" t="str">
         <x:v>Under construction</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1932">
+      <x:c r="A1932" t="str">
+        <x:v>PORT_KLAIPEDA</x:v>
+      </x:c>
+      <x:c r="B1932" t="str">
+        <x:v>Port</x:v>
+      </x:c>
+      <x:c r="C1932" t="str">
+        <x:v>Port of Klaipėda</x:v>
+      </x:c>
+      <x:c r="D1932" t="str">
+        <x:v>Lithuania</x:v>
+      </x:c>
+      <x:c r="E1932" t="str">
+        <x:v>COMP_KLAIPEDA_AUTH</x:v>
+      </x:c>
+      <x:c r="F1932" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1933">
+      <x:c r="A1933" t="str">
+        <x:v>AIRPORT_JKIA</x:v>
+      </x:c>
+      <x:c r="B1933" t="str">
+        <x:v>Airport</x:v>
+      </x:c>
+      <x:c r="C1933" t="str">
+        <x:v>Jomo Kenyatta International Airport (JKIA / NBO)</x:v>
+      </x:c>
+      <x:c r="D1933" t="str">
+        <x:v>Kenya</x:v>
+      </x:c>
+      <x:c r="E1933"/>
+      <x:c r="F1933" t="str">
+        <x:v>Operating / labour-disruption exposure</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1934">
+      <x:c r="A1934" t="str">
+        <x:v>COMP_UKRZALIZNYTSIA</x:v>
+      </x:c>
+      <x:c r="B1934" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1934" t="str">
+        <x:v>Ukrzaliznytsia (Ukrainian Railways)</x:v>
+      </x:c>
+      <x:c r="D1934" t="str">
+        <x:v>Ukraine</x:v>
+      </x:c>
+      <x:c r="E1934"/>
+      <x:c r="F1934" t="str">
+        <x:v>Active / conflict-exposed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1935">
+      <x:c r="A1935" t="str">
+        <x:v>COMP_NATS_UK</x:v>
+      </x:c>
+      <x:c r="B1935" t="str">
+        <x:v>Critical Infrastructure Operator</x:v>
+      </x:c>
+      <x:c r="C1935" t="str">
+        <x:v>NATS</x:v>
+      </x:c>
+      <x:c r="D1935" t="str">
+        <x:v>United Kingdom</x:v>
+      </x:c>
+      <x:c r="E1935"/>
+      <x:c r="F1935" t="str">
+        <x:v>Operating / post-disruption recovery</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1936">
+      <x:c r="A1936" t="str">
+        <x:v>CORRIDOR_BAB_EL_MANDEB</x:v>
+      </x:c>
+      <x:c r="B1936" t="str">
+        <x:v>Maritime Chokepoint</x:v>
+      </x:c>
+      <x:c r="C1936" t="str">
+        <x:v>Bab al-Mandab Strait</x:v>
+      </x:c>
+      <x:c r="D1936" t="str">
+        <x:v>Yemen / Djibouti / Eritrea</x:v>
+      </x:c>
+      <x:c r="E1936"/>
+      <x:c r="F1936" t="str">
+        <x:v>Active / elevated security risk</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1937">
+      <x:c r="A1937" t="str">
+        <x:v>AREA_HANISH</x:v>
+      </x:c>
+      <x:c r="B1937" t="str">
+        <x:v>Strategic Maritime Area</x:v>
+      </x:c>
+      <x:c r="C1937" t="str">
+        <x:v>Hanish Islands</x:v>
+      </x:c>
+      <x:c r="D1937" t="str">
+        <x:v>Yemen</x:v>
+      </x:c>
+      <x:c r="E1937"/>
+      <x:c r="F1937" t="str">
+        <x:v>Houthi control reported Sep 2026</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1938">
+      <x:c r="A1938" t="str">
+        <x:v>VESSEL_GLAMOR</x:v>
+      </x:c>
+      <x:c r="B1938" t="str">
+        <x:v>Vessel</x:v>
+      </x:c>
+      <x:c r="C1938" t="str">
+        <x:v>GLAMOR</x:v>
+      </x:c>
+      <x:c r="D1938" t="str">
+        <x:v>Saint Vincent and the Grenadines</x:v>
+      </x:c>
+      <x:c r="E1938"/>
+      <x:c r="F1938" t="str">
+        <x:v>Operating after attempted boarding</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1939">
+      <x:c r="A1939" t="str">
+        <x:v>COMP_DOLPHIN_SEATRADE</x:v>
+      </x:c>
+      <x:c r="B1939" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="C1939" t="str">
+        <x:v>Dolphin Seatrade</x:v>
+      </x:c>
+      <x:c r="D1939" t="str">
+        <x:v>Greece</x:v>
+      </x:c>
+      <x:c r="E1939"/>
+      <x:c r="F1939" t="str">
+        <x:v>Active</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -56539,6 +56796,52 @@
       </x:c>
       <x:c r="G199" t="str">
         <x:v>SRC_SAGAR_NCPOR_KANYA_TOW</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="200">
+      <x:c r="A200" t="str">
+        <x:v>REL_SEC_001</x:v>
+      </x:c>
+      <x:c r="B200" t="str">
+        <x:v>PORT_KLAIPEDA</x:v>
+      </x:c>
+      <x:c r="C200" t="str">
+        <x:v>OPERATED_BY</x:v>
+      </x:c>
+      <x:c r="D200" t="str">
+        <x:v>COMP_KLAIPEDA_AUTH</x:v>
+      </x:c>
+      <x:c r="E200" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="F200" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G200" t="str">
+        <x:v>SRC_SEC_004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="201">
+      <x:c r="A201" t="str">
+        <x:v>REL_SEC_002</x:v>
+      </x:c>
+      <x:c r="B201" t="str">
+        <x:v>VESSEL_GLAMOR</x:v>
+      </x:c>
+      <x:c r="C201" t="str">
+        <x:v>MANAGED_BY</x:v>
+      </x:c>
+      <x:c r="D201" t="str">
+        <x:v>COMP_DOLPHIN_SEATRADE</x:v>
+      </x:c>
+      <x:c r="E201" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="F201" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G201" t="str">
+        <x:v>SRC_SEC_003</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
